--- a/docs/Nucleus_Enhancer_Validation_Results_v3.0.0.xlsx
+++ b/docs/Nucleus_Enhancer_Validation_Results_v3.0.0.xlsx
@@ -23,13 +23,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1391" uniqueCount="641">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1470" uniqueCount="677">
   <si>
     <t xml:space="preserve">How to use this workbook</t>
   </si>
   <si>
     <t xml:space="preserve">Work through the 'Test Cases' sheet top to bottom. For each row set the Result cell (dropdown: Pass / Fail / Partial / N/A / Not run), and record what you saw in 'Actual / notes', plus your initials and the date.
-There are 115 cases across all feature areas.
+There are 122 cases across all feature areas.
 This is an internal self-check, not a formal/Quality validation. Use the Diagnostics sheet (or docs/Nucleus_Enhancer_Diagnostics.md) to capture detail when something misbehaves.</t>
   </si>
   <si>
@@ -1810,6 +1810,114 @@
   </si>
   <si>
     <t xml:space="preserve">Sign-in completes normally; the flow uses PKCE and a CSRF 'state' the extension verifies. A tampered/mismatched callback aborts with STATE_MISMATCH in the service-worker console</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-team membership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User with 2+ NucleusTeamMember__c records (different teams)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connect; open the template menu + manager About</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identity shows 'Team A · Team B'; menu/manager list templates targeted at EITHER team plus Global — and NOTHING from teams the user is not in. Admin if IsAdmin__c is set on any membership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single-team unchanged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User in exactly one team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Connect; open the template menu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Behaves exactly as before — their team's templates + Global; identity shows the one team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acknowledgements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mark a controlled doc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin; a template</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tick 'Requires acknowledgement' on it; Save</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It becomes a controlled document — an Acknowledge chip appears for members of its team(s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Analyst acknowledges</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Template ticked RequiresAck; member of its team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open it in the manager → click 'I have read &amp; understood vX'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chip flips to '✓ Acknowledged'; banner count drops; a NucleusTemplateAck__c record is created (CreatedBy = you)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Re-ack on new version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Already acknowledged a controlled template</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin publishes a new version; re-sync</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shows outstanding again — the old acknowledgement no longer matches the current version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin matrix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin; some acknowledgements recorded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manager → Acknowledgements tab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Per controlled template: acked/total + %, status, and the OUTSTANDING members' names — scoped to the template's assigned team(s)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outstanding nudge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Outstanding controlled templates for you</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trigger a background sync (SF tab open)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At most one browser notification per day; clicking it opens the manager</t>
   </si>
   <si>
     <t xml:space="preserve">UX</t>
@@ -2536,7 +2644,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K145"/>
+  <dimension ref="A1:K153"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7.16"/>
@@ -6891,42 +6999,62 @@
         <v>43</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="11" t="s">
+    <row r="141" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="B141" s="11"/>
-      <c r="C141" s="11"/>
-      <c r="D141" s="11"/>
-      <c r="E141" s="11"/>
-      <c r="F141" s="11"/>
-      <c r="G141" s="11"/>
-      <c r="H141" s="11"/>
-      <c r="I141" s="11"/>
-      <c r="J141" s="11"/>
-      <c r="K141" s="11"/>
-    </row>
-    <row r="142" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B141" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="F141" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="G141" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="H141" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I141" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J141" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K141" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="2" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>595</v>
+        <v>574</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="H142" s="12" t="s">
         <v>43</v>
@@ -6941,47 +7069,27 @@
         <v>43</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="B143" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="C143" s="2" t="s">
-        <v>602</v>
-      </c>
-      <c r="D143" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E143" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="F143" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="G143" s="2" t="s">
+    <row r="143" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="11" t="s">
         <v>605</v>
       </c>
-      <c r="H143" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I143" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J143" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K143" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="144" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B143" s="11"/>
+      <c r="C143" s="11"/>
+      <c r="D143" s="11"/>
+      <c r="E143" s="11"/>
+      <c r="F143" s="11"/>
+      <c r="G143" s="11"/>
+      <c r="H143" s="11"/>
+      <c r="I143" s="11"/>
+      <c r="J143" s="11"/>
+      <c r="K143" s="11"/>
+    </row>
+    <row r="144" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="2" t="s">
         <v>606</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>595</v>
+        <v>605</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>607</v>
@@ -7011,18 +7119,18 @@
         <v>43</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="2" t="s">
         <v>611</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>595</v>
+        <v>605</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>612</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>613</v>
@@ -7046,8 +7154,268 @@
         <v>43</v>
       </c>
     </row>
+    <row r="146" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="F146" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="G146" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="H146" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I146" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J146" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K146" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="F147" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="G147" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="H147" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K147" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="F148" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="G148" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="H148" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K148" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="11" t="s">
+        <v>631</v>
+      </c>
+      <c r="B149" s="11"/>
+      <c r="C149" s="11"/>
+      <c r="D149" s="11"/>
+      <c r="E149" s="11"/>
+      <c r="F149" s="11"/>
+      <c r="G149" s="11"/>
+      <c r="H149" s="11"/>
+      <c r="I149" s="11"/>
+      <c r="J149" s="11"/>
+      <c r="K149" s="11"/>
+    </row>
+    <row r="150" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A150" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="F150" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="G150" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="H150" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I150" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J150" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K150" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="F151" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="G151" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="H151" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I151" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J151" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K151" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="152" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="F152" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="G152" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="H152" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I152" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J152" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K152" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="F153" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="G153" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="H153" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I153" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J153" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K153" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="29">
+  <mergeCells count="30">
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A8:K8"/>
@@ -7076,7 +7444,8 @@
     <mergeCell ref="A130:K130"/>
     <mergeCell ref="A133:K133"/>
     <mergeCell ref="A136:K136"/>
-    <mergeCell ref="A141:K141"/>
+    <mergeCell ref="A143:K143"/>
+    <mergeCell ref="A149:K149"/>
   </mergeCells>
   <conditionalFormatting sqref="H3:H400">
     <cfRule type="cellIs" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -7093,7 +7462,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" prompt="Choose Pass / Fail / Partial / N/A / Not run" promptTitle="Result" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H4:H7 H9:H13 H15:H20 H22:H27 H29:H31 H33 H35:H36 H38:H41 H43:H45 H47:H56 H58:H64 H66:H70 H72 H74:H77 H79:H80 H82:H85 H87:H91 H93:H98 H100:H111 H113:H116 H118:H119 H121:H124 H126:H127 H129 H131:H132 H134:H135 H137:H140 H142:H145" type="none">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" prompt="Choose Pass / Fail / Partial / N/A / Not run" promptTitle="Result" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H4:H7 H9:H13 H15:H20 H22:H27 H29:H31 H33 H35:H36 H38:H41 H43:H45 H47:H56 H58:H64 H66:H70 H72 H74:H77 H79:H80 H82:H85 H87:H91 H93:H98 H100:H111 H113:H116 H118:H119 H121:H124 H126:H127 H129 H131:H132 H134:H135 H137:H142 H144:H148 H150:H153" type="none">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -7113,7 +7482,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.37"/>
@@ -7122,13 +7491,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>616</v>
+        <v>652</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>617</v>
+        <v>653</v>
       </c>
       <c r="B2" s="3"/>
     </row>
@@ -7179,7 +7548,7 @@
     </row>
     <row r="8" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>618</v>
+        <v>654</v>
       </c>
       <c r="B8" s="2" t="e">
         <f aca="false">of:=COUNTA('Test Cases'!A3:A400)-COUNTIF('Test Cases'!D3:D400,"")</f>
@@ -7188,7 +7557,7 @@
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>619</v>
+        <v>655</v>
       </c>
       <c r="B9" s="3"/>
     </row>
@@ -7437,9 +7806,18 @@
     </row>
     <row r="37" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>595</v>
+        <v>605</v>
       </c>
       <c r="B37" s="2" t="e">
+        <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Acknowledgements",'Test Cases'!H3:H400,"Pass")</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="8" t="s">
+        <v>631</v>
+      </c>
+      <c r="B38" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"UX",'Test Cases'!H3:H400,"Pass")</f>
         <v>#VALUE!</v>
       </c>
@@ -7474,88 +7852,88 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>620</v>
+        <v>656</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>621</v>
+        <v>657</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>622</v>
+        <v>658</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>623</v>
+        <v>659</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>624</v>
+        <v>660</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>625</v>
+        <v>661</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>626</v>
+        <v>662</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>627</v>
+        <v>663</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>628</v>
+        <v>664</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>629</v>
+        <v>665</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>630</v>
+        <v>666</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>631</v>
+        <v>667</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>632</v>
+        <v>668</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>633</v>
+        <v>669</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>634</v>
+        <v>670</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>635</v>
+        <v>671</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>636</v>
+        <v>672</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>637</v>
+        <v>673</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>638</v>
+        <v>674</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>639</v>
+        <v>675</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>640</v>
+        <v>676</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Nucleus_Enhancer_Validation_Results_v3.0.0.xlsx
+++ b/docs/Nucleus_Enhancer_Validation_Results_v3.0.0.xlsx
@@ -23,13 +23,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1470" uniqueCount="677">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1538" uniqueCount="707">
   <si>
     <t xml:space="preserve">How to use this workbook</t>
   </si>
   <si>
     <t xml:space="preserve">Work through the 'Test Cases' sheet top to bottom. For each row set the Result cell (dropdown: Pass / Fail / Partial / N/A / Not run), and record what you saw in 'Actual / notes', plus your initials and the date.
-There are 122 cases across all feature areas.
+There are 128 cases across all feature areas.
 This is an internal self-check, not a formal/Quality validation. Use the Diagnostics sheet (or docs/Nucleus_Enhancer_Diagnostics.md) to capture detail when something misbehaves.</t>
   </si>
   <si>
@@ -1918,6 +1918,96 @@
   </si>
   <si>
     <t xml:space="preserve">At most one browser notification per day; clicking it opens the manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suggestions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Member suggests an edit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Member (read-only viewer)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Click 'Suggest edit' on a template; change the text + add a reason; Send</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confirmation shown; a NucleusTemplateChangeRequest__c (Pending) is created by you. Template itself is unchanged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin sees pending</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin; a suggestion exists</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open the manager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">'Suggestions' tab appears with a count badge; the suggestion is listed with submitter + reason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diff</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin; Suggestions tab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Click 'View diff'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Side-by-side added/removed lines: suggested vs current version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apply</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin; a suggestion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Click 'Apply…'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Request marked Approved; editor opens prefilled with the proposed content + a change reason; Saving publishes a normal new version</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Click 'Reject' and confirm</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Request marked Rejected; it leaves the pending list; template unchanged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin nudge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pending suggestions exist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trigger a background sync</t>
+  </si>
+  <si>
+    <t xml:space="preserve">At most one browser notification per day to admins; clicking opens the manager</t>
   </si>
   <si>
     <t xml:space="preserve">UX</t>
@@ -2644,7 +2734,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K153"/>
+  <dimension ref="A1:K160"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7.16"/>
@@ -7274,7 +7364,7 @@
       <c r="J149" s="11"/>
       <c r="K149" s="11"/>
     </row>
-    <row r="150" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="2" t="s">
         <v>632</v>
       </c>
@@ -7309,7 +7399,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="2" t="s">
         <v>637</v>
       </c>
@@ -7320,7 +7410,7 @@
         <v>638</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>639</v>
@@ -7355,7 +7445,7 @@
         <v>643</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>644</v>
@@ -7379,7 +7469,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="2" t="s">
         <v>647</v>
       </c>
@@ -7390,7 +7480,7 @@
         <v>648</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E153" s="2" t="s">
         <v>649</v>
@@ -7414,8 +7504,233 @@
         <v>43</v>
       </c>
     </row>
+    <row r="154" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="F154" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="G154" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="H154" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I154" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J154" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K154" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="F155" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="G155" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="H155" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I155" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J155" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K155" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="11" t="s">
+        <v>661</v>
+      </c>
+      <c r="B156" s="11"/>
+      <c r="C156" s="11"/>
+      <c r="D156" s="11"/>
+      <c r="E156" s="11"/>
+      <c r="F156" s="11"/>
+      <c r="G156" s="11"/>
+      <c r="H156" s="11"/>
+      <c r="I156" s="11"/>
+      <c r="J156" s="11"/>
+      <c r="K156" s="11"/>
+    </row>
+    <row r="157" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="F157" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="G157" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="H157" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I157" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J157" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K157" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="F158" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="G158" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="H158" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I158" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J158" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K158" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="159" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="F159" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="G159" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="H159" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I159" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J159" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K159" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="F160" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="G160" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="H160" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I160" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J160" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K160" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="30">
+  <mergeCells count="31">
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A8:K8"/>
@@ -7446,6 +7761,7 @@
     <mergeCell ref="A136:K136"/>
     <mergeCell ref="A143:K143"/>
     <mergeCell ref="A149:K149"/>
+    <mergeCell ref="A156:K156"/>
   </mergeCells>
   <conditionalFormatting sqref="H3:H400">
     <cfRule type="cellIs" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -7462,7 +7778,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" prompt="Choose Pass / Fail / Partial / N/A / Not run" promptTitle="Result" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H4:H7 H9:H13 H15:H20 H22:H27 H29:H31 H33 H35:H36 H38:H41 H43:H45 H47:H56 H58:H64 H66:H70 H72 H74:H77 H79:H80 H82:H85 H87:H91 H93:H98 H100:H111 H113:H116 H118:H119 H121:H124 H126:H127 H129 H131:H132 H134:H135 H137:H142 H144:H148 H150:H153" type="none">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" prompt="Choose Pass / Fail / Partial / N/A / Not run" promptTitle="Result" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H4:H7 H9:H13 H15:H20 H22:H27 H29:H31 H33 H35:H36 H38:H41 H43:H45 H47:H56 H58:H64 H66:H70 H72 H74:H77 H79:H80 H82:H85 H87:H91 H93:H98 H100:H111 H113:H116 H118:H119 H121:H124 H126:H127 H129 H131:H132 H134:H135 H137:H142 H144:H148 H150:H155 H157:H160" type="none">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -7482,7 +7798,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B39"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.37"/>
@@ -7491,13 +7807,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>652</v>
+        <v>682</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>653</v>
+        <v>683</v>
       </c>
       <c r="B2" s="3"/>
     </row>
@@ -7548,7 +7864,7 @@
     </row>
     <row r="8" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>654</v>
+        <v>684</v>
       </c>
       <c r="B8" s="2" t="e">
         <f aca="false">of:=COUNTA('Test Cases'!A3:A400)-COUNTIF('Test Cases'!D3:D400,"")</f>
@@ -7557,7 +7873,7 @@
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>655</v>
+        <v>685</v>
       </c>
       <c r="B9" s="3"/>
     </row>
@@ -7818,6 +8134,15 @@
         <v>631</v>
       </c>
       <c r="B38" s="2" t="e">
+        <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Suggestions",'Test Cases'!H3:H400,"Pass")</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="8" t="s">
+        <v>661</v>
+      </c>
+      <c r="B39" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"UX",'Test Cases'!H3:H400,"Pass")</f>
         <v>#VALUE!</v>
       </c>
@@ -7852,88 +8177,88 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>656</v>
+        <v>686</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>657</v>
+        <v>687</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>658</v>
+        <v>688</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>659</v>
+        <v>689</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>660</v>
+        <v>690</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>661</v>
+        <v>691</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>662</v>
+        <v>692</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>663</v>
+        <v>693</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>664</v>
+        <v>694</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>665</v>
+        <v>695</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>666</v>
+        <v>696</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>667</v>
+        <v>697</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>668</v>
+        <v>698</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>669</v>
+        <v>699</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>670</v>
+        <v>700</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>671</v>
+        <v>701</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>672</v>
+        <v>702</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>673</v>
+        <v>703</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>674</v>
+        <v>704</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>675</v>
+        <v>705</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>676</v>
+        <v>706</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Nucleus_Enhancer_Validation_Results_v3.0.0.xlsx
+++ b/docs/Nucleus_Enhancer_Validation_Results_v3.0.0.xlsx
@@ -23,13 +23,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1538" uniqueCount="707">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1527" uniqueCount="702">
   <si>
     <t xml:space="preserve">How to use this workbook</t>
   </si>
   <si>
     <t xml:space="preserve">Work through the 'Test Cases' sheet top to bottom. For each row set the Result cell (dropdown: Pass / Fail / Partial / N/A / Not run), and record what you saw in 'Actual / notes', plus your initials and the date.
-There are 128 cases across all feature areas.
+There are 127 cases across all feature areas.
 This is an internal self-check, not a formal/Quality validation. Use the Diagnostics sheet (or docs/Nucleus_Enhancer_Diagnostics.md) to capture detail when something misbehaves.</t>
   </si>
   <si>
@@ -445,21 +445,6 @@
   </si>
   <si>
     <t xml:space="preserve">Template auto-inserted (toast 'Auto-inserted …'); off = suggestion only</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CT-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sync Settings Across Devices</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Two devices same login</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toggle on</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toggle states (not templates) sync via Chrome Sync</t>
   </si>
   <si>
     <t xml:space="preserve">Columns</t>
@@ -2734,7 +2719,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K160"/>
+  <dimension ref="A1:K159"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7.16"/>
@@ -3559,68 +3544,68 @@
         <v>43</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2" t="s">
+    <row r="27" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C27" s="2" t="s">
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="11"/>
+      <c r="E27" s="11"/>
+      <c r="F27" s="11"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+    </row>
+    <row r="28" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="B28" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F27" s="2" t="s">
+      <c r="E28" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="G27" s="2" t="s">
+      <c r="F28" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="H27" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="11" t="s">
+      <c r="G28" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B28" s="11"/>
-      <c r="C28" s="11"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="11"/>
-      <c r="G28" s="11"/>
-      <c r="H28" s="11"/>
-      <c r="I28" s="11"/>
-      <c r="J28" s="11"/>
-      <c r="K28" s="11"/>
-    </row>
-    <row r="29" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H28" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K28" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="2" t="s">
         <v>146</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>147</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>148</v>
@@ -3649,13 +3634,13 @@
         <v>151</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>152</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>153</v>
@@ -3679,112 +3664,112 @@
         <v>43</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="2" t="s">
+    <row r="31" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="11" t="s">
         <v>156</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C31" s="2" t="s">
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="11"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
+      <c r="K31" s="11"/>
+    </row>
+    <row r="32" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="B32" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="F31" s="2" t="s">
+      <c r="E32" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="G31" s="2" t="s">
+      <c r="F32" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="H31" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K31" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="11" t="s">
+      <c r="G32" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="11"/>
-      <c r="H32" s="11"/>
-      <c r="I32" s="11"/>
-      <c r="J32" s="11"/>
-      <c r="K32" s="11"/>
-    </row>
-    <row r="33" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="2" t="s">
+      <c r="H32" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K32" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C33" s="2" t="s">
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="11"/>
+      <c r="G33" s="11"/>
+      <c r="H33" s="11"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
+      <c r="K33" s="11"/>
+    </row>
+    <row r="34" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="B34" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="F33" s="2" t="s">
+      <c r="E34" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="G33" s="2" t="s">
+      <c r="F34" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="H33" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J33" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K33" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="11" t="s">
+      <c r="G34" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="B34" s="11"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11"/>
-      <c r="F34" s="11"/>
-      <c r="G34" s="11"/>
-      <c r="H34" s="11"/>
-      <c r="I34" s="11"/>
-      <c r="J34" s="11"/>
-      <c r="K34" s="11"/>
-    </row>
-    <row r="35" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H34" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K34" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="2" t="s">
         <v>168</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>169</v>
@@ -3814,71 +3799,71 @@
         <v>43</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2" t="s">
+    <row r="36" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C36" s="2" t="s">
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="11"/>
+      <c r="G36" s="11"/>
+      <c r="H36" s="11"/>
+      <c r="I36" s="11"/>
+      <c r="J36" s="11"/>
+      <c r="K36" s="11"/>
+    </row>
+    <row r="37" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="D36" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E36" s="2" t="s">
+      <c r="B37" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="F36" s="2" t="s">
+      <c r="D37" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F37" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="G36" s="2" t="s">
+      <c r="G37" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="H36" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J36" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="B37" s="11"/>
-      <c r="C37" s="11"/>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11"/>
-      <c r="F37" s="11"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="11"/>
-      <c r="I37" s="11"/>
-      <c r="J37" s="11"/>
-      <c r="K37" s="11"/>
+      <c r="H37" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K37" s="2" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C38" s="2" t="s">
+      <c r="D38" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E38" s="2" t="s">
         <v>180</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>119</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>181</v>
@@ -3904,13 +3889,13 @@
         <v>183</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>184</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>185</v>
@@ -3934,18 +3919,18 @@
         <v>43</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="2" t="s">
         <v>188</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>189</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>190</v>
@@ -3969,77 +3954,77 @@
         <v>43</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="2" t="s">
+    <row r="41" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C41" s="2" t="s">
+      <c r="B41" s="11"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="11"/>
+      <c r="E41" s="11"/>
+      <c r="F41" s="11"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="11"/>
+      <c r="J41" s="11"/>
+      <c r="K41" s="11"/>
+    </row>
+    <row r="42" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="B42" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="D42" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E41" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="F41" s="2" t="s">
+      <c r="E42" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="G41" s="2" t="s">
+      <c r="F42" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G42" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="H41" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J41" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K41" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="11" t="s">
+      <c r="H42" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="B42" s="11"/>
-      <c r="C42" s="11"/>
-      <c r="D42" s="11"/>
-      <c r="E42" s="11"/>
-      <c r="F42" s="11"/>
-      <c r="G42" s="11"/>
-      <c r="H42" s="11"/>
-      <c r="I42" s="11"/>
-      <c r="J42" s="11"/>
-      <c r="K42" s="11"/>
-    </row>
-    <row r="43" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="2" t="s">
+      <c r="B43" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>199</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>200</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>57</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F43" s="2" t="s">
         <v>84</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H43" s="12" t="s">
         <v>43</v>
@@ -4056,95 +4041,95 @@
     </row>
     <row r="44" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>203</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>57</v>
       </c>
       <c r="E44" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="G44" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="F44" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G44" s="2" t="s">
+      <c r="H44" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J44" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K44" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="H44" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I44" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J44" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K44" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="2" t="s">
+      <c r="B45" s="11"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="11"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="11"/>
+      <c r="I45" s="11"/>
+      <c r="J45" s="11"/>
+      <c r="K45" s="11"/>
+    </row>
+    <row r="46" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C45" s="2" t="s">
+      <c r="B46" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="D45" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="F45" s="2" t="s">
+      <c r="D46" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E46" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="G45" s="2" t="s">
+      <c r="F46" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="H45" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I45" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J45" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K45" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="11" t="s">
+      <c r="G46" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="B46" s="11"/>
-      <c r="C46" s="11"/>
-      <c r="D46" s="11"/>
-      <c r="E46" s="11"/>
-      <c r="F46" s="11"/>
-      <c r="G46" s="11"/>
-      <c r="H46" s="11"/>
-      <c r="I46" s="11"/>
-      <c r="J46" s="11"/>
-      <c r="K46" s="11"/>
+      <c r="H46" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K46" s="2" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="2" t="s">
         <v>212</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>213</v>
@@ -4179,13 +4164,13 @@
         <v>217</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>218</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E48" s="2" t="s">
         <v>219</v>
@@ -4214,13 +4199,13 @@
         <v>222</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>223</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E49" s="2" t="s">
         <v>224</v>
@@ -4249,54 +4234,54 @@
         <v>227</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>228</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>229</v>
       </c>
       <c r="F50" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="G50" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="G50" s="2" t="s">
+      <c r="H50" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K50" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="H50" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I50" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J50" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K50" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="2" t="s">
+      <c r="B51" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C51" s="2" t="s">
+      <c r="D51" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E51" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="D51" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E51" s="2" t="s">
+      <c r="F51" s="2" t="s">
         <v>234</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>235</v>
@@ -4314,18 +4299,18 @@
         <v>43</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2" t="s">
         <v>236</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>237</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>238</v>
@@ -4354,7 +4339,7 @@
         <v>241</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>242</v>
@@ -4366,10 +4351,10 @@
         <v>243</v>
       </c>
       <c r="F53" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="G53" s="2" t="s">
         <v>244</v>
-      </c>
-      <c r="G53" s="2" t="s">
-        <v>245</v>
       </c>
       <c r="H53" s="12" t="s">
         <v>43</v>
@@ -4386,22 +4371,22 @@
     </row>
     <row r="54" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="B54" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C54" s="2" t="s">
+      <c r="D54" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E54" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="D54" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E54" s="2" t="s">
+      <c r="F54" s="2" t="s">
         <v>248</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>249</v>
@@ -4419,18 +4404,18 @@
         <v>43</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="2" t="s">
         <v>250</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>251</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>252</v>
@@ -4454,68 +4439,68 @@
         <v>43</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="2" t="s">
+    <row r="56" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="B56" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C56" s="2" t="s">
+      <c r="B56" s="11"/>
+      <c r="C56" s="11"/>
+      <c r="D56" s="11"/>
+      <c r="E56" s="11"/>
+      <c r="F56" s="11"/>
+      <c r="G56" s="11"/>
+      <c r="H56" s="11"/>
+      <c r="I56" s="11"/>
+      <c r="J56" s="11"/>
+      <c r="K56" s="11"/>
+    </row>
+    <row r="57" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="D56" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E56" s="2" t="s">
+      <c r="B57" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C57" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="F56" s="2" t="s">
+      <c r="D57" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E57" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="G56" s="2" t="s">
+      <c r="F57" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="H56" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I56" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J56" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K56" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="11" t="s">
+      <c r="G57" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="B57" s="11"/>
-      <c r="C57" s="11"/>
-      <c r="D57" s="11"/>
-      <c r="E57" s="11"/>
-      <c r="F57" s="11"/>
-      <c r="G57" s="11"/>
-      <c r="H57" s="11"/>
-      <c r="I57" s="11"/>
-      <c r="J57" s="11"/>
-      <c r="K57" s="11"/>
-    </row>
-    <row r="58" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H57" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J57" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K57" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
         <v>261</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>262</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>263</v>
@@ -4544,7 +4529,7 @@
         <v>266</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>267</v>
@@ -4579,13 +4564,13 @@
         <v>271</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>272</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>273</v>
@@ -4609,18 +4594,18 @@
         <v>43</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
         <v>276</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>277</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>278</v>
@@ -4644,12 +4629,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="62" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2" t="s">
         <v>281</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>282</v>
@@ -4684,92 +4669,92 @@
         <v>286</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>287</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="E63" s="2" t="s">
         <v>288</v>
       </c>
       <c r="F63" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="G63" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="G63" s="2" t="s">
+      <c r="H63" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K63" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="11" t="s">
         <v>290</v>
       </c>
-      <c r="H63" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I63" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J63" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K63" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="2" t="s">
+      <c r="B64" s="11"/>
+      <c r="C64" s="11"/>
+      <c r="D64" s="11"/>
+      <c r="E64" s="11"/>
+      <c r="F64" s="11"/>
+      <c r="G64" s="11"/>
+      <c r="H64" s="11"/>
+      <c r="I64" s="11"/>
+      <c r="J64" s="11"/>
+      <c r="K64" s="11"/>
+    </row>
+    <row r="65" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="B64" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="C64" s="2" t="s">
+      <c r="B65" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C65" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="D64" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E64" s="2" t="s">
+      <c r="D65" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E65" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="F64" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="G64" s="2" t="s">
+      <c r="F65" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="H64" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I64" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J64" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K64" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="11" t="s">
+      <c r="G65" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="B65" s="11"/>
-      <c r="C65" s="11"/>
-      <c r="D65" s="11"/>
-      <c r="E65" s="11"/>
-      <c r="F65" s="11"/>
-      <c r="G65" s="11"/>
-      <c r="H65" s="11"/>
-      <c r="I65" s="11"/>
-      <c r="J65" s="11"/>
-      <c r="K65" s="11"/>
+      <c r="H65" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J65" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K65" s="2" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2" t="s">
         <v>296</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>297</v>
@@ -4804,218 +4789,218 @@
         <v>301</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>302</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>303</v>
       </c>
       <c r="F67" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="G67" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="G67" s="2" t="s">
+      <c r="H67" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J67" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K67" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="H67" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I67" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J67" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K67" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="2" t="s">
+      <c r="B68" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C68" s="2" t="s">
         <v>306</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>307</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E68" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="G68" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F68" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="G68" s="2" t="s">
+      <c r="H68" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J68" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K68" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="H68" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I68" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J68" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K68" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="2" t="s">
+      <c r="B69" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C69" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="B69" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="C69" s="2" t="s">
+      <c r="D69" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E69" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="D69" s="2" t="s">
+      <c r="F69" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="H69" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J69" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="11" t="s">
+        <v>313</v>
+      </c>
+      <c r="B70" s="11"/>
+      <c r="C70" s="11"/>
+      <c r="D70" s="11"/>
+      <c r="E70" s="11"/>
+      <c r="F70" s="11"/>
+      <c r="G70" s="11"/>
+      <c r="H70" s="11"/>
+      <c r="I70" s="11"/>
+      <c r="J70" s="11"/>
+      <c r="K70" s="11"/>
+    </row>
+    <row r="71" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="H71" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K71" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="11" t="s">
+        <v>319</v>
+      </c>
+      <c r="B72" s="11"/>
+      <c r="C72" s="11"/>
+      <c r="D72" s="11"/>
+      <c r="E72" s="11"/>
+      <c r="F72" s="11"/>
+      <c r="G72" s="11"/>
+      <c r="H72" s="11"/>
+      <c r="I72" s="11"/>
+      <c r="J72" s="11"/>
+      <c r="K72" s="11"/>
+    </row>
+    <row r="73" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="D73" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E69" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="F69" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="H69" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I69" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J69" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K69" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="D70" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="H70" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I70" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J70" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K70" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="11" t="s">
-        <v>318</v>
-      </c>
-      <c r="B71" s="11"/>
-      <c r="C71" s="11"/>
-      <c r="D71" s="11"/>
-      <c r="E71" s="11"/>
-      <c r="F71" s="11"/>
-      <c r="G71" s="11"/>
-      <c r="H71" s="11"/>
-      <c r="I71" s="11"/>
-      <c r="J71" s="11"/>
-      <c r="K71" s="11"/>
-    </row>
-    <row r="72" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="D72" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="F72" s="2" t="s">
+      <c r="E73" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="G72" s="2" t="s">
+      <c r="F73" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="H72" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I72" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J72" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K72" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="11" t="s">
+      <c r="G73" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="B73" s="11"/>
-      <c r="C73" s="11"/>
-      <c r="D73" s="11"/>
-      <c r="E73" s="11"/>
-      <c r="F73" s="11"/>
-      <c r="G73" s="11"/>
-      <c r="H73" s="11"/>
-      <c r="I73" s="11"/>
-      <c r="J73" s="11"/>
-      <c r="K73" s="11"/>
+      <c r="H73" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K73" s="2" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="74" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="2" t="s">
         <v>325</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>326</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>327</v>
@@ -5039,18 +5024,18 @@
         <v>43</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="2" t="s">
         <v>330</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>331</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>332</v>
@@ -5079,13 +5064,13 @@
         <v>335</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>336</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>337</v>
@@ -5109,68 +5094,68 @@
         <v>43</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="2" t="s">
+    <row r="77" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="11" t="s">
         <v>340</v>
       </c>
-      <c r="B77" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="C77" s="2" t="s">
+      <c r="B77" s="11"/>
+      <c r="C77" s="11"/>
+      <c r="D77" s="11"/>
+      <c r="E77" s="11"/>
+      <c r="F77" s="11"/>
+      <c r="G77" s="11"/>
+      <c r="H77" s="11"/>
+      <c r="I77" s="11"/>
+      <c r="J77" s="11"/>
+      <c r="K77" s="11"/>
+    </row>
+    <row r="78" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="D77" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E77" s="2" t="s">
+      <c r="B78" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C78" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="F77" s="2" t="s">
+      <c r="D78" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E78" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="G77" s="2" t="s">
+      <c r="F78" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="H77" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I77" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J77" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K77" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="11" t="s">
+      <c r="G78" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="B78" s="11"/>
-      <c r="C78" s="11"/>
-      <c r="D78" s="11"/>
-      <c r="E78" s="11"/>
-      <c r="F78" s="11"/>
-      <c r="G78" s="11"/>
-      <c r="H78" s="11"/>
-      <c r="I78" s="11"/>
-      <c r="J78" s="11"/>
-      <c r="K78" s="11"/>
+      <c r="H78" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J78" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K78" s="2" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="79" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
         <v>346</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>347</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>348</v>
@@ -5194,68 +5179,68 @@
         <v>43</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="2" t="s">
+    <row r="80" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="11" t="s">
         <v>351</v>
       </c>
-      <c r="B80" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="C80" s="2" t="s">
+      <c r="B80" s="11"/>
+      <c r="C80" s="11"/>
+      <c r="D80" s="11"/>
+      <c r="E80" s="11"/>
+      <c r="F80" s="11"/>
+      <c r="G80" s="11"/>
+      <c r="H80" s="11"/>
+      <c r="I80" s="11"/>
+      <c r="J80" s="11"/>
+      <c r="K80" s="11"/>
+    </row>
+    <row r="81" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="D80" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E80" s="2" t="s">
+      <c r="B81" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="C81" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="F80" s="2" t="s">
+      <c r="D81" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E81" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="G80" s="2" t="s">
+      <c r="F81" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="H80" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K80" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="11" t="s">
+      <c r="G81" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="B81" s="11"/>
-      <c r="C81" s="11"/>
-      <c r="D81" s="11"/>
-      <c r="E81" s="11"/>
-      <c r="F81" s="11"/>
-      <c r="G81" s="11"/>
-      <c r="H81" s="11"/>
-      <c r="I81" s="11"/>
-      <c r="J81" s="11"/>
-      <c r="K81" s="11"/>
+      <c r="H81" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K81" s="2" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="82" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2" t="s">
         <v>357</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>358</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E82" s="2" t="s">
         <v>359</v>
@@ -5284,7 +5269,7 @@
         <v>362</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>363</v>
@@ -5319,13 +5304,13 @@
         <v>367</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>368</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E84" s="2" t="s">
         <v>369</v>
@@ -5349,62 +5334,62 @@
         <v>43</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="2" t="s">
+    <row r="85" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="11" t="s">
         <v>372</v>
       </c>
-      <c r="B85" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="C85" s="2" t="s">
+      <c r="B85" s="11"/>
+      <c r="C85" s="11"/>
+      <c r="D85" s="11"/>
+      <c r="E85" s="11"/>
+      <c r="F85" s="11"/>
+      <c r="G85" s="11"/>
+      <c r="H85" s="11"/>
+      <c r="I85" s="11"/>
+      <c r="J85" s="11"/>
+      <c r="K85" s="11"/>
+    </row>
+    <row r="86" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="D85" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E85" s="2" t="s">
+      <c r="B86" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="C86" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="F85" s="2" t="s">
+      <c r="D86" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E86" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="G85" s="2" t="s">
+      <c r="F86" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="H85" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I85" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J85" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K85" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="11" t="s">
+      <c r="G86" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="B86" s="11"/>
-      <c r="C86" s="11"/>
-      <c r="D86" s="11"/>
-      <c r="E86" s="11"/>
-      <c r="F86" s="11"/>
-      <c r="G86" s="11"/>
-      <c r="H86" s="11"/>
-      <c r="I86" s="11"/>
-      <c r="J86" s="11"/>
-      <c r="K86" s="11"/>
-    </row>
-    <row r="87" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H86" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K86" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2" t="s">
         <v>378</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>379</v>
@@ -5434,12 +5419,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="2" t="s">
         <v>383</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>384</v>
@@ -5474,7 +5459,7 @@
         <v>388</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>389</v>
@@ -5504,12 +5489,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2" t="s">
         <v>393</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>394</v>
@@ -5539,62 +5524,62 @@
         <v>43</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="2" t="s">
+    <row r="91" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="11" t="s">
         <v>398</v>
       </c>
-      <c r="B91" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="C91" s="2" t="s">
+      <c r="B91" s="11"/>
+      <c r="C91" s="11"/>
+      <c r="D91" s="11"/>
+      <c r="E91" s="11"/>
+      <c r="F91" s="11"/>
+      <c r="G91" s="11"/>
+      <c r="H91" s="11"/>
+      <c r="I91" s="11"/>
+      <c r="J91" s="11"/>
+      <c r="K91" s="11"/>
+    </row>
+    <row r="92" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="D91" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E91" s="2" t="s">
+      <c r="B92" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="C92" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="F91" s="2" t="s">
+      <c r="D92" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E92" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="G91" s="2" t="s">
+      <c r="F92" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="H91" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I91" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J91" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K91" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="92" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="11" t="s">
+      <c r="G92" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="B92" s="11"/>
-      <c r="C92" s="11"/>
-      <c r="D92" s="11"/>
-      <c r="E92" s="11"/>
-      <c r="F92" s="11"/>
-      <c r="G92" s="11"/>
-      <c r="H92" s="11"/>
-      <c r="I92" s="11"/>
-      <c r="J92" s="11"/>
-      <c r="K92" s="11"/>
+      <c r="H92" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J92" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K92" s="2" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="93" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="s">
         <v>404</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>405</v>
@@ -5629,22 +5614,22 @@
         <v>409</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>410</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E94" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="F94" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="F94" s="2" t="s">
+      <c r="G94" s="2" t="s">
         <v>412</v>
-      </c>
-      <c r="G94" s="2" t="s">
-        <v>413</v>
       </c>
       <c r="H94" s="12" t="s">
         <v>43</v>
@@ -5661,25 +5646,25 @@
     </row>
     <row r="95" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="C95" s="2" t="s">
         <v>414</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>415</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="F95" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="G95" s="2" t="s">
         <v>416</v>
-      </c>
-      <c r="G95" s="2" t="s">
-        <v>417</v>
       </c>
       <c r="H95" s="12" t="s">
         <v>43</v>
@@ -5696,19 +5681,19 @@
     </row>
     <row r="96" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="C96" s="2" t="s">
         <v>418</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>419</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="F96" s="2" t="s">
         <v>420</v>
@@ -5734,7 +5719,7 @@
         <v>422</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>423</v>
@@ -5764,62 +5749,62 @@
         <v>43</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="2" t="s">
+    <row r="98" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="11" t="s">
         <v>427</v>
       </c>
-      <c r="B98" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="C98" s="2" t="s">
+      <c r="B98" s="11"/>
+      <c r="C98" s="11"/>
+      <c r="D98" s="11"/>
+      <c r="E98" s="11"/>
+      <c r="F98" s="11"/>
+      <c r="G98" s="11"/>
+      <c r="H98" s="11"/>
+      <c r="I98" s="11"/>
+      <c r="J98" s="11"/>
+      <c r="K98" s="11"/>
+    </row>
+    <row r="99" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="D98" s="2" t="s">
+      <c r="B99" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="D99" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E98" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="F98" s="2" t="s">
+      <c r="E99" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="G98" s="2" t="s">
+      <c r="F99" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="H98" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I98" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J98" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K98" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="99" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="11" t="s">
+      <c r="G99" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="B99" s="11"/>
-      <c r="C99" s="11"/>
-      <c r="D99" s="11"/>
-      <c r="E99" s="11"/>
-      <c r="F99" s="11"/>
-      <c r="G99" s="11"/>
-      <c r="H99" s="11"/>
-      <c r="I99" s="11"/>
-      <c r="J99" s="11"/>
-      <c r="K99" s="11"/>
-    </row>
-    <row r="100" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H99" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J99" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K99" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2" t="s">
         <v>433</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>434</v>
@@ -5854,7 +5839,7 @@
         <v>438</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>439</v>
@@ -5863,188 +5848,188 @@
         <v>51</v>
       </c>
       <c r="E101" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="F101" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="F101" s="2" t="s">
+      <c r="G101" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="G101" s="2" t="s">
+      <c r="H101" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I101" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J101" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K101" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="H101" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I101" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J101" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K101" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="102" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="2" t="s">
+      <c r="B102" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="C102" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="B102" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="C102" s="2" t="s">
+      <c r="D102" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="F102" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="D102" s="2" t="s">
+      <c r="G102" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="H102" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J102" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K102" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="D103" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E102" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="F102" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="G102" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="H102" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I102" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J102" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K102" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="C103" s="2" t="s">
+      <c r="E103" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="F103" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="D103" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="F103" s="2" t="s">
+      <c r="G103" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="G103" s="2" t="s">
+      <c r="H103" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J103" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K103" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="H103" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I103" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J103" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K103" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="2" t="s">
+      <c r="B104" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="C104" s="2" t="s">
         <v>451</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>452</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="F104" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="G104" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="G104" s="2" t="s">
+      <c r="H104" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I104" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J104" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K104" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="H104" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I104" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J104" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K104" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="2" t="s">
+      <c r="B105" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="C105" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="B105" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="C105" s="2" t="s">
+      <c r="D105" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="F105" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="D105" s="2" t="s">
+      <c r="G105" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H105" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I105" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J105" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K105" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="D106" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E105" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="F105" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="G105" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="H105" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I105" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J105" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K105" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="C106" s="2" t="s">
+      <c r="E106" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="F106" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="D106" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E106" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="F106" s="2" t="s">
+      <c r="G106" s="2" t="s">
         <v>461</v>
-      </c>
-      <c r="G106" s="2" t="s">
-        <v>462</v>
       </c>
       <c r="H106" s="12" t="s">
         <v>43</v>
@@ -6061,19 +6046,19 @@
     </row>
     <row r="107" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="C107" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="B107" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="C107" s="2" t="s">
+      <c r="D107" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E107" s="2" t="s">
         <v>464</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E107" s="2" t="s">
-        <v>440</v>
       </c>
       <c r="F107" s="2" t="s">
         <v>465</v>
@@ -6099,13 +6084,13 @@
         <v>467</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>468</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E108" s="2" t="s">
         <v>469</v>
@@ -6129,56 +6114,56 @@
         <v>43</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="2" t="s">
         <v>472</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>473</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E109" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="F109" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="F109" s="2" t="s">
+      <c r="G109" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="G109" s="2" t="s">
+      <c r="H109" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I109" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J109" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K109" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="H109" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I109" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J109" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K109" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="2" t="s">
+      <c r="B110" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="C110" s="2" t="s">
         <v>477</v>
-      </c>
-      <c r="B110" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>478</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>39</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>440</v>
+        <v>478</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>479</v>
@@ -6199,62 +6184,62 @@
         <v>43</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="2" t="s">
+    <row r="111" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="11" t="s">
         <v>481</v>
       </c>
-      <c r="B111" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="C111" s="2" t="s">
+      <c r="B111" s="11"/>
+      <c r="C111" s="11"/>
+      <c r="D111" s="11"/>
+      <c r="E111" s="11"/>
+      <c r="F111" s="11"/>
+      <c r="G111" s="11"/>
+      <c r="H111" s="11"/>
+      <c r="I111" s="11"/>
+      <c r="J111" s="11"/>
+      <c r="K111" s="11"/>
+    </row>
+    <row r="112" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="2" t="s">
         <v>482</v>
       </c>
-      <c r="D111" s="2" t="s">
+      <c r="B112" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="D112" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E111" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="F111" s="2" t="s">
+      <c r="E112" s="2" t="s">
         <v>484</v>
       </c>
-      <c r="G111" s="2" t="s">
+      <c r="F112" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="H111" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I111" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J111" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K111" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="112" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="11" t="s">
+      <c r="G112" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="B112" s="11"/>
-      <c r="C112" s="11"/>
-      <c r="D112" s="11"/>
-      <c r="E112" s="11"/>
-      <c r="F112" s="11"/>
-      <c r="G112" s="11"/>
-      <c r="H112" s="11"/>
-      <c r="I112" s="11"/>
-      <c r="J112" s="11"/>
-      <c r="K112" s="11"/>
+      <c r="H112" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I112" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J112" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K112" s="2" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="113" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="2" t="s">
         <v>487</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>488</v>
@@ -6266,10 +6251,10 @@
         <v>489</v>
       </c>
       <c r="F113" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="G113" s="2" t="s">
         <v>490</v>
-      </c>
-      <c r="G113" s="2" t="s">
-        <v>491</v>
       </c>
       <c r="H113" s="12" t="s">
         <v>43</v>
@@ -6286,22 +6271,22 @@
     </row>
     <row r="114" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C114" s="2" t="s">
         <v>492</v>
-      </c>
-      <c r="B114" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>493</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>39</v>
       </c>
       <c r="E114" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="F114" s="2" t="s">
         <v>494</v>
-      </c>
-      <c r="F114" s="2" t="s">
-        <v>490</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>495</v>
@@ -6324,13 +6309,13 @@
         <v>496</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>497</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E115" s="2" t="s">
         <v>498</v>
@@ -6354,147 +6339,147 @@
         <v>43</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="2" t="s">
+    <row r="116" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="11" t="s">
         <v>501</v>
       </c>
-      <c r="B116" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="C116" s="2" t="s">
+      <c r="B116" s="11"/>
+      <c r="C116" s="11"/>
+      <c r="D116" s="11"/>
+      <c r="E116" s="11"/>
+      <c r="F116" s="11"/>
+      <c r="G116" s="11"/>
+      <c r="H116" s="11"/>
+      <c r="I116" s="11"/>
+      <c r="J116" s="11"/>
+      <c r="K116" s="11"/>
+    </row>
+    <row r="117" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="D116" s="2" t="s">
+      <c r="B117" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="D117" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E116" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="F116" s="2" t="s">
+      <c r="E117" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="F117" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="G116" s="2" t="s">
+      <c r="G117" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="H116" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I116" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J116" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K116" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="11" t="s">
+      <c r="H117" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I117" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J117" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K117" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="B117" s="11"/>
-      <c r="C117" s="11"/>
-      <c r="D117" s="11"/>
-      <c r="E117" s="11"/>
-      <c r="F117" s="11"/>
-      <c r="G117" s="11"/>
-      <c r="H117" s="11"/>
-      <c r="I117" s="11"/>
-      <c r="J117" s="11"/>
-      <c r="K117" s="11"/>
-    </row>
-    <row r="118" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="2" t="s">
+      <c r="B118" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="C118" s="2" t="s">
         <v>507</v>
       </c>
-      <c r="B118" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="C118" s="2" t="s">
+      <c r="D118" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E118" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="D118" s="2" t="s">
+      <c r="F118" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="H118" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I118" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J118" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K118" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="11" t="s">
+        <v>510</v>
+      </c>
+      <c r="B119" s="11"/>
+      <c r="C119" s="11"/>
+      <c r="D119" s="11"/>
+      <c r="E119" s="11"/>
+      <c r="F119" s="11"/>
+      <c r="G119" s="11"/>
+      <c r="H119" s="11"/>
+      <c r="I119" s="11"/>
+      <c r="J119" s="11"/>
+      <c r="K119" s="11"/>
+    </row>
+    <row r="120" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="D120" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E118" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="F118" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="G118" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="H118" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I118" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J118" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K118" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="119" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="B119" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="C119" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="D119" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E119" s="2" t="s">
+      <c r="E120" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="F119" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="G119" s="2" t="s">
+      <c r="F120" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="H119" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I119" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J119" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K119" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="11" t="s">
+      <c r="G120" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="B120" s="11"/>
-      <c r="C120" s="11"/>
-      <c r="D120" s="11"/>
-      <c r="E120" s="11"/>
-      <c r="F120" s="11"/>
-      <c r="G120" s="11"/>
-      <c r="H120" s="11"/>
-      <c r="I120" s="11"/>
-      <c r="J120" s="11"/>
-      <c r="K120" s="11"/>
-    </row>
-    <row r="121" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H120" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I120" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J120" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K120" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="2" t="s">
         <v>516</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>517</v>
@@ -6529,13 +6514,13 @@
         <v>521</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>522</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E122" s="2" t="s">
         <v>523</v>
@@ -6564,7 +6549,7 @@
         <v>526</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>527</v>
@@ -6594,62 +6579,62 @@
         <v>43</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="2" t="s">
+    <row r="124" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="11" t="s">
         <v>531</v>
       </c>
-      <c r="B124" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="C124" s="2" t="s">
+      <c r="B124" s="11"/>
+      <c r="C124" s="11"/>
+      <c r="D124" s="11"/>
+      <c r="E124" s="11"/>
+      <c r="F124" s="11"/>
+      <c r="G124" s="11"/>
+      <c r="H124" s="11"/>
+      <c r="I124" s="11"/>
+      <c r="J124" s="11"/>
+      <c r="K124" s="11"/>
+    </row>
+    <row r="125" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="D124" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E124" s="2" t="s">
+      <c r="B125" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="C125" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="F124" s="2" t="s">
+      <c r="D125" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E125" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="G124" s="2" t="s">
+      <c r="F125" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="H124" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I124" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J124" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K124" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="125" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A125" s="11" t="s">
+      <c r="G125" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="B125" s="11"/>
-      <c r="C125" s="11"/>
-      <c r="D125" s="11"/>
-      <c r="E125" s="11"/>
-      <c r="F125" s="11"/>
-      <c r="G125" s="11"/>
-      <c r="H125" s="11"/>
-      <c r="I125" s="11"/>
-      <c r="J125" s="11"/>
-      <c r="K125" s="11"/>
+      <c r="H125" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I125" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J125" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K125" s="2" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="126" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="2" t="s">
         <v>537</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>538</v>
@@ -6679,112 +6664,112 @@
         <v>43</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="2" t="s">
+    <row r="127" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="11" t="s">
         <v>542</v>
       </c>
-      <c r="B127" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="C127" s="2" t="s">
+      <c r="B127" s="11"/>
+      <c r="C127" s="11"/>
+      <c r="D127" s="11"/>
+      <c r="E127" s="11"/>
+      <c r="F127" s="11"/>
+      <c r="G127" s="11"/>
+      <c r="H127" s="11"/>
+      <c r="I127" s="11"/>
+      <c r="J127" s="11"/>
+      <c r="K127" s="11"/>
+    </row>
+    <row r="128" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="D127" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E127" s="2" t="s">
+      <c r="B128" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="C128" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="F127" s="2" t="s">
+      <c r="D128" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E128" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="G127" s="2" t="s">
+      <c r="F128" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="H127" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I127" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J127" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K127" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="128" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="11" t="s">
+      <c r="G128" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="B128" s="11"/>
-      <c r="C128" s="11"/>
-      <c r="D128" s="11"/>
-      <c r="E128" s="11"/>
-      <c r="F128" s="11"/>
-      <c r="G128" s="11"/>
-      <c r="H128" s="11"/>
-      <c r="I128" s="11"/>
-      <c r="J128" s="11"/>
-      <c r="K128" s="11"/>
-    </row>
-    <row r="129" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="2" t="s">
+      <c r="H128" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I128" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J128" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K128" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="11" t="s">
         <v>548</v>
       </c>
-      <c r="B129" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="C129" s="2" t="s">
+      <c r="B129" s="11"/>
+      <c r="C129" s="11"/>
+      <c r="D129" s="11"/>
+      <c r="E129" s="11"/>
+      <c r="F129" s="11"/>
+      <c r="G129" s="11"/>
+      <c r="H129" s="11"/>
+      <c r="I129" s="11"/>
+      <c r="J129" s="11"/>
+      <c r="K129" s="11"/>
+    </row>
+    <row r="130" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="D129" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E129" s="2" t="s">
+      <c r="B130" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="C130" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="F129" s="2" t="s">
+      <c r="D130" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E130" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="G129" s="2" t="s">
+      <c r="F130" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="H129" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I129" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J129" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K129" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="130" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A130" s="11" t="s">
+      <c r="G130" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="B130" s="11"/>
-      <c r="C130" s="11"/>
-      <c r="D130" s="11"/>
-      <c r="E130" s="11"/>
-      <c r="F130" s="11"/>
-      <c r="G130" s="11"/>
-      <c r="H130" s="11"/>
-      <c r="I130" s="11"/>
-      <c r="J130" s="11"/>
-      <c r="K130" s="11"/>
+      <c r="H130" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I130" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J130" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K130" s="2" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="131" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="2" t="s">
         <v>554</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>555</v>
@@ -6814,71 +6799,71 @@
         <v>43</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="2" t="s">
+    <row r="132" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="11" t="s">
         <v>559</v>
       </c>
-      <c r="B132" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="C132" s="2" t="s">
+      <c r="B132" s="11"/>
+      <c r="C132" s="11"/>
+      <c r="D132" s="11"/>
+      <c r="E132" s="11"/>
+      <c r="F132" s="11"/>
+      <c r="G132" s="11"/>
+      <c r="H132" s="11"/>
+      <c r="I132" s="11"/>
+      <c r="J132" s="11"/>
+      <c r="K132" s="11"/>
+    </row>
+    <row r="133" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="D132" s="2" t="s">
+      <c r="B133" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="H133" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I133" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J133" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K133" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="D134" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E132" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="F132" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="G132" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="H132" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I132" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J132" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K132" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="133" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="11" t="s">
-        <v>564</v>
-      </c>
-      <c r="B133" s="11"/>
-      <c r="C133" s="11"/>
-      <c r="D133" s="11"/>
-      <c r="E133" s="11"/>
-      <c r="F133" s="11"/>
-      <c r="G133" s="11"/>
-      <c r="H133" s="11"/>
-      <c r="I133" s="11"/>
-      <c r="J133" s="11"/>
-      <c r="K133" s="11"/>
-    </row>
-    <row r="134" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="C134" s="2" t="s">
+      <c r="E134" s="2" t="s">
         <v>566</v>
-      </c>
-      <c r="D134" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E134" s="2" t="s">
-        <v>119</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>567</v>
@@ -6899,62 +6884,62 @@
         <v>43</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="2" t="s">
+    <row r="135" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="11" t="s">
         <v>569</v>
       </c>
-      <c r="B135" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="C135" s="2" t="s">
+      <c r="B135" s="11"/>
+      <c r="C135" s="11"/>
+      <c r="D135" s="11"/>
+      <c r="E135" s="11"/>
+      <c r="F135" s="11"/>
+      <c r="G135" s="11"/>
+      <c r="H135" s="11"/>
+      <c r="I135" s="11"/>
+      <c r="J135" s="11"/>
+      <c r="K135" s="11"/>
+    </row>
+    <row r="136" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="D135" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E135" s="2" t="s">
+      <c r="B136" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="C136" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="F135" s="2" t="s">
+      <c r="D136" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E136" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="G135" s="2" t="s">
+      <c r="F136" s="2" t="s">
         <v>573</v>
       </c>
-      <c r="H135" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I135" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J135" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K135" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="136" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="11" t="s">
+      <c r="G136" s="2" t="s">
         <v>574</v>
       </c>
-      <c r="B136" s="11"/>
-      <c r="C136" s="11"/>
-      <c r="D136" s="11"/>
-      <c r="E136" s="11"/>
-      <c r="F136" s="11"/>
-      <c r="G136" s="11"/>
-      <c r="H136" s="11"/>
-      <c r="I136" s="11"/>
-      <c r="J136" s="11"/>
-      <c r="K136" s="11"/>
-    </row>
-    <row r="137" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H136" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I136" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J136" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K136" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="2" t="s">
         <v>575</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>576</v>
@@ -6989,13 +6974,13 @@
         <v>580</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>581</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>582</v>
@@ -7019,12 +7004,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="139" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="2" t="s">
         <v>585</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>586</v>
@@ -7054,12 +7039,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="140" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="2" t="s">
         <v>590</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>591</v>
@@ -7089,18 +7074,18 @@
         <v>43</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="141" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="2" t="s">
         <v>595</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>596</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E141" s="2" t="s">
         <v>597</v>
@@ -7124,62 +7109,62 @@
         <v>43</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="2" t="s">
+    <row r="142" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="11" t="s">
         <v>600</v>
       </c>
-      <c r="B142" s="2" t="s">
-        <v>574</v>
-      </c>
-      <c r="C142" s="2" t="s">
+      <c r="B142" s="11"/>
+      <c r="C142" s="11"/>
+      <c r="D142" s="11"/>
+      <c r="E142" s="11"/>
+      <c r="F142" s="11"/>
+      <c r="G142" s="11"/>
+      <c r="H142" s="11"/>
+      <c r="I142" s="11"/>
+      <c r="J142" s="11"/>
+      <c r="K142" s="11"/>
+    </row>
+    <row r="143" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="D142" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E142" s="2" t="s">
+      <c r="B143" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="C143" s="2" t="s">
         <v>602</v>
       </c>
-      <c r="F142" s="2" t="s">
+      <c r="D143" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E143" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="G142" s="2" t="s">
+      <c r="F143" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="H142" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I142" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J142" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K142" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="143" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="11" t="s">
+      <c r="G143" s="2" t="s">
         <v>605</v>
       </c>
-      <c r="B143" s="11"/>
-      <c r="C143" s="11"/>
-      <c r="D143" s="11"/>
-      <c r="E143" s="11"/>
-      <c r="F143" s="11"/>
-      <c r="G143" s="11"/>
-      <c r="H143" s="11"/>
-      <c r="I143" s="11"/>
-      <c r="J143" s="11"/>
-      <c r="K143" s="11"/>
+      <c r="H143" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I143" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J143" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K143" s="2" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="144" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="2" t="s">
         <v>606</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>607</v>
@@ -7214,7 +7199,7 @@
         <v>611</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>612</v>
@@ -7244,12 +7229,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="146" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="2" t="s">
         <v>616</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>617</v>
@@ -7279,18 +7264,18 @@
         <v>43</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="147" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="2" t="s">
         <v>621</v>
       </c>
       <c r="B147" s="2" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="C147" s="2" t="s">
         <v>622</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E147" s="2" t="s">
         <v>623</v>
@@ -7314,62 +7299,62 @@
         <v>43</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="2" t="s">
+    <row r="148" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="11" t="s">
         <v>626</v>
       </c>
-      <c r="B148" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="C148" s="2" t="s">
+      <c r="B148" s="11"/>
+      <c r="C148" s="11"/>
+      <c r="D148" s="11"/>
+      <c r="E148" s="11"/>
+      <c r="F148" s="11"/>
+      <c r="G148" s="11"/>
+      <c r="H148" s="11"/>
+      <c r="I148" s="11"/>
+      <c r="J148" s="11"/>
+      <c r="K148" s="11"/>
+    </row>
+    <row r="149" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="2" t="s">
         <v>627</v>
       </c>
-      <c r="D148" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E148" s="2" t="s">
+      <c r="B149" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="C149" s="2" t="s">
         <v>628</v>
       </c>
-      <c r="F148" s="2" t="s">
+      <c r="D149" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E149" s="2" t="s">
         <v>629</v>
       </c>
-      <c r="G148" s="2" t="s">
+      <c r="F149" s="2" t="s">
         <v>630</v>
       </c>
-      <c r="H148" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I148" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J148" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K148" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="149" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="11" t="s">
+      <c r="G149" s="2" t="s">
         <v>631</v>
       </c>
-      <c r="B149" s="11"/>
-      <c r="C149" s="11"/>
-      <c r="D149" s="11"/>
-      <c r="E149" s="11"/>
-      <c r="F149" s="11"/>
-      <c r="G149" s="11"/>
-      <c r="H149" s="11"/>
-      <c r="I149" s="11"/>
-      <c r="J149" s="11"/>
-      <c r="K149" s="11"/>
-    </row>
-    <row r="150" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H149" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I149" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J149" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K149" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="150" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="2" t="s">
         <v>632</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>633</v>
@@ -7399,18 +7384,18 @@
         <v>43</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="2" t="s">
         <v>637</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>638</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>639</v>
@@ -7434,18 +7419,18 @@
         <v>43</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="152" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="2" t="s">
         <v>642</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>643</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E152" s="2" t="s">
         <v>644</v>
@@ -7469,27 +7454,27 @@
         <v>43</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="153" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="2" t="s">
         <v>647</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>648</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E153" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="F153" s="2" t="s">
         <v>649</v>
       </c>
-      <c r="F153" s="2" t="s">
+      <c r="G153" s="2" t="s">
         <v>650</v>
-      </c>
-      <c r="G153" s="2" t="s">
-        <v>651</v>
       </c>
       <c r="H153" s="12" t="s">
         <v>43</v>
@@ -7506,19 +7491,19 @@
     </row>
     <row r="154" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="C154" s="2" t="s">
         <v>652</v>
-      </c>
-      <c r="B154" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>653</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>57</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="F154" s="2" t="s">
         <v>654</v>
@@ -7539,68 +7524,68 @@
         <v>43</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="2" t="s">
+    <row r="155" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="11" t="s">
         <v>656</v>
       </c>
-      <c r="B155" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="C155" s="2" t="s">
+      <c r="B155" s="11"/>
+      <c r="C155" s="11"/>
+      <c r="D155" s="11"/>
+      <c r="E155" s="11"/>
+      <c r="F155" s="11"/>
+      <c r="G155" s="11"/>
+      <c r="H155" s="11"/>
+      <c r="I155" s="11"/>
+      <c r="J155" s="11"/>
+      <c r="K155" s="11"/>
+    </row>
+    <row r="156" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="2" t="s">
         <v>657</v>
       </c>
-      <c r="D155" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E155" s="2" t="s">
+      <c r="B156" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="C156" s="2" t="s">
         <v>658</v>
       </c>
-      <c r="F155" s="2" t="s">
+      <c r="D156" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E156" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="G155" s="2" t="s">
+      <c r="F156" s="2" t="s">
         <v>660</v>
       </c>
-      <c r="H155" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I155" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J155" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K155" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="156" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="11" t="s">
+      <c r="G156" s="2" t="s">
         <v>661</v>
       </c>
-      <c r="B156" s="11"/>
-      <c r="C156" s="11"/>
-      <c r="D156" s="11"/>
-      <c r="E156" s="11"/>
-      <c r="F156" s="11"/>
-      <c r="G156" s="11"/>
-      <c r="H156" s="11"/>
-      <c r="I156" s="11"/>
-      <c r="J156" s="11"/>
-      <c r="K156" s="11"/>
-    </row>
-    <row r="157" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H156" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I156" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J156" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K156" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="157" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="2" t="s">
         <v>662</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>663</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E157" s="2" t="s">
         <v>664</v>
@@ -7624,18 +7609,18 @@
         <v>43</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="158" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="2" t="s">
         <v>667</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>668</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>669</v>
@@ -7664,13 +7649,13 @@
         <v>672</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>673</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>674</v>
@@ -7691,41 +7676,6 @@
         <v>43</v>
       </c>
       <c r="K159" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="160" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="2" t="s">
-        <v>677</v>
-      </c>
-      <c r="B160" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="C160" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="D160" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E160" s="2" t="s">
-        <v>679</v>
-      </c>
-      <c r="F160" s="2" t="s">
-        <v>680</v>
-      </c>
-      <c r="G160" s="2" t="s">
-        <v>681</v>
-      </c>
-      <c r="H160" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I160" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J160" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K160" s="2" t="s">
         <v>43</v>
       </c>
     </row>
@@ -7736,32 +7686,32 @@
     <mergeCell ref="A8:K8"/>
     <mergeCell ref="A14:K14"/>
     <mergeCell ref="A21:K21"/>
-    <mergeCell ref="A28:K28"/>
-    <mergeCell ref="A32:K32"/>
-    <mergeCell ref="A34:K34"/>
-    <mergeCell ref="A37:K37"/>
-    <mergeCell ref="A42:K42"/>
-    <mergeCell ref="A46:K46"/>
-    <mergeCell ref="A57:K57"/>
-    <mergeCell ref="A65:K65"/>
-    <mergeCell ref="A71:K71"/>
-    <mergeCell ref="A73:K73"/>
-    <mergeCell ref="A78:K78"/>
-    <mergeCell ref="A81:K81"/>
-    <mergeCell ref="A86:K86"/>
-    <mergeCell ref="A92:K92"/>
-    <mergeCell ref="A99:K99"/>
-    <mergeCell ref="A112:K112"/>
-    <mergeCell ref="A117:K117"/>
-    <mergeCell ref="A120:K120"/>
-    <mergeCell ref="A125:K125"/>
-    <mergeCell ref="A128:K128"/>
-    <mergeCell ref="A130:K130"/>
-    <mergeCell ref="A133:K133"/>
-    <mergeCell ref="A136:K136"/>
-    <mergeCell ref="A143:K143"/>
-    <mergeCell ref="A149:K149"/>
-    <mergeCell ref="A156:K156"/>
+    <mergeCell ref="A27:K27"/>
+    <mergeCell ref="A31:K31"/>
+    <mergeCell ref="A33:K33"/>
+    <mergeCell ref="A36:K36"/>
+    <mergeCell ref="A41:K41"/>
+    <mergeCell ref="A45:K45"/>
+    <mergeCell ref="A56:K56"/>
+    <mergeCell ref="A64:K64"/>
+    <mergeCell ref="A70:K70"/>
+    <mergeCell ref="A72:K72"/>
+    <mergeCell ref="A77:K77"/>
+    <mergeCell ref="A80:K80"/>
+    <mergeCell ref="A85:K85"/>
+    <mergeCell ref="A91:K91"/>
+    <mergeCell ref="A98:K98"/>
+    <mergeCell ref="A111:K111"/>
+    <mergeCell ref="A116:K116"/>
+    <mergeCell ref="A119:K119"/>
+    <mergeCell ref="A124:K124"/>
+    <mergeCell ref="A127:K127"/>
+    <mergeCell ref="A129:K129"/>
+    <mergeCell ref="A132:K132"/>
+    <mergeCell ref="A135:K135"/>
+    <mergeCell ref="A142:K142"/>
+    <mergeCell ref="A148:K148"/>
+    <mergeCell ref="A155:K155"/>
   </mergeCells>
   <conditionalFormatting sqref="H3:H400">
     <cfRule type="cellIs" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -7778,7 +7728,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" prompt="Choose Pass / Fail / Partial / N/A / Not run" promptTitle="Result" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H4:H7 H9:H13 H15:H20 H22:H27 H29:H31 H33 H35:H36 H38:H41 H43:H45 H47:H56 H58:H64 H66:H70 H72 H74:H77 H79:H80 H82:H85 H87:H91 H93:H98 H100:H111 H113:H116 H118:H119 H121:H124 H126:H127 H129 H131:H132 H134:H135 H137:H142 H144:H148 H150:H155 H157:H160" type="none">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" prompt="Choose Pass / Fail / Partial / N/A / Not run" promptTitle="Result" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H4:H7 H9:H13 H15:H20 H22:H26 H28:H30 H32 H34:H35 H37:H40 H42:H44 H46:H55 H57:H63 H65:H69 H71 H73:H76 H78:H79 H81:H84 H86:H90 H92:H97 H99:H110 H112:H115 H117:H118 H120:H123 H125:H126 H128 H130:H131 H133:H134 H136:H141 H143:H147 H149:H154 H156:H159" type="none">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -7807,13 +7757,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>682</v>
+        <v>677</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>683</v>
+        <v>678</v>
       </c>
       <c r="B2" s="3"/>
     </row>
@@ -7864,7 +7814,7 @@
     </row>
     <row r="8" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="B8" s="2" t="e">
         <f aca="false">of:=COUNTA('Test Cases'!A3:A400)-COUNTIF('Test Cases'!D3:D400,"")</f>
@@ -7873,7 +7823,7 @@
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>685</v>
+        <v>680</v>
       </c>
       <c r="B9" s="3"/>
     </row>
@@ -7915,7 +7865,7 @@
     </row>
     <row r="14" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="B14" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Columns",'Test Cases'!H3:H400,"Pass")</f>
@@ -7924,7 +7874,7 @@
     </row>
     <row r="15" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="B15" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Process mappings",'Test Cases'!H3:H400,"Pass")</f>
@@ -7933,7 +7883,7 @@
     </row>
     <row r="16" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="B16" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Template upload",'Test Cases'!H3:H400,"Pass")</f>
@@ -7942,7 +7892,7 @@
     </row>
     <row r="17" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="B17" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Theme",'Test Cases'!H3:H400,"Pass")</f>
@@ -7951,7 +7901,7 @@
     </row>
     <row r="18" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B18" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Banners",'Test Cases'!H3:H400,"Pass")</f>
@@ -7960,7 +7910,7 @@
     </row>
     <row r="19" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="B19" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Right-click",'Test Cases'!H3:H400,"Pass")</f>
@@ -7969,7 +7919,7 @@
     </row>
     <row r="20" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="B20" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Templates",'Test Cases'!H3:H400,"Pass")</f>
@@ -7978,7 +7928,7 @@
     </row>
     <row r="21" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="B21" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Rich-text insert",'Test Cases'!H3:H400,"Pass")</f>
@@ -7987,7 +7937,7 @@
     </row>
     <row r="22" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>318</v>
+        <v>313</v>
       </c>
       <c r="B22" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Notes format",'Test Cases'!H3:H400,"Pass")</f>
@@ -7996,7 +7946,7 @@
     </row>
     <row r="23" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
       <c r="B23" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Navigation",'Test Cases'!H3:H400,"Pass")</f>
@@ -8005,7 +7955,7 @@
     </row>
     <row r="24" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>345</v>
+        <v>340</v>
       </c>
       <c r="B24" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Photo download",'Test Cases'!H3:H400,"Pass")</f>
@@ -8014,7 +7964,7 @@
     </row>
     <row r="25" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>356</v>
+        <v>351</v>
       </c>
       <c r="B25" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Case report",'Test Cases'!H3:H400,"Pass")</f>
@@ -8023,7 +7973,7 @@
     </row>
     <row r="26" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="8" t="s">
-        <v>377</v>
+        <v>372</v>
       </c>
       <c r="B26" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Manager",'Test Cases'!H3:H400,"Pass")</f>
@@ -8032,7 +7982,7 @@
     </row>
     <row r="27" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="8" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="B27" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Manager edit",'Test Cases'!H3:H400,"Pass")</f>
@@ -8041,7 +7991,7 @@
     </row>
     <row r="28" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="B28" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"RTE editor",'Test Cases'!H3:H400,"Pass")</f>
@@ -8050,7 +8000,7 @@
     </row>
     <row r="29" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="B29" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Teams",'Test Cases'!H3:H400,"Pass")</f>
@@ -8059,7 +8009,7 @@
     </row>
     <row r="30" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="B30" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"History",'Test Cases'!H3:H400,"Pass")</f>
@@ -8068,7 +8018,7 @@
     </row>
     <row r="31" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="B31" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Usage",'Test Cases'!H3:H400,"Pass")</f>
@@ -8077,7 +8027,7 @@
     </row>
     <row r="32" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="B32" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Read-only",'Test Cases'!H3:H400,"Pass")</f>
@@ -8086,7 +8036,7 @@
     </row>
     <row r="33" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="B33" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Dark mode",'Test Cases'!H3:H400,"Pass")</f>
@@ -8095,7 +8045,7 @@
     </row>
     <row r="34" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="B34" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Background",'Test Cases'!H3:H400,"Pass")</f>
@@ -8104,7 +8054,7 @@
     </row>
     <row r="35" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
-        <v>564</v>
+        <v>559</v>
       </c>
       <c r="B35" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Diagnostics",'Test Cases'!H3:H400,"Pass")</f>
@@ -8113,7 +8063,7 @@
     </row>
     <row r="36" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="B36" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Security",'Test Cases'!H3:H400,"Pass")</f>
@@ -8122,7 +8072,7 @@
     </row>
     <row r="37" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>605</v>
+        <v>600</v>
       </c>
       <c r="B37" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Acknowledgements",'Test Cases'!H3:H400,"Pass")</f>
@@ -8131,7 +8081,7 @@
     </row>
     <row r="38" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="B38" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Suggestions",'Test Cases'!H3:H400,"Pass")</f>
@@ -8140,7 +8090,7 @@
     </row>
     <row r="39" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="s">
-        <v>661</v>
+        <v>656</v>
       </c>
       <c r="B39" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"UX",'Test Cases'!H3:H400,"Pass")</f>
@@ -8177,88 +8127,88 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>686</v>
+        <v>681</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>687</v>
+        <v>682</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>688</v>
+        <v>683</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>690</v>
+        <v>685</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>691</v>
+        <v>686</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>692</v>
+        <v>687</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>693</v>
+        <v>688</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>694</v>
+        <v>689</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>695</v>
+        <v>690</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>696</v>
+        <v>691</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>697</v>
+        <v>692</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>700</v>
+        <v>695</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>701</v>
+        <v>696</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>702</v>
+        <v>697</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>703</v>
+        <v>698</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>704</v>
+        <v>699</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>706</v>
+        <v>701</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Nucleus_Enhancer_Validation_Results_v3.0.0.xlsx
+++ b/docs/Nucleus_Enhancer_Validation_Results_v3.0.0.xlsx
@@ -23,13 +23,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1527" uniqueCount="702">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1562" uniqueCount="718">
   <si>
     <t xml:space="preserve">How to use this workbook</t>
   </si>
   <si>
     <t xml:space="preserve">Work through the 'Test Cases' sheet top to bottom. For each row set the Result cell (dropdown: Pass / Fail / Partial / N/A / Not run), and record what you saw in 'Actual / notes', plus your initials and the date.
-There are 127 cases across all feature areas.
+There are 130 cases across all feature areas.
 This is an internal self-check, not a formal/Quality validation. Use the Diagnostics sheet (or docs/Nucleus_Enhancer_Diagnostics.md) to capture detail when something misbehaves.</t>
   </si>
   <si>
@@ -1045,6 +1045,54 @@
   </si>
   <si>
     <t xml:space="preserve">Instant, no dim (served from cache); count still correct. Add a process then revisit → it reloads</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Case alias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shown where SF doesn't</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A forensic case that has a Project/alias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open a Task related to it; open the Recently Viewed cases list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The project alias appears next to the case (e.g. 'CY-26-0542 · Tioga'); cases with no alias show nothing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not duplicated</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A list that already has a Project column (Examiner Team / All)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No extra alias added — the existing Project column is left alone</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live toggle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aliases showing on a page</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turn 'Show Case Project / Alias' off, then on — WITHOUT refreshing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Off = aliases vanish immediately; On = they reappear immediately. No page refresh needed. (If the org has no Project field, the feature is silently inert)</t>
   </si>
   <si>
     <t xml:space="preserve">Photo download</t>
@@ -2719,7 +2767,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K159"/>
+  <dimension ref="A1:K163"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7.16"/>
@@ -5109,7 +5157,7 @@
       <c r="J77" s="11"/>
       <c r="K77" s="11"/>
     </row>
-    <row r="78" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="2" t="s">
         <v>341</v>
       </c>
@@ -5144,7 +5192,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
         <v>346</v>
       </c>
@@ -5179,62 +5227,62 @@
         <v>43</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="11" t="s">
+    <row r="80" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="B80" s="11"/>
-      <c r="C80" s="11"/>
-      <c r="D80" s="11"/>
-      <c r="E80" s="11"/>
-      <c r="F80" s="11"/>
-      <c r="G80" s="11"/>
-      <c r="H80" s="11"/>
-      <c r="I80" s="11"/>
-      <c r="J80" s="11"/>
-      <c r="K80" s="11"/>
-    </row>
-    <row r="81" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="2" t="s">
+      <c r="B80" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="C80" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="B81" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="C81" s="2" t="s">
+      <c r="D80" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E80" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="D81" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E81" s="2" t="s">
+      <c r="F80" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="F81" s="2" t="s">
+      <c r="G80" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="G81" s="2" t="s">
+      <c r="H80" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="11" t="s">
         <v>356</v>
       </c>
-      <c r="H81" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I81" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J81" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K81" s="2" t="s">
-        <v>43</v>
-      </c>
+      <c r="B81" s="11"/>
+      <c r="C81" s="11"/>
+      <c r="D81" s="11"/>
+      <c r="E81" s="11"/>
+      <c r="F81" s="11"/>
+      <c r="G81" s="11"/>
+      <c r="H81" s="11"/>
+      <c r="I81" s="11"/>
+      <c r="J81" s="11"/>
+      <c r="K81" s="11"/>
     </row>
     <row r="82" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2" t="s">
         <v>357</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>358</v>
@@ -5269,13 +5317,13 @@
         <v>362</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>363</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E83" s="2" t="s">
         <v>364</v>
@@ -5299,62 +5347,62 @@
         <v>43</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="2" t="s">
+    <row r="84" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="11" t="s">
         <v>367</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="C84" s="2" t="s">
+      <c r="B84" s="11"/>
+      <c r="C84" s="11"/>
+      <c r="D84" s="11"/>
+      <c r="E84" s="11"/>
+      <c r="F84" s="11"/>
+      <c r="G84" s="11"/>
+      <c r="H84" s="11"/>
+      <c r="I84" s="11"/>
+      <c r="J84" s="11"/>
+      <c r="K84" s="11"/>
+    </row>
+    <row r="85" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="D84" s="2" t="s">
+      <c r="B85" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D85" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E84" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="F84" s="2" t="s">
+      <c r="E85" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="G84" s="2" t="s">
+      <c r="F85" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="H84" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I84" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J84" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K84" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="11" t="s">
+      <c r="G85" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="B85" s="11"/>
-      <c r="C85" s="11"/>
-      <c r="D85" s="11"/>
-      <c r="E85" s="11"/>
-      <c r="F85" s="11"/>
-      <c r="G85" s="11"/>
-      <c r="H85" s="11"/>
-      <c r="I85" s="11"/>
-      <c r="J85" s="11"/>
-      <c r="K85" s="11"/>
-    </row>
-    <row r="86" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H85" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I85" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J85" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K85" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2" t="s">
         <v>373</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>374</v>
@@ -5384,12 +5432,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2" t="s">
         <v>378</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>379</v>
@@ -5424,13 +5472,13 @@
         <v>383</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>372</v>
+        <v>367</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>384</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E88" s="2" t="s">
         <v>385</v>
@@ -5454,103 +5502,103 @@
         <v>43</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="2" t="s">
+    <row r="89" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="11" t="s">
         <v>388</v>
       </c>
-      <c r="B89" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E89" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="F89" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="G89" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="H89" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I89" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J89" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K89" s="2" t="s">
-        <v>43</v>
-      </c>
+      <c r="B89" s="11"/>
+      <c r="C89" s="11"/>
+      <c r="D89" s="11"/>
+      <c r="E89" s="11"/>
+      <c r="F89" s="11"/>
+      <c r="G89" s="11"/>
+      <c r="H89" s="11"/>
+      <c r="I89" s="11"/>
+      <c r="J89" s="11"/>
+      <c r="K89" s="11"/>
     </row>
     <row r="90" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="2" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>372</v>
+        <v>388</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E90" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="H90" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J90" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K90" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="C91" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="F90" s="2" t="s">
+      <c r="D91" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E91" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="G90" s="2" t="s">
+      <c r="F91" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="H90" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I90" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J90" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K90" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="11" t="s">
+      <c r="G91" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="B91" s="11"/>
-      <c r="C91" s="11"/>
-      <c r="D91" s="11"/>
-      <c r="E91" s="11"/>
-      <c r="F91" s="11"/>
-      <c r="G91" s="11"/>
-      <c r="H91" s="11"/>
-      <c r="I91" s="11"/>
-      <c r="J91" s="11"/>
-      <c r="K91" s="11"/>
+      <c r="H91" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J91" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K91" s="2" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="92" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2" t="s">
         <v>399</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>400</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E92" s="2" t="s">
         <v>401</v>
@@ -5579,13 +5627,13 @@
         <v>404</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="C93" s="2" t="s">
         <v>405</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E93" s="2" t="s">
         <v>406</v>
@@ -5609,12 +5657,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2" t="s">
         <v>409</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>410</v>
@@ -5623,13 +5671,13 @@
         <v>51</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H94" s="12" t="s">
         <v>43</v>
@@ -5644,62 +5692,42 @@
         <v>43</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="C95" s="2" t="s">
+    <row r="95" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="11" t="s">
         <v>414</v>
       </c>
-      <c r="D95" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E95" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="F95" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="G95" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="H95" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I95" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J95" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K95" s="2" t="s">
-        <v>43</v>
-      </c>
+      <c r="B95" s="11"/>
+      <c r="C95" s="11"/>
+      <c r="D95" s="11"/>
+      <c r="E95" s="11"/>
+      <c r="F95" s="11"/>
+      <c r="G95" s="11"/>
+      <c r="H95" s="11"/>
+      <c r="I95" s="11"/>
+      <c r="J95" s="11"/>
+      <c r="K95" s="11"/>
     </row>
     <row r="96" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E96" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="B96" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="C96" s="2" t="s">
+      <c r="F96" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="D96" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E96" s="2" t="s">
+      <c r="G96" s="2" t="s">
         <v>419</v>
-      </c>
-      <c r="F96" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="G96" s="2" t="s">
-        <v>421</v>
       </c>
       <c r="H96" s="12" t="s">
         <v>43</v>
@@ -5716,69 +5744,89 @@
     </row>
     <row r="97" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E97" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="B97" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="C97" s="2" t="s">
+      <c r="F97" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="D97" s="2" t="s">
+      <c r="G97" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="H97" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J97" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K97" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="D98" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E97" s="2" t="s">
-        <v>424</v>
-      </c>
-      <c r="F97" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="G97" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="H97" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I97" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J97" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K97" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="11" t="s">
+      <c r="E98" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="F98" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="B98" s="11"/>
-      <c r="C98" s="11"/>
-      <c r="D98" s="11"/>
-      <c r="E98" s="11"/>
-      <c r="F98" s="11"/>
-      <c r="G98" s="11"/>
-      <c r="H98" s="11"/>
-      <c r="I98" s="11"/>
-      <c r="J98" s="11"/>
-      <c r="K98" s="11"/>
-    </row>
-    <row r="99" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G98" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="H98" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I98" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J98" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K98" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>431</v>
@@ -5804,7 +5852,7 @@
         <v>433</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>434</v>
@@ -5839,7 +5887,7 @@
         <v>438</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>439</v>
@@ -5848,13 +5896,13 @@
         <v>51</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H101" s="12" t="s">
         <v>43</v>
@@ -5869,91 +5917,71 @@
         <v>43</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="2" t="s">
-        <v>442</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="C102" s="2" t="s">
+    <row r="102" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="11" t="s">
         <v>443</v>
       </c>
-      <c r="D102" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E102" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="F102" s="2" t="s">
+      <c r="B102" s="11"/>
+      <c r="C102" s="11"/>
+      <c r="D102" s="11"/>
+      <c r="E102" s="11"/>
+      <c r="F102" s="11"/>
+      <c r="G102" s="11"/>
+      <c r="H102" s="11"/>
+      <c r="I102" s="11"/>
+      <c r="J102" s="11"/>
+      <c r="K102" s="11"/>
+    </row>
+    <row r="103" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="G102" s="2" t="s">
+      <c r="B103" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C103" s="2" t="s">
         <v>445</v>
-      </c>
-      <c r="H102" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I102" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J102" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K102" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>447</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="F103" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="G103" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="G103" s="2" t="s">
+      <c r="H103" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J103" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K103" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="H103" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I103" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J103" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K103" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A104" s="2" t="s">
+      <c r="B104" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C104" s="2" t="s">
         <v>450</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>451</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>435</v>
+        <v>451</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>452</v>
@@ -5974,21 +6002,21 @@
         <v>43</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="105" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2" t="s">
         <v>454</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>427</v>
+        <v>443</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>455</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>435</v>
+        <v>451</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>456</v>
@@ -6009,21 +6037,21 @@
         <v>43</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2" t="s">
         <v>458</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>427</v>
+        <v>443</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>459</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>435</v>
+        <v>451</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>460</v>
@@ -6049,92 +6077,92 @@
         <v>462</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>427</v>
+        <v>443</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>463</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E107" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="F107" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="F107" s="2" t="s">
+      <c r="G107" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="G107" s="2" t="s">
+      <c r="H107" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I107" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J107" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K107" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="H107" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I107" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J107" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K107" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="2" t="s">
+      <c r="B108" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C108" s="2" t="s">
         <v>467</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>468</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E108" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="G108" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="F108" s="2" t="s">
+      <c r="H108" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I108" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J108" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K108" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="G108" s="2" t="s">
+      <c r="B109" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C109" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="H108" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I108" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J108" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K108" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="109" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="2" t="s">
+      <c r="D109" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="F109" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="B109" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="C109" s="2" t="s">
+      <c r="G109" s="2" t="s">
         <v>473</v>
-      </c>
-      <c r="D109" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E109" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="F109" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="G109" s="2" t="s">
-        <v>475</v>
       </c>
       <c r="H109" s="12" t="s">
         <v>43</v>
@@ -6151,75 +6179,95 @@
     </row>
     <row r="110" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="F110" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="B110" s="2" t="s">
-        <v>427</v>
-      </c>
-      <c r="C110" s="2" t="s">
+      <c r="G110" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="D110" s="2" t="s">
+      <c r="H110" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I110" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J110" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K110" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="D111" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E110" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="F110" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="G110" s="2" t="s">
+      <c r="E111" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="H110" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I110" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J110" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K110" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="111" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="11" t="s">
+      <c r="F111" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="B111" s="11"/>
-      <c r="C111" s="11"/>
-      <c r="D111" s="11"/>
-      <c r="E111" s="11"/>
-      <c r="F111" s="11"/>
-      <c r="G111" s="11"/>
-      <c r="H111" s="11"/>
-      <c r="I111" s="11"/>
-      <c r="J111" s="11"/>
-      <c r="K111" s="11"/>
+      <c r="G111" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="H111" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I111" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J111" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K111" s="2" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="112" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="2" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>481</v>
+        <v>443</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H112" s="12" t="s">
         <v>43</v>
@@ -6234,27 +6282,27 @@
         <v>43</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>481</v>
+        <v>443</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>39</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>489</v>
+        <v>451</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H113" s="12" t="s">
         <v>43</v>
@@ -6271,25 +6319,25 @@
     </row>
     <row r="114" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>481</v>
+        <v>443</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>39</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H114" s="12" t="s">
         <v>43</v>
@@ -6304,77 +6352,77 @@
         <v>43</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="C115" s="2" t="s">
+    <row r="115" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="11" t="s">
         <v>497</v>
       </c>
-      <c r="D115" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E115" s="2" t="s">
+      <c r="B115" s="11"/>
+      <c r="C115" s="11"/>
+      <c r="D115" s="11"/>
+      <c r="E115" s="11"/>
+      <c r="F115" s="11"/>
+      <c r="G115" s="11"/>
+      <c r="H115" s="11"/>
+      <c r="I115" s="11"/>
+      <c r="J115" s="11"/>
+      <c r="K115" s="11"/>
+    </row>
+    <row r="116" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="F115" s="2" t="s">
+      <c r="B116" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="C116" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="G115" s="2" t="s">
+      <c r="D116" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E116" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="H115" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I115" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J115" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K115" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="116" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="11" t="s">
+      <c r="F116" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="B116" s="11"/>
-      <c r="C116" s="11"/>
-      <c r="D116" s="11"/>
-      <c r="E116" s="11"/>
-      <c r="F116" s="11"/>
-      <c r="G116" s="11"/>
-      <c r="H116" s="11"/>
-      <c r="I116" s="11"/>
-      <c r="J116" s="11"/>
-      <c r="K116" s="11"/>
-    </row>
-    <row r="117" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G116" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="H116" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I116" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J116" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K116" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="2" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B117" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="F117" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="C117" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="D117" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E117" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="F117" s="2" t="s">
-        <v>504</v>
-      </c>
       <c r="G117" s="2" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H117" s="12" t="s">
         <v>43</v>
@@ -6391,25 +6439,25 @@
     </row>
     <row r="118" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="H118" s="12" t="s">
         <v>43</v>
@@ -6424,77 +6472,77 @@
         <v>43</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="11" t="s">
-        <v>510</v>
-      </c>
-      <c r="B119" s="11"/>
-      <c r="C119" s="11"/>
-      <c r="D119" s="11"/>
-      <c r="E119" s="11"/>
-      <c r="F119" s="11"/>
-      <c r="G119" s="11"/>
-      <c r="H119" s="11"/>
-      <c r="I119" s="11"/>
-      <c r="J119" s="11"/>
-      <c r="K119" s="11"/>
-    </row>
-    <row r="120" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="B120" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="C120" s="2" t="s">
+    <row r="119" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="D120" s="2" t="s">
+      <c r="B119" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="D119" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E120" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="F120" s="2" t="s">
+      <c r="E119" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="G120" s="2" t="s">
+      <c r="F119" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="H120" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I120" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J120" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K120" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G119" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="H119" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I119" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J119" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K119" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="11" t="s">
+        <v>517</v>
+      </c>
+      <c r="B120" s="11"/>
+      <c r="C120" s="11"/>
+      <c r="D120" s="11"/>
+      <c r="E120" s="11"/>
+      <c r="F120" s="11"/>
+      <c r="G120" s="11"/>
+      <c r="H120" s="11"/>
+      <c r="I120" s="11"/>
+      <c r="J120" s="11"/>
+      <c r="K120" s="11"/>
+    </row>
+    <row r="121" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="2" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>518</v>
+        <v>435</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H121" s="12" t="s">
         <v>43</v>
@@ -6511,22 +6559,22 @@
     </row>
     <row r="122" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>57</v>
       </c>
       <c r="E122" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="F122" s="2" t="s">
         <v>523</v>
-      </c>
-      <c r="F122" s="2" t="s">
-        <v>524</v>
       </c>
       <c r="G122" s="2" t="s">
         <v>525</v>
@@ -6544,68 +6592,68 @@
         <v>43</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="2" t="s">
+    <row r="123" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="11" t="s">
         <v>526</v>
       </c>
-      <c r="B123" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="C123" s="2" t="s">
+      <c r="B123" s="11"/>
+      <c r="C123" s="11"/>
+      <c r="D123" s="11"/>
+      <c r="E123" s="11"/>
+      <c r="F123" s="11"/>
+      <c r="G123" s="11"/>
+      <c r="H123" s="11"/>
+      <c r="I123" s="11"/>
+      <c r="J123" s="11"/>
+      <c r="K123" s="11"/>
+    </row>
+    <row r="124" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="D123" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E123" s="2" t="s">
+      <c r="B124" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="C124" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="F123" s="2" t="s">
+      <c r="D124" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E124" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="G123" s="2" t="s">
+      <c r="F124" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="H123" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I123" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J123" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K123" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="124" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="11" t="s">
+      <c r="G124" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="B124" s="11"/>
-      <c r="C124" s="11"/>
-      <c r="D124" s="11"/>
-      <c r="E124" s="11"/>
-      <c r="F124" s="11"/>
-      <c r="G124" s="11"/>
-      <c r="H124" s="11"/>
-      <c r="I124" s="11"/>
-      <c r="J124" s="11"/>
-      <c r="K124" s="11"/>
+      <c r="H124" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I124" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J124" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K124" s="2" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="125" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="2" t="s">
         <v>532</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>533</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E125" s="2" t="s">
         <v>534</v>
@@ -6634,13 +6682,13 @@
         <v>537</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>538</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>539</v>
@@ -6664,92 +6712,112 @@
         <v>43</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A127" s="11" t="s">
+    <row r="127" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="B127" s="11"/>
-      <c r="C127" s="11"/>
-      <c r="D127" s="11"/>
-      <c r="E127" s="11"/>
-      <c r="F127" s="11"/>
-      <c r="G127" s="11"/>
-      <c r="H127" s="11"/>
-      <c r="I127" s="11"/>
-      <c r="J127" s="11"/>
-      <c r="K127" s="11"/>
-    </row>
-    <row r="128" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="2" t="s">
+      <c r="B127" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="C127" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="B128" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="C128" s="2" t="s">
+      <c r="D127" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E127" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="D128" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E128" s="2" t="s">
+      <c r="F127" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="F128" s="2" t="s">
+      <c r="G127" s="2" t="s">
         <v>546</v>
       </c>
-      <c r="G128" s="2" t="s">
+      <c r="H127" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I127" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J127" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K127" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="11" t="s">
         <v>547</v>
       </c>
-      <c r="H128" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I128" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J128" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K128" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="129" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="11" t="s">
+      <c r="B128" s="11"/>
+      <c r="C128" s="11"/>
+      <c r="D128" s="11"/>
+      <c r="E128" s="11"/>
+      <c r="F128" s="11"/>
+      <c r="G128" s="11"/>
+      <c r="H128" s="11"/>
+      <c r="I128" s="11"/>
+      <c r="J128" s="11"/>
+      <c r="K128" s="11"/>
+    </row>
+    <row r="129" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="B129" s="11"/>
-      <c r="C129" s="11"/>
-      <c r="D129" s="11"/>
-      <c r="E129" s="11"/>
-      <c r="F129" s="11"/>
-      <c r="G129" s="11"/>
-      <c r="H129" s="11"/>
-      <c r="I129" s="11"/>
-      <c r="J129" s="11"/>
-      <c r="K129" s="11"/>
+      <c r="B129" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="F129" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="H129" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I129" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J129" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K129" s="2" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="130" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="2" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="H130" s="12" t="s">
         <v>43</v>
@@ -6764,112 +6832,92 @@
         <v>43</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="B131" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="C131" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="D131" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E131" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="F131" s="2" t="s">
-        <v>557</v>
-      </c>
-      <c r="G131" s="2" t="s">
+    <row r="131" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="11" t="s">
         <v>558</v>
       </c>
-      <c r="H131" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I131" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J131" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K131" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="132" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="11" t="s">
+      <c r="B131" s="11"/>
+      <c r="C131" s="11"/>
+      <c r="D131" s="11"/>
+      <c r="E131" s="11"/>
+      <c r="F131" s="11"/>
+      <c r="G131" s="11"/>
+      <c r="H131" s="11"/>
+      <c r="I131" s="11"/>
+      <c r="J131" s="11"/>
+      <c r="K131" s="11"/>
+    </row>
+    <row r="132" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="B132" s="11"/>
-      <c r="C132" s="11"/>
-      <c r="D132" s="11"/>
-      <c r="E132" s="11"/>
-      <c r="F132" s="11"/>
-      <c r="G132" s="11"/>
-      <c r="H132" s="11"/>
-      <c r="I132" s="11"/>
-      <c r="J132" s="11"/>
-      <c r="K132" s="11"/>
-    </row>
-    <row r="133" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="2" t="s">
+      <c r="B132" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="C132" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="B133" s="2" t="s">
-        <v>559</v>
-      </c>
-      <c r="C133" s="2" t="s">
+      <c r="D132" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E132" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="D133" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E133" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="F133" s="2" t="s">
+      <c r="F132" s="2" t="s">
         <v>562</v>
       </c>
-      <c r="G133" s="2" t="s">
+      <c r="G132" s="2" t="s">
         <v>563</v>
       </c>
-      <c r="H133" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I133" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J133" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K133" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="134" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H132" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I132" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J132" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K132" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="11" t="s">
+        <v>564</v>
+      </c>
+      <c r="B133" s="11"/>
+      <c r="C133" s="11"/>
+      <c r="D133" s="11"/>
+      <c r="E133" s="11"/>
+      <c r="F133" s="11"/>
+      <c r="G133" s="11"/>
+      <c r="H133" s="11"/>
+      <c r="I133" s="11"/>
+      <c r="J133" s="11"/>
+      <c r="K133" s="11"/>
+    </row>
+    <row r="134" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="B134" s="2" t="s">
         <v>564</v>
       </c>
-      <c r="B134" s="2" t="s">
-        <v>559</v>
-      </c>
       <c r="C134" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>57</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H134" s="12" t="s">
         <v>43</v>
@@ -6884,71 +6932,71 @@
         <v>43</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="11" t="s">
-        <v>569</v>
-      </c>
-      <c r="B135" s="11"/>
-      <c r="C135" s="11"/>
-      <c r="D135" s="11"/>
-      <c r="E135" s="11"/>
-      <c r="F135" s="11"/>
-      <c r="G135" s="11"/>
-      <c r="H135" s="11"/>
-      <c r="I135" s="11"/>
-      <c r="J135" s="11"/>
-      <c r="K135" s="11"/>
-    </row>
-    <row r="136" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="2" t="s">
+    <row r="135" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="B136" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="C136" s="2" t="s">
+      <c r="B135" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="C135" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="D136" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E136" s="2" t="s">
+      <c r="D135" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E135" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="F136" s="2" t="s">
+      <c r="F135" s="2" t="s">
         <v>573</v>
       </c>
-      <c r="G136" s="2" t="s">
+      <c r="G135" s="2" t="s">
         <v>574</v>
       </c>
-      <c r="H136" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I136" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J136" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K136" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="137" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H135" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I135" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J135" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K135" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="11" t="s">
+        <v>575</v>
+      </c>
+      <c r="B136" s="11"/>
+      <c r="C136" s="11"/>
+      <c r="D136" s="11"/>
+      <c r="E136" s="11"/>
+      <c r="F136" s="11"/>
+      <c r="G136" s="11"/>
+      <c r="H136" s="11"/>
+      <c r="I136" s="11"/>
+      <c r="J136" s="11"/>
+      <c r="K136" s="11"/>
+    </row>
+    <row r="137" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A137" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="B137" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="B137" s="2" t="s">
-        <v>569</v>
-      </c>
       <c r="C137" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>577</v>
+        <v>119</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>578</v>
@@ -6969,18 +7017,18 @@
         <v>43</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="138" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="2" t="s">
         <v>580</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>581</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E138" s="2" t="s">
         <v>582</v>
@@ -7004,132 +7052,132 @@
         <v>43</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="2" t="s">
+    <row r="139" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="11" t="s">
         <v>585</v>
       </c>
-      <c r="B139" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="C139" s="2" t="s">
+      <c r="B139" s="11"/>
+      <c r="C139" s="11"/>
+      <c r="D139" s="11"/>
+      <c r="E139" s="11"/>
+      <c r="F139" s="11"/>
+      <c r="G139" s="11"/>
+      <c r="H139" s="11"/>
+      <c r="I139" s="11"/>
+      <c r="J139" s="11"/>
+      <c r="K139" s="11"/>
+    </row>
+    <row r="140" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="D139" s="2" t="s">
+      <c r="B140" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="F140" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="G140" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="H140" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I140" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J140" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K140" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="F141" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="G141" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="H141" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I141" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J141" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K141" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="142" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A142" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="D142" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E139" s="2" t="s">
-        <v>587</v>
-      </c>
-      <c r="F139" s="2" t="s">
-        <v>588</v>
-      </c>
-      <c r="G139" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="H139" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I139" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J139" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K139" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="140" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="C140" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="D140" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E140" s="2" t="s">
-        <v>592</v>
-      </c>
-      <c r="F140" s="2" t="s">
-        <v>593</v>
-      </c>
-      <c r="G140" s="2" t="s">
-        <v>594</v>
-      </c>
-      <c r="H140" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I140" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J140" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K140" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="141" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="B141" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="C141" s="2" t="s">
-        <v>596</v>
-      </c>
-      <c r="D141" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E141" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="F141" s="2" t="s">
+      <c r="E142" s="2" t="s">
         <v>598</v>
       </c>
-      <c r="G141" s="2" t="s">
+      <c r="F142" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="H141" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I141" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J141" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K141" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="142" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="11" t="s">
+      <c r="G142" s="2" t="s">
         <v>600</v>
       </c>
-      <c r="B142" s="11"/>
-      <c r="C142" s="11"/>
-      <c r="D142" s="11"/>
-      <c r="E142" s="11"/>
-      <c r="F142" s="11"/>
-      <c r="G142" s="11"/>
-      <c r="H142" s="11"/>
-      <c r="I142" s="11"/>
-      <c r="J142" s="11"/>
-      <c r="K142" s="11"/>
-    </row>
-    <row r="143" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H142" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I142" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J142" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K142" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="143" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="2" t="s">
         <v>601</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>602</v>
@@ -7159,12 +7207,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="2" t="s">
         <v>606</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>607</v>
@@ -7199,13 +7247,13 @@
         <v>611</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>612</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>613</v>
@@ -7229,97 +7277,97 @@
         <v>43</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="2" t="s">
+    <row r="146" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="11" t="s">
         <v>616</v>
       </c>
-      <c r="B146" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="C146" s="2" t="s">
+      <c r="B146" s="11"/>
+      <c r="C146" s="11"/>
+      <c r="D146" s="11"/>
+      <c r="E146" s="11"/>
+      <c r="F146" s="11"/>
+      <c r="G146" s="11"/>
+      <c r="H146" s="11"/>
+      <c r="I146" s="11"/>
+      <c r="J146" s="11"/>
+      <c r="K146" s="11"/>
+    </row>
+    <row r="147" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="2" t="s">
         <v>617</v>
       </c>
-      <c r="D146" s="2" t="s">
+      <c r="B147" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="D147" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E146" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="F146" s="2" t="s">
+      <c r="E147" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="G146" s="2" t="s">
+      <c r="F147" s="2" t="s">
         <v>620</v>
       </c>
-      <c r="H146" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I146" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J146" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K146" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="147" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="2" t="s">
+      <c r="G147" s="2" t="s">
         <v>621</v>
       </c>
-      <c r="B147" s="2" t="s">
-        <v>600</v>
-      </c>
-      <c r="C147" s="2" t="s">
+      <c r="H147" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K147" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="2" t="s">
         <v>622</v>
       </c>
-      <c r="D147" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E147" s="2" t="s">
+      <c r="B148" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="C148" s="2" t="s">
         <v>623</v>
       </c>
-      <c r="F147" s="2" t="s">
+      <c r="D148" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E148" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="G147" s="2" t="s">
+      <c r="F148" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="H147" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K147" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="148" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="11" t="s">
+      <c r="G148" s="2" t="s">
         <v>626</v>
       </c>
-      <c r="B148" s="11"/>
-      <c r="C148" s="11"/>
-      <c r="D148" s="11"/>
-      <c r="E148" s="11"/>
-      <c r="F148" s="11"/>
-      <c r="G148" s="11"/>
-      <c r="H148" s="11"/>
-      <c r="I148" s="11"/>
-      <c r="J148" s="11"/>
-      <c r="K148" s="11"/>
-    </row>
-    <row r="149" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H148" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J148" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K148" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="149" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="2" t="s">
         <v>627</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>626</v>
+        <v>616</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>628</v>
@@ -7349,12 +7397,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="2" t="s">
         <v>632</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>626</v>
+        <v>616</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>633</v>
@@ -7389,7 +7437,7 @@
         <v>637</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>626</v>
+        <v>616</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>638</v>
@@ -7419,147 +7467,147 @@
         <v>43</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="2" t="s">
+    <row r="152" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="11" t="s">
         <v>642</v>
       </c>
-      <c r="B152" s="2" t="s">
-        <v>626</v>
-      </c>
-      <c r="C152" s="2" t="s">
+      <c r="B152" s="11"/>
+      <c r="C152" s="11"/>
+      <c r="D152" s="11"/>
+      <c r="E152" s="11"/>
+      <c r="F152" s="11"/>
+      <c r="G152" s="11"/>
+      <c r="H152" s="11"/>
+      <c r="I152" s="11"/>
+      <c r="J152" s="11"/>
+      <c r="K152" s="11"/>
+    </row>
+    <row r="153" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="D152" s="2" t="s">
+      <c r="B153" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="D153" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E152" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="F152" s="2" t="s">
+      <c r="E153" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="G152" s="2" t="s">
+      <c r="F153" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="H152" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I152" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J152" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K152" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="153" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="2" t="s">
+      <c r="G153" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="B153" s="2" t="s">
-        <v>626</v>
-      </c>
-      <c r="C153" s="2" t="s">
+      <c r="H153" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I153" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J153" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K153" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A154" s="2" t="s">
         <v>648</v>
       </c>
-      <c r="D153" s="2" t="s">
+      <c r="B154" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="F154" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="G154" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="H154" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I154" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J154" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K154" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="155" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A155" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="D155" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E153" s="2" t="s">
-        <v>644</v>
-      </c>
-      <c r="F153" s="2" t="s">
-        <v>649</v>
-      </c>
-      <c r="G153" s="2" t="s">
-        <v>650</v>
-      </c>
-      <c r="H153" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I153" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J153" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K153" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="154" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="2" t="s">
-        <v>651</v>
-      </c>
-      <c r="B154" s="2" t="s">
-        <v>626</v>
-      </c>
-      <c r="C154" s="2" t="s">
-        <v>652</v>
-      </c>
-      <c r="D154" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E154" s="2" t="s">
-        <v>653</v>
-      </c>
-      <c r="F154" s="2" t="s">
-        <v>654</v>
-      </c>
-      <c r="G154" s="2" t="s">
+      <c r="E155" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="H154" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I154" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J154" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K154" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="155" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A155" s="11" t="s">
+      <c r="F155" s="2" t="s">
         <v>656</v>
       </c>
-      <c r="B155" s="11"/>
-      <c r="C155" s="11"/>
-      <c r="D155" s="11"/>
-      <c r="E155" s="11"/>
-      <c r="F155" s="11"/>
-      <c r="G155" s="11"/>
-      <c r="H155" s="11"/>
-      <c r="I155" s="11"/>
-      <c r="J155" s="11"/>
-      <c r="K155" s="11"/>
-    </row>
-    <row r="156" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="G155" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="H155" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I155" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J155" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K155" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="156" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="2" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>656</v>
+        <v>642</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H156" s="12" t="s">
         <v>43</v>
@@ -7574,21 +7622,21 @@
         <v>43</v>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="2" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>656</v>
+        <v>642</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>57</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>664</v>
+        <v>660</v>
       </c>
       <c r="F157" s="2" t="s">
         <v>665</v>
@@ -7614,13 +7662,13 @@
         <v>667</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>656</v>
+        <v>642</v>
       </c>
       <c r="C158" s="2" t="s">
         <v>668</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E158" s="2" t="s">
         <v>669</v>
@@ -7644,43 +7692,163 @@
         <v>43</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="2" t="s">
+    <row r="159" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="11" t="s">
         <v>672</v>
       </c>
-      <c r="B159" s="2" t="s">
-        <v>656</v>
-      </c>
-      <c r="C159" s="2" t="s">
+      <c r="B159" s="11"/>
+      <c r="C159" s="11"/>
+      <c r="D159" s="11"/>
+      <c r="E159" s="11"/>
+      <c r="F159" s="11"/>
+      <c r="G159" s="11"/>
+      <c r="H159" s="11"/>
+      <c r="I159" s="11"/>
+      <c r="J159" s="11"/>
+      <c r="K159" s="11"/>
+    </row>
+    <row r="160" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="D159" s="2" t="s">
+      <c r="B160" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="F160" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="G160" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="H160" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I160" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J160" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K160" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="161" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A161" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="D161" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E159" s="2" t="s">
-        <v>674</v>
-      </c>
-      <c r="F159" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="G159" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="H159" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I159" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J159" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K159" s="2" t="s">
+      <c r="E161" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="F161" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="G161" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="H161" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I161" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J161" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K161" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="162" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A162" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="F162" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="G162" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="H162" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I162" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J162" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K162" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="163" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="F163" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="G163" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="H163" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I163" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J163" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K163" s="2" t="s">
         <v>43</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="31">
+  <mergeCells count="32">
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A8:K8"/>
@@ -7697,21 +7865,22 @@
     <mergeCell ref="A70:K70"/>
     <mergeCell ref="A72:K72"/>
     <mergeCell ref="A77:K77"/>
-    <mergeCell ref="A80:K80"/>
-    <mergeCell ref="A85:K85"/>
-    <mergeCell ref="A91:K91"/>
-    <mergeCell ref="A98:K98"/>
-    <mergeCell ref="A111:K111"/>
-    <mergeCell ref="A116:K116"/>
-    <mergeCell ref="A119:K119"/>
-    <mergeCell ref="A124:K124"/>
-    <mergeCell ref="A127:K127"/>
-    <mergeCell ref="A129:K129"/>
-    <mergeCell ref="A132:K132"/>
-    <mergeCell ref="A135:K135"/>
-    <mergeCell ref="A142:K142"/>
-    <mergeCell ref="A148:K148"/>
-    <mergeCell ref="A155:K155"/>
+    <mergeCell ref="A81:K81"/>
+    <mergeCell ref="A84:K84"/>
+    <mergeCell ref="A89:K89"/>
+    <mergeCell ref="A95:K95"/>
+    <mergeCell ref="A102:K102"/>
+    <mergeCell ref="A115:K115"/>
+    <mergeCell ref="A120:K120"/>
+    <mergeCell ref="A123:K123"/>
+    <mergeCell ref="A128:K128"/>
+    <mergeCell ref="A131:K131"/>
+    <mergeCell ref="A133:K133"/>
+    <mergeCell ref="A136:K136"/>
+    <mergeCell ref="A139:K139"/>
+    <mergeCell ref="A146:K146"/>
+    <mergeCell ref="A152:K152"/>
+    <mergeCell ref="A159:K159"/>
   </mergeCells>
   <conditionalFormatting sqref="H3:H400">
     <cfRule type="cellIs" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -7728,7 +7897,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" prompt="Choose Pass / Fail / Partial / N/A / Not run" promptTitle="Result" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H4:H7 H9:H13 H15:H20 H22:H26 H28:H30 H32 H34:H35 H37:H40 H42:H44 H46:H55 H57:H63 H65:H69 H71 H73:H76 H78:H79 H81:H84 H86:H90 H92:H97 H99:H110 H112:H115 H117:H118 H120:H123 H125:H126 H128 H130:H131 H133:H134 H136:H141 H143:H147 H149:H154 H156:H159" type="none">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" prompt="Choose Pass / Fail / Partial / N/A / Not run" promptTitle="Result" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H4:H7 H9:H13 H15:H20 H22:H26 H28:H30 H32 H34:H35 H37:H40 H42:H44 H46:H55 H57:H63 H65:H69 H71 H73:H76 H78:H80 H82:H83 H85:H88 H90:H94 H96:H101 H103:H114 H116:H119 H121:H122 H124:H127 H129:H130 H132 H134:H135 H137:H138 H140:H145 H147:H151 H153:H158 H160:H163" type="none">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -7748,7 +7917,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B40"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.37"/>
@@ -7757,13 +7926,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>677</v>
+        <v>693</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>678</v>
+        <v>694</v>
       </c>
       <c r="B2" s="3"/>
     </row>
@@ -7814,7 +7983,7 @@
     </row>
     <row r="8" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>679</v>
+        <v>695</v>
       </c>
       <c r="B8" s="2" t="e">
         <f aca="false">of:=COUNTA('Test Cases'!A3:A400)-COUNTIF('Test Cases'!D3:D400,"")</f>
@@ -7823,7 +7992,7 @@
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>680</v>
+        <v>696</v>
       </c>
       <c r="B9" s="3"/>
     </row>
@@ -7958,141 +8127,150 @@
         <v>340</v>
       </c>
       <c r="B24" s="2" t="e">
+        <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Case alias",'Test Cases'!H3:H400,"Pass")</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="8" t="s">
+        <v>356</v>
+      </c>
+      <c r="B25" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Photo download",'Test Cases'!H3:H400,"Pass")</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="8" t="s">
-        <v>351</v>
-      </c>
-      <c r="B25" s="2" t="e">
+    <row r="26" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="8" t="s">
+        <v>367</v>
+      </c>
+      <c r="B26" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Case report",'Test Cases'!H3:H400,"Pass")</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="8" t="s">
-        <v>372</v>
-      </c>
-      <c r="B26" s="2" t="e">
+    <row r="27" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="8" t="s">
+        <v>388</v>
+      </c>
+      <c r="B27" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Manager",'Test Cases'!H3:H400,"Pass")</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="8" t="s">
-        <v>398</v>
-      </c>
-      <c r="B27" s="2" t="e">
+    <row r="28" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="8" t="s">
+        <v>414</v>
+      </c>
+      <c r="B28" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Manager edit",'Test Cases'!H3:H400,"Pass")</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="8" t="s">
-        <v>427</v>
-      </c>
-      <c r="B28" s="2" t="e">
+    <row r="29" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="B29" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"RTE editor",'Test Cases'!H3:H400,"Pass")</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="8" t="s">
-        <v>481</v>
-      </c>
-      <c r="B29" s="2" t="e">
+    <row r="30" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="B30" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Teams",'Test Cases'!H3:H400,"Pass")</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="8" t="s">
-        <v>501</v>
-      </c>
-      <c r="B30" s="2" t="e">
+    <row r="31" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="8" t="s">
+        <v>517</v>
+      </c>
+      <c r="B31" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"History",'Test Cases'!H3:H400,"Pass")</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="8" t="s">
-        <v>510</v>
-      </c>
-      <c r="B31" s="2" t="e">
+    <row r="32" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="8" t="s">
+        <v>526</v>
+      </c>
+      <c r="B32" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Usage",'Test Cases'!H3:H400,"Pass")</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="8" t="s">
-        <v>531</v>
-      </c>
-      <c r="B32" s="2" t="e">
+    <row r="33" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="8" t="s">
+        <v>547</v>
+      </c>
+      <c r="B33" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Read-only",'Test Cases'!H3:H400,"Pass")</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="8" t="s">
-        <v>542</v>
-      </c>
-      <c r="B33" s="2" t="e">
+    <row r="34" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="8" t="s">
+        <v>558</v>
+      </c>
+      <c r="B34" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Dark mode",'Test Cases'!H3:H400,"Pass")</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="8" t="s">
-        <v>548</v>
-      </c>
-      <c r="B34" s="2" t="e">
+    <row r="35" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="8" t="s">
+        <v>564</v>
+      </c>
+      <c r="B35" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Background",'Test Cases'!H3:H400,"Pass")</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="8" t="s">
-        <v>559</v>
-      </c>
-      <c r="B35" s="2" t="e">
+    <row r="36" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="8" t="s">
+        <v>575</v>
+      </c>
+      <c r="B36" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Diagnostics",'Test Cases'!H3:H400,"Pass")</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="8" t="s">
-        <v>569</v>
-      </c>
-      <c r="B36" s="2" t="e">
+    <row r="37" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="8" t="s">
+        <v>585</v>
+      </c>
+      <c r="B37" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Security",'Test Cases'!H3:H400,"Pass")</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="8" t="s">
-        <v>600</v>
-      </c>
-      <c r="B37" s="2" t="e">
+    <row r="38" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="8" t="s">
+        <v>616</v>
+      </c>
+      <c r="B38" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Acknowledgements",'Test Cases'!H3:H400,"Pass")</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="8" t="s">
-        <v>626</v>
-      </c>
-      <c r="B38" s="2" t="e">
+    <row r="39" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="8" t="s">
+        <v>642</v>
+      </c>
+      <c r="B39" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Suggestions",'Test Cases'!H3:H400,"Pass")</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="8" t="s">
-        <v>656</v>
-      </c>
-      <c r="B39" s="2" t="e">
+    <row r="40" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="8" t="s">
+        <v>672</v>
+      </c>
+      <c r="B40" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"UX",'Test Cases'!H3:H400,"Pass")</f>
         <v>#VALUE!</v>
       </c>
@@ -8127,88 +8305,88 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>681</v>
+        <v>697</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>682</v>
+        <v>698</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>683</v>
+        <v>699</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>684</v>
+        <v>700</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>685</v>
+        <v>701</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>686</v>
+        <v>702</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>687</v>
+        <v>703</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>688</v>
+        <v>704</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>689</v>
+        <v>705</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>690</v>
+        <v>706</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>691</v>
+        <v>707</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>692</v>
+        <v>708</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>693</v>
+        <v>709</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>694</v>
+        <v>710</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>695</v>
+        <v>711</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>696</v>
+        <v>712</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>697</v>
+        <v>713</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>698</v>
+        <v>714</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>699</v>
+        <v>715</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>700</v>
+        <v>716</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>701</v>
+        <v>717</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Nucleus_Enhancer_Validation_Results_v3.0.0.xlsx
+++ b/docs/Nucleus_Enhancer_Validation_Results_v3.0.0.xlsx
@@ -23,13 +23,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1562" uniqueCount="718">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1573" uniqueCount="723">
   <si>
     <t xml:space="preserve">How to use this workbook</t>
   </si>
   <si>
     <t xml:space="preserve">Work through the 'Test Cases' sheet top to bottom. For each row set the Result cell (dropdown: Pass / Fail / Partial / N/A / Not run), and record what you saw in 'Actual / notes', plus your initials and the date.
-There are 130 cases across all feature areas.
+There are 131 cases across all feature areas.
 This is an internal self-check, not a formal/Quality validation. Use the Diagnostics sheet (or docs/Nucleus_Enhancer_Diagnostics.md) to capture detail when something misbehaves.</t>
   </si>
   <si>
@@ -1296,10 +1296,10 @@
     <t xml:space="preserve">Existing template</t>
   </si>
   <si>
-    <t xml:space="preserve">Change CONTENT, pick minor/major, give reason, save</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Version bumps; reason required; new history snapshot</t>
+    <t xml:space="preserve">Change CONTENT, pick minor/major, optionally add a reason, save</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Version bumps; new history snapshot; reason recorded if given (everything except Name is optional — a blank reason/content still saves)</t>
   </si>
   <si>
     <t xml:space="preserve">ME-03</t>
@@ -1342,6 +1342,21 @@
   </si>
   <si>
     <t xml:space="preserve">ME-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Delete hidden without permission</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin whose Salesforce DELETE permission has been removed (e.g. at go-live)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open Manager templates list + bulk bar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No Delete buttons appear (row or bulk) — gated on the real Salesforce permission, not just the IsAdmin flag; reload + sync after the permission change</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME-07</t>
   </si>
   <si>
     <t xml:space="preserve">Status lifecycle</t>
@@ -2767,7 +2782,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K163"/>
+  <dimension ref="A1:K164"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7.16"/>
@@ -5742,7 +5757,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2" t="s">
         <v>420</v>
       </c>
@@ -5882,7 +5897,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2" t="s">
         <v>438</v>
       </c>
@@ -5917,62 +5932,62 @@
         <v>43</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="11" t="s">
+    <row r="102" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="B102" s="11"/>
-      <c r="C102" s="11"/>
-      <c r="D102" s="11"/>
-      <c r="E102" s="11"/>
-      <c r="F102" s="11"/>
-      <c r="G102" s="11"/>
-      <c r="H102" s="11"/>
-      <c r="I102" s="11"/>
-      <c r="J102" s="11"/>
-      <c r="K102" s="11"/>
-    </row>
-    <row r="103" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="2" t="s">
+      <c r="B102" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="C102" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="B103" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="C103" s="2" t="s">
+      <c r="D102" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E102" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="D103" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E103" s="2" t="s">
+      <c r="F102" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="F103" s="2" t="s">
+      <c r="G102" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="G103" s="2" t="s">
+      <c r="H102" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J102" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K102" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="11" t="s">
         <v>448</v>
       </c>
-      <c r="H103" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I103" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J103" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K103" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B103" s="11"/>
+      <c r="C103" s="11"/>
+      <c r="D103" s="11"/>
+      <c r="E103" s="11"/>
+      <c r="F103" s="11"/>
+      <c r="G103" s="11"/>
+      <c r="H103" s="11"/>
+      <c r="I103" s="11"/>
+      <c r="J103" s="11"/>
+      <c r="K103" s="11"/>
+    </row>
+    <row r="104" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
         <v>449</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="C104" s="2" t="s">
         <v>450</v>
@@ -6007,7 +6022,7 @@
         <v>454</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>455</v>
@@ -6016,83 +6031,83 @@
         <v>51</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="F105" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="H105" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I105" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J105" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K105" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E106" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="G105" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="H105" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I105" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J105" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K105" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="106" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A106" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="D106" s="2" t="s">
+      <c r="F106" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="H106" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I106" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J106" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K106" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D107" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E106" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="F106" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="G106" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="H106" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I106" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J106" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K106" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="107" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="D107" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="E107" s="2" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H107" s="12" t="s">
         <v>43</v>
@@ -6107,27 +6122,27 @@
         <v>43</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H108" s="12" t="s">
         <v>43</v>
@@ -6142,62 +6157,62 @@
         <v>43</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="D109" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="H109" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I109" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J109" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K109" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D110" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E109" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="F109" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="G109" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="H109" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I109" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J109" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K109" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="B110" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="C110" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="D110" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="E110" s="2" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H110" s="12" t="s">
         <v>43</v>
@@ -6214,19 +6229,19 @@
     </row>
     <row r="111" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>480</v>
+        <v>456</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>481</v>
@@ -6252,13 +6267,13 @@
         <v>483</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>484</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E112" s="2" t="s">
         <v>485</v>
@@ -6282,27 +6297,27 @@
         <v>43</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="2" t="s">
         <v>488</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>489</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>451</v>
+        <v>490</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H113" s="12" t="s">
         <v>43</v>
@@ -6317,21 +6332,21 @@
         <v>43</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>39</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>494</v>
+        <v>456</v>
       </c>
       <c r="F114" s="2" t="s">
         <v>495</v>
@@ -6352,62 +6367,62 @@
         <v>43</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="11" t="s">
+    <row r="115" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="B115" s="11"/>
-      <c r="C115" s="11"/>
-      <c r="D115" s="11"/>
-      <c r="E115" s="11"/>
-      <c r="F115" s="11"/>
-      <c r="G115" s="11"/>
-      <c r="H115" s="11"/>
-      <c r="I115" s="11"/>
-      <c r="J115" s="11"/>
-      <c r="K115" s="11"/>
-    </row>
-    <row r="116" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="2" t="s">
+      <c r="B115" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="C115" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="B116" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="C116" s="2" t="s">
+      <c r="D115" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E115" s="2" t="s">
         <v>499</v>
       </c>
-      <c r="D116" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E116" s="2" t="s">
+      <c r="F115" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="F116" s="2" t="s">
+      <c r="G115" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="G116" s="2" t="s">
+      <c r="H115" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I115" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J115" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K115" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="11" t="s">
         <v>502</v>
       </c>
-      <c r="H116" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I116" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J116" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K116" s="2" t="s">
-        <v>43</v>
-      </c>
+      <c r="B116" s="11"/>
+      <c r="C116" s="11"/>
+      <c r="D116" s="11"/>
+      <c r="E116" s="11"/>
+      <c r="F116" s="11"/>
+      <c r="G116" s="11"/>
+      <c r="H116" s="11"/>
+      <c r="I116" s="11"/>
+      <c r="J116" s="11"/>
+      <c r="K116" s="11"/>
     </row>
     <row r="117" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="2" t="s">
         <v>503</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>504</v>
@@ -6419,10 +6434,10 @@
         <v>505</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H117" s="12" t="s">
         <v>43</v>
@@ -6439,22 +6454,22 @@
     </row>
     <row r="118" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="2" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>39</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="G118" s="2" t="s">
         <v>511</v>
@@ -6477,13 +6492,13 @@
         <v>512</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>513</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E119" s="2" t="s">
         <v>514</v>
@@ -6507,147 +6522,147 @@
         <v>43</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="11" t="s">
+    <row r="120" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="2" t="s">
         <v>517</v>
       </c>
-      <c r="B120" s="11"/>
-      <c r="C120" s="11"/>
-      <c r="D120" s="11"/>
-      <c r="E120" s="11"/>
-      <c r="F120" s="11"/>
-      <c r="G120" s="11"/>
-      <c r="H120" s="11"/>
-      <c r="I120" s="11"/>
-      <c r="J120" s="11"/>
-      <c r="K120" s="11"/>
-    </row>
-    <row r="121" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="2" t="s">
+      <c r="B120" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="C120" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="B121" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="C121" s="2" t="s">
+      <c r="D120" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E120" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="D121" s="2" t="s">
+      <c r="F120" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="H120" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I120" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J120" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K120" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="11" t="s">
+        <v>522</v>
+      </c>
+      <c r="B121" s="11"/>
+      <c r="C121" s="11"/>
+      <c r="D121" s="11"/>
+      <c r="E121" s="11"/>
+      <c r="F121" s="11"/>
+      <c r="G121" s="11"/>
+      <c r="H121" s="11"/>
+      <c r="I121" s="11"/>
+      <c r="J121" s="11"/>
+      <c r="K121" s="11"/>
+    </row>
+    <row r="122" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="D122" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E121" s="2" t="s">
+      <c r="E122" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="F121" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="G121" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="H121" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I121" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J121" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K121" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="122" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="2" t="s">
+      <c r="F122" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="H122" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I122" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J122" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K122" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="B123" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="B122" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="C122" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="D122" s="2" t="s">
+      <c r="C123" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="D123" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E122" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="F122" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="G122" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="H122" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I122" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J122" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K122" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="11" t="s">
-        <v>526</v>
-      </c>
-      <c r="B123" s="11"/>
-      <c r="C123" s="11"/>
-      <c r="D123" s="11"/>
-      <c r="E123" s="11"/>
-      <c r="F123" s="11"/>
-      <c r="G123" s="11"/>
-      <c r="H123" s="11"/>
-      <c r="I123" s="11"/>
-      <c r="J123" s="11"/>
-      <c r="K123" s="11"/>
-    </row>
-    <row r="124" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A124" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="B124" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="C124" s="2" t="s">
+      <c r="E123" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="F123" s="2" t="s">
         <v>528</v>
       </c>
-      <c r="D124" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E124" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="F124" s="2" t="s">
+      <c r="G123" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="G124" s="2" t="s">
+      <c r="H123" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I123" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J123" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K123" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="11" t="s">
         <v>531</v>
       </c>
-      <c r="H124" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I124" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J124" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K124" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="125" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B124" s="11"/>
+      <c r="C124" s="11"/>
+      <c r="D124" s="11"/>
+      <c r="E124" s="11"/>
+      <c r="F124" s="11"/>
+      <c r="G124" s="11"/>
+      <c r="H124" s="11"/>
+      <c r="I124" s="11"/>
+      <c r="J124" s="11"/>
+      <c r="K124" s="11"/>
+    </row>
+    <row r="125" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="2" t="s">
         <v>532</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>533</v>
@@ -6682,13 +6697,13 @@
         <v>537</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>538</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E126" s="2" t="s">
         <v>539</v>
@@ -6717,7 +6732,7 @@
         <v>542</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>543</v>
@@ -6747,62 +6762,62 @@
         <v>43</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="11" t="s">
+    <row r="128" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="B128" s="11"/>
-      <c r="C128" s="11"/>
-      <c r="D128" s="11"/>
-      <c r="E128" s="11"/>
-      <c r="F128" s="11"/>
-      <c r="G128" s="11"/>
-      <c r="H128" s="11"/>
-      <c r="I128" s="11"/>
-      <c r="J128" s="11"/>
-      <c r="K128" s="11"/>
-    </row>
-    <row r="129" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="2" t="s">
+      <c r="B128" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="C128" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="B129" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="C129" s="2" t="s">
+      <c r="D128" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E128" s="2" t="s">
         <v>549</v>
       </c>
-      <c r="D129" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E129" s="2" t="s">
+      <c r="F128" s="2" t="s">
         <v>550</v>
       </c>
-      <c r="F129" s="2" t="s">
+      <c r="G128" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="G129" s="2" t="s">
+      <c r="H128" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I128" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J128" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K128" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="11" t="s">
         <v>552</v>
       </c>
-      <c r="H129" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I129" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J129" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K129" s="2" t="s">
-        <v>43</v>
-      </c>
+      <c r="B129" s="11"/>
+      <c r="C129" s="11"/>
+      <c r="D129" s="11"/>
+      <c r="E129" s="11"/>
+      <c r="F129" s="11"/>
+      <c r="G129" s="11"/>
+      <c r="H129" s="11"/>
+      <c r="I129" s="11"/>
+      <c r="J129" s="11"/>
+      <c r="K129" s="11"/>
     </row>
     <row r="130" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="2" t="s">
         <v>553</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>554</v>
@@ -6832,112 +6847,112 @@
         <v>43</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A131" s="11" t="s">
+    <row r="131" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="B131" s="11"/>
-      <c r="C131" s="11"/>
-      <c r="D131" s="11"/>
-      <c r="E131" s="11"/>
-      <c r="F131" s="11"/>
-      <c r="G131" s="11"/>
-      <c r="H131" s="11"/>
-      <c r="I131" s="11"/>
-      <c r="J131" s="11"/>
-      <c r="K131" s="11"/>
-    </row>
-    <row r="132" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A132" s="2" t="s">
+      <c r="B131" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="C131" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="B132" s="2" t="s">
-        <v>558</v>
-      </c>
-      <c r="C132" s="2" t="s">
+      <c r="D131" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E131" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="D132" s="2" t="s">
+      <c r="F131" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="H131" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I131" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J131" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K131" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="11" t="s">
+        <v>563</v>
+      </c>
+      <c r="B132" s="11"/>
+      <c r="C132" s="11"/>
+      <c r="D132" s="11"/>
+      <c r="E132" s="11"/>
+      <c r="F132" s="11"/>
+      <c r="G132" s="11"/>
+      <c r="H132" s="11"/>
+      <c r="I132" s="11"/>
+      <c r="J132" s="11"/>
+      <c r="K132" s="11"/>
+    </row>
+    <row r="133" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="D133" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E132" s="2" t="s">
-        <v>561</v>
-      </c>
-      <c r="F132" s="2" t="s">
-        <v>562</v>
-      </c>
-      <c r="G132" s="2" t="s">
-        <v>563</v>
-      </c>
-      <c r="H132" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I132" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J132" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K132" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="133" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="11" t="s">
-        <v>564</v>
-      </c>
-      <c r="B133" s="11"/>
-      <c r="C133" s="11"/>
-      <c r="D133" s="11"/>
-      <c r="E133" s="11"/>
-      <c r="F133" s="11"/>
-      <c r="G133" s="11"/>
-      <c r="H133" s="11"/>
-      <c r="I133" s="11"/>
-      <c r="J133" s="11"/>
-      <c r="K133" s="11"/>
-    </row>
-    <row r="134" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="2" t="s">
-        <v>565</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>564</v>
-      </c>
-      <c r="C134" s="2" t="s">
+      <c r="E133" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="D134" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E134" s="2" t="s">
+      <c r="F133" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="F134" s="2" t="s">
+      <c r="G133" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="G134" s="2" t="s">
+      <c r="H133" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I133" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J133" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K133" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="11" t="s">
         <v>569</v>
       </c>
-      <c r="H134" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I134" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J134" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K134" s="2" t="s">
-        <v>43</v>
-      </c>
+      <c r="B134" s="11"/>
+      <c r="C134" s="11"/>
+      <c r="D134" s="11"/>
+      <c r="E134" s="11"/>
+      <c r="F134" s="11"/>
+      <c r="G134" s="11"/>
+      <c r="H134" s="11"/>
+      <c r="I134" s="11"/>
+      <c r="J134" s="11"/>
+      <c r="K134" s="11"/>
     </row>
     <row r="135" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="2" t="s">
         <v>570</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>571</v>
@@ -6967,71 +6982,71 @@
         <v>43</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="11" t="s">
+    <row r="136" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="B136" s="11"/>
-      <c r="C136" s="11"/>
-      <c r="D136" s="11"/>
-      <c r="E136" s="11"/>
-      <c r="F136" s="11"/>
-      <c r="G136" s="11"/>
-      <c r="H136" s="11"/>
-      <c r="I136" s="11"/>
-      <c r="J136" s="11"/>
-      <c r="K136" s="11"/>
-    </row>
-    <row r="137" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="2" t="s">
+      <c r="B136" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="C136" s="2" t="s">
         <v>576</v>
       </c>
-      <c r="B137" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="C137" s="2" t="s">
+      <c r="D136" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E136" s="2" t="s">
         <v>577</v>
       </c>
-      <c r="D137" s="2" t="s">
+      <c r="F136" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="G136" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="H136" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I136" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J136" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K136" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="137" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="11" t="s">
+        <v>580</v>
+      </c>
+      <c r="B137" s="11"/>
+      <c r="C137" s="11"/>
+      <c r="D137" s="11"/>
+      <c r="E137" s="11"/>
+      <c r="F137" s="11"/>
+      <c r="G137" s="11"/>
+      <c r="H137" s="11"/>
+      <c r="I137" s="11"/>
+      <c r="J137" s="11"/>
+      <c r="K137" s="11"/>
+    </row>
+    <row r="138" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="2" t="s">
+        <v>581</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="D138" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E137" s="2" t="s">
+      <c r="E138" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="F137" s="2" t="s">
-        <v>578</v>
-      </c>
-      <c r="G137" s="2" t="s">
-        <v>579</v>
-      </c>
-      <c r="H137" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I137" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J137" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K137" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="138" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="B138" s="2" t="s">
-        <v>575</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>581</v>
-      </c>
-      <c r="D138" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E138" s="2" t="s">
-        <v>582</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>583</v>
@@ -7052,62 +7067,62 @@
         <v>43</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A139" s="11" t="s">
+    <row r="139" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A139" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="B139" s="11"/>
-      <c r="C139" s="11"/>
-      <c r="D139" s="11"/>
-      <c r="E139" s="11"/>
-      <c r="F139" s="11"/>
-      <c r="G139" s="11"/>
-      <c r="H139" s="11"/>
-      <c r="I139" s="11"/>
-      <c r="J139" s="11"/>
-      <c r="K139" s="11"/>
-    </row>
-    <row r="140" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="2" t="s">
+      <c r="B139" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="C139" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="B140" s="2" t="s">
-        <v>585</v>
-      </c>
-      <c r="C140" s="2" t="s">
+      <c r="D139" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E139" s="2" t="s">
         <v>587</v>
       </c>
-      <c r="D140" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E140" s="2" t="s">
+      <c r="F139" s="2" t="s">
         <v>588</v>
       </c>
-      <c r="F140" s="2" t="s">
+      <c r="G139" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="G140" s="2" t="s">
+      <c r="H139" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I139" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J139" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K139" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="140" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="11" t="s">
         <v>590</v>
       </c>
-      <c r="H140" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I140" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J140" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K140" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="141" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B140" s="11"/>
+      <c r="C140" s="11"/>
+      <c r="D140" s="11"/>
+      <c r="E140" s="11"/>
+      <c r="F140" s="11"/>
+      <c r="G140" s="11"/>
+      <c r="H140" s="11"/>
+      <c r="I140" s="11"/>
+      <c r="J140" s="11"/>
+      <c r="K140" s="11"/>
+    </row>
+    <row r="141" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="2" t="s">
         <v>591</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>592</v>
@@ -7142,13 +7157,13 @@
         <v>596</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>597</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E142" s="2" t="s">
         <v>598</v>
@@ -7172,12 +7187,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="143" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="2" t="s">
         <v>601</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>602</v>
@@ -7207,12 +7222,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="144" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="2" t="s">
         <v>606</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>607</v>
@@ -7242,18 +7257,18 @@
         <v>43</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="145" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="2" t="s">
         <v>611</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>612</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E145" s="2" t="s">
         <v>613</v>
@@ -7277,62 +7292,62 @@
         <v>43</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="11" t="s">
+    <row r="146" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="B146" s="11"/>
-      <c r="C146" s="11"/>
-      <c r="D146" s="11"/>
-      <c r="E146" s="11"/>
-      <c r="F146" s="11"/>
-      <c r="G146" s="11"/>
-      <c r="H146" s="11"/>
-      <c r="I146" s="11"/>
-      <c r="J146" s="11"/>
-      <c r="K146" s="11"/>
-    </row>
-    <row r="147" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="2" t="s">
+      <c r="B146" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="C146" s="2" t="s">
         <v>617</v>
       </c>
-      <c r="B147" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="C147" s="2" t="s">
+      <c r="D146" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E146" s="2" t="s">
         <v>618</v>
       </c>
-      <c r="D147" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E147" s="2" t="s">
+      <c r="F146" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="F147" s="2" t="s">
+      <c r="G146" s="2" t="s">
         <v>620</v>
       </c>
-      <c r="G147" s="2" t="s">
+      <c r="H146" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I146" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J146" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K146" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="147" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="11" t="s">
         <v>621</v>
       </c>
-      <c r="H147" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J147" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K147" s="2" t="s">
-        <v>43</v>
-      </c>
+      <c r="B147" s="11"/>
+      <c r="C147" s="11"/>
+      <c r="D147" s="11"/>
+      <c r="E147" s="11"/>
+      <c r="F147" s="11"/>
+      <c r="G147" s="11"/>
+      <c r="H147" s="11"/>
+      <c r="I147" s="11"/>
+      <c r="J147" s="11"/>
+      <c r="K147" s="11"/>
     </row>
     <row r="148" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="2" t="s">
         <v>622</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>623</v>
@@ -7367,7 +7382,7 @@
         <v>627</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>628</v>
@@ -7397,12 +7412,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="150" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="2" t="s">
         <v>632</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>633</v>
@@ -7432,18 +7447,18 @@
         <v>43</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="151" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A151" s="2" t="s">
         <v>637</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>638</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E151" s="2" t="s">
         <v>639</v>
@@ -7467,62 +7482,62 @@
         <v>43</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="11" t="s">
+    <row r="152" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A152" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="B152" s="11"/>
-      <c r="C152" s="11"/>
-      <c r="D152" s="11"/>
-      <c r="E152" s="11"/>
-      <c r="F152" s="11"/>
-      <c r="G152" s="11"/>
-      <c r="H152" s="11"/>
-      <c r="I152" s="11"/>
-      <c r="J152" s="11"/>
-      <c r="K152" s="11"/>
-    </row>
-    <row r="153" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="2" t="s">
+      <c r="B152" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="C152" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="B153" s="2" t="s">
-        <v>642</v>
-      </c>
-      <c r="C153" s="2" t="s">
+      <c r="D152" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E152" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="D153" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E153" s="2" t="s">
+      <c r="F152" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="F153" s="2" t="s">
+      <c r="G152" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="G153" s="2" t="s">
+      <c r="H152" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I152" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J152" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K152" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="11" t="s">
         <v>647</v>
       </c>
-      <c r="H153" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I153" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J153" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K153" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="154" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B153" s="11"/>
+      <c r="C153" s="11"/>
+      <c r="D153" s="11"/>
+      <c r="E153" s="11"/>
+      <c r="F153" s="11"/>
+      <c r="G153" s="11"/>
+      <c r="H153" s="11"/>
+      <c r="I153" s="11"/>
+      <c r="J153" s="11"/>
+      <c r="K153" s="11"/>
+    </row>
+    <row r="154" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="2" t="s">
         <v>648</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>649</v>
@@ -7552,18 +7567,18 @@
         <v>43</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="155" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="2" t="s">
         <v>653</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="C155" s="2" t="s">
         <v>654</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E155" s="2" t="s">
         <v>655</v>
@@ -7587,18 +7602,18 @@
         <v>43</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="156" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="2" t="s">
         <v>658</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>659</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E156" s="2" t="s">
         <v>660</v>
@@ -7622,27 +7637,27 @@
         <v>43</v>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="157" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="2" t="s">
         <v>663</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="C157" s="2" t="s">
         <v>664</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>660</v>
+        <v>665</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H157" s="12" t="s">
         <v>43</v>
@@ -7659,19 +7674,19 @@
     </row>
     <row r="158" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="B158" s="2" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>57</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>669</v>
+        <v>665</v>
       </c>
       <c r="F158" s="2" t="s">
         <v>670</v>
@@ -7692,68 +7707,68 @@
         <v>43</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A159" s="11" t="s">
+    <row r="159" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A159" s="2" t="s">
         <v>672</v>
       </c>
-      <c r="B159" s="11"/>
-      <c r="C159" s="11"/>
-      <c r="D159" s="11"/>
-      <c r="E159" s="11"/>
-      <c r="F159" s="11"/>
-      <c r="G159" s="11"/>
-      <c r="H159" s="11"/>
-      <c r="I159" s="11"/>
-      <c r="J159" s="11"/>
-      <c r="K159" s="11"/>
-    </row>
-    <row r="160" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="2" t="s">
+      <c r="B159" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="C159" s="2" t="s">
         <v>673</v>
       </c>
-      <c r="B160" s="2" t="s">
-        <v>672</v>
-      </c>
-      <c r="C160" s="2" t="s">
+      <c r="D159" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E159" s="2" t="s">
         <v>674</v>
       </c>
-      <c r="D160" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E160" s="2" t="s">
+      <c r="F159" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="F160" s="2" t="s">
+      <c r="G159" s="2" t="s">
         <v>676</v>
       </c>
-      <c r="G160" s="2" t="s">
+      <c r="H159" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I159" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J159" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K159" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="160" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="11" t="s">
         <v>677</v>
       </c>
-      <c r="H160" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I160" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J160" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K160" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="161" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B160" s="11"/>
+      <c r="C160" s="11"/>
+      <c r="D160" s="11"/>
+      <c r="E160" s="11"/>
+      <c r="F160" s="11"/>
+      <c r="G160" s="11"/>
+      <c r="H160" s="11"/>
+      <c r="I160" s="11"/>
+      <c r="J160" s="11"/>
+      <c r="K160" s="11"/>
+    </row>
+    <row r="161" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="C161" s="2" t="s">
         <v>679</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E161" s="2" t="s">
         <v>680</v>
@@ -7777,18 +7792,18 @@
         <v>43</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="2" t="s">
         <v>683</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="C162" s="2" t="s">
         <v>684</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E162" s="2" t="s">
         <v>685</v>
@@ -7817,13 +7832,13 @@
         <v>688</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="C163" s="2" t="s">
         <v>689</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E163" s="2" t="s">
         <v>690</v>
@@ -7844,6 +7859,41 @@
         <v>43</v>
       </c>
       <c r="K163" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="164" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A164" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="F164" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="G164" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="H164" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I164" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J164" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K164" s="2" t="s">
         <v>43</v>
       </c>
     </row>
@@ -7869,18 +7919,18 @@
     <mergeCell ref="A84:K84"/>
     <mergeCell ref="A89:K89"/>
     <mergeCell ref="A95:K95"/>
-    <mergeCell ref="A102:K102"/>
-    <mergeCell ref="A115:K115"/>
-    <mergeCell ref="A120:K120"/>
-    <mergeCell ref="A123:K123"/>
-    <mergeCell ref="A128:K128"/>
-    <mergeCell ref="A131:K131"/>
-    <mergeCell ref="A133:K133"/>
-    <mergeCell ref="A136:K136"/>
-    <mergeCell ref="A139:K139"/>
-    <mergeCell ref="A146:K146"/>
-    <mergeCell ref="A152:K152"/>
-    <mergeCell ref="A159:K159"/>
+    <mergeCell ref="A103:K103"/>
+    <mergeCell ref="A116:K116"/>
+    <mergeCell ref="A121:K121"/>
+    <mergeCell ref="A124:K124"/>
+    <mergeCell ref="A129:K129"/>
+    <mergeCell ref="A132:K132"/>
+    <mergeCell ref="A134:K134"/>
+    <mergeCell ref="A137:K137"/>
+    <mergeCell ref="A140:K140"/>
+    <mergeCell ref="A147:K147"/>
+    <mergeCell ref="A153:K153"/>
+    <mergeCell ref="A160:K160"/>
   </mergeCells>
   <conditionalFormatting sqref="H3:H400">
     <cfRule type="cellIs" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -7897,7 +7947,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" prompt="Choose Pass / Fail / Partial / N/A / Not run" promptTitle="Result" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H4:H7 H9:H13 H15:H20 H22:H26 H28:H30 H32 H34:H35 H37:H40 H42:H44 H46:H55 H57:H63 H65:H69 H71 H73:H76 H78:H80 H82:H83 H85:H88 H90:H94 H96:H101 H103:H114 H116:H119 H121:H122 H124:H127 H129:H130 H132 H134:H135 H137:H138 H140:H145 H147:H151 H153:H158 H160:H163" type="none">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" prompt="Choose Pass / Fail / Partial / N/A / Not run" promptTitle="Result" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H4:H7 H9:H13 H15:H20 H22:H26 H28:H30 H32 H34:H35 H37:H40 H42:H44 H46:H55 H57:H63 H65:H69 H71 H73:H76 H78:H80 H82:H83 H85:H88 H90:H94 H96:H102 H104:H115 H117:H120 H122:H123 H125:H128 H130:H131 H133 H135:H136 H138:H139 H141:H146 H148:H152 H154:H159 H161:H164" type="none">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -7926,13 +7976,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>693</v>
+        <v>698</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>694</v>
+        <v>699</v>
       </c>
       <c r="B2" s="3"/>
     </row>
@@ -7983,7 +8033,7 @@
     </row>
     <row r="8" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="B8" s="2" t="e">
         <f aca="false">of:=COUNTA('Test Cases'!A3:A400)-COUNTIF('Test Cases'!D3:D400,"")</f>
@@ -7992,7 +8042,7 @@
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>696</v>
+        <v>701</v>
       </c>
       <c r="B9" s="3"/>
     </row>
@@ -8169,7 +8219,7 @@
     </row>
     <row r="29" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="B29" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"RTE editor",'Test Cases'!H3:H400,"Pass")</f>
@@ -8178,7 +8228,7 @@
     </row>
     <row r="30" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
       <c r="B30" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Teams",'Test Cases'!H3:H400,"Pass")</f>
@@ -8187,7 +8237,7 @@
     </row>
     <row r="31" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
       <c r="B31" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"History",'Test Cases'!H3:H400,"Pass")</f>
@@ -8196,7 +8246,7 @@
     </row>
     <row r="32" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="8" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="B32" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Usage",'Test Cases'!H3:H400,"Pass")</f>
@@ -8205,7 +8255,7 @@
     </row>
     <row r="33" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="8" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="B33" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Read-only",'Test Cases'!H3:H400,"Pass")</f>
@@ -8214,7 +8264,7 @@
     </row>
     <row r="34" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="8" t="s">
-        <v>558</v>
+        <v>563</v>
       </c>
       <c r="B34" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Dark mode",'Test Cases'!H3:H400,"Pass")</f>
@@ -8223,7 +8273,7 @@
     </row>
     <row r="35" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="8" t="s">
-        <v>564</v>
+        <v>569</v>
       </c>
       <c r="B35" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Background",'Test Cases'!H3:H400,"Pass")</f>
@@ -8232,7 +8282,7 @@
     </row>
     <row r="36" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>575</v>
+        <v>580</v>
       </c>
       <c r="B36" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Diagnostics",'Test Cases'!H3:H400,"Pass")</f>
@@ -8241,7 +8291,7 @@
     </row>
     <row r="37" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>585</v>
+        <v>590</v>
       </c>
       <c r="B37" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Security",'Test Cases'!H3:H400,"Pass")</f>
@@ -8250,7 +8300,7 @@
     </row>
     <row r="38" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="8" t="s">
-        <v>616</v>
+        <v>621</v>
       </c>
       <c r="B38" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Acknowledgements",'Test Cases'!H3:H400,"Pass")</f>
@@ -8259,7 +8309,7 @@
     </row>
     <row r="39" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="8" t="s">
-        <v>642</v>
+        <v>647</v>
       </c>
       <c r="B39" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Suggestions",'Test Cases'!H3:H400,"Pass")</f>
@@ -8268,7 +8318,7 @@
     </row>
     <row r="40" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
-        <v>672</v>
+        <v>677</v>
       </c>
       <c r="B40" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"UX",'Test Cases'!H3:H400,"Pass")</f>
@@ -8305,88 +8355,88 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>697</v>
+        <v>702</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>698</v>
+        <v>703</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>699</v>
+        <v>704</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>700</v>
+        <v>705</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>701</v>
+        <v>706</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>703</v>
+        <v>708</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>704</v>
+        <v>709</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>705</v>
+        <v>710</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>707</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>708</v>
+        <v>713</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>709</v>
+        <v>714</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>710</v>
+        <v>715</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>711</v>
+        <v>716</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>714</v>
+        <v>719</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>715</v>
+        <v>720</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>716</v>
+        <v>721</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>717</v>
+        <v>722</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Nucleus_Enhancer_Validation_Results_v3.0.0.xlsx
+++ b/docs/Nucleus_Enhancer_Validation_Results_v3.0.0.xlsx
@@ -1296,10 +1296,10 @@
     <t xml:space="preserve">Existing template</t>
   </si>
   <si>
-    <t xml:space="preserve">Change CONTENT, pick minor/major, optionally add a reason, save</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Version bumps; new history snapshot; reason recorded if given (everything except Name is optional — a blank reason/content still saves)</t>
+    <t xml:space="preserve">Change CONTENT, pick minor/major, give reason, save</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Version bumps; reason required; new history snapshot</t>
   </si>
   <si>
     <t xml:space="preserve">ME-03</t>
@@ -5757,7 +5757,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="97" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2" t="s">
         <v>420</v>
       </c>

--- a/docs/Nucleus_Enhancer_Validation_Results_v3.0.0.xlsx
+++ b/docs/Nucleus_Enhancer_Validation_Results_v3.0.0.xlsx
@@ -23,13 +23,13 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1573" uniqueCount="723">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1685" uniqueCount="773">
   <si>
     <t xml:space="preserve">How to use this workbook</t>
   </si>
   <si>
     <t xml:space="preserve">Work through the 'Test Cases' sheet top to bottom. For each row set the Result cell (dropdown: Pass / Fail / Partial / N/A / Not run), and record what you saw in 'Actual / notes', plus your initials and the date.
-There are 131 cases across all feature areas.
+There are 141 cases across all feature areas.
 This is an internal self-check, not a formal/Quality validation. Use the Diagnostics sheet (or docs/Nucleus_Enhancer_Diagnostics.md) to capture detail when something misbehaves.</t>
   </si>
   <si>
@@ -792,6 +792,81 @@
     <t xml:space="preserve">No quick-fill fires; native menu as normal</t>
   </si>
   <si>
+    <t xml:space="preserve">Generated Material</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GM-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exhibit Type from MG22 name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New/Edit Generated Material whose Name contains MG22a or MG22B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Right-click the Exhibit Type picklist</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Auto-selects 'MG22a SFR' / 'MG22B SFR' to match the name (case-insensitive); toast. Option labels are adjustable in content/datetime.js if your org words them differently</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GM-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status QA cycle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generated Material Status field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Right-click the Status field repeatedly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Steps Awaiting QA → QA Complete → Complete Awaiting Return → Returned, one per right-click, toast each step. The Exhibit/Process cycle (Awaiting Start→In Progress→Completed) is unaffected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GM-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Encryption Password from Case Background</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generated Material with an Encryption Password field; the parent case's Case Background holds a password (e.g. 'Password: xxxx', 'Password-xxxx' or 'Password xxxx')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Right-click the Encryption Password field</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fills the password parsed from the case background; toast 'Encryption password set from case background'. 'No password found…' if there is none</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GM-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Password — New from a case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Create a Generated Material via a case's related-list 'New' (URL carries the case in backgroundContext)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Right-click Encryption Password</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resolves the parent case from the URL-encoded backgroundContext and fills the password — works even though the case page isn't directly visible / on another tab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GM-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Password — selectivity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Case Background prose merely mentions the word 'password', not a labelled value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Does NOT grab a stray word — the parser is line-anchored to a 'Password:' / 'Password ' line; leaves the field for manual entry</t>
+  </si>
+  <si>
     <t xml:space="preserve">Templates</t>
   </si>
   <si>
@@ -1068,6 +1143,21 @@
     <t xml:space="preserve">CA-02</t>
   </si>
   <si>
+    <t xml:space="preserve">Tasks split-view team lists</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A Tasks list filtered by team (e.g. Examiner Team Leicester / Manchester) with CY cases that have an alias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open the list and look at the Related To column</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EVERY CY case shows its alias next to the number IMMEDIATELY (e.g. 'CY-26-0734 · Albarola'), with no clicking in/out and no refresh; LP/DC/DP cases with no alias stay blank. (These are legacy-Aura data-recordid links rendered in zero-width force-lookup cells — the alias must still be matched AND visible)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CA-03</t>
+  </si>
+  <si>
     <t xml:space="preserve">Not duplicated</t>
   </si>
   <si>
@@ -1080,7 +1170,7 @@
     <t xml:space="preserve">No extra alias added — the existing Project column is left alone</t>
   </si>
   <si>
-    <t xml:space="preserve">CA-03</t>
+    <t xml:space="preserve">CA-04</t>
   </si>
   <si>
     <t xml:space="preserve">Live toggle</t>
@@ -1212,6 +1302,21 @@
     <t xml:space="preserve">M-02</t>
   </si>
   <si>
+    <t xml:space="preserve">Teams tile count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Templates spanning several teams (DF, eDiscovery, Quality…)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Templates view → read the 'Teams' tile and hover it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Counts the DISTINCT teams the templates cover (multi-team aware) — not '1'; the tooltip explains it counts distinct assigned teams (Global isn't a team)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M-03</t>
+  </si>
+  <si>
     <t xml:space="preserve">List columns &amp; badges</t>
   </si>
   <si>
@@ -1224,7 +1329,7 @@
     <t xml:space="preserve">Headers Doc ID/Name/Version/Status/Category/Scope/Review Due/Actions; status &amp; scope badges correct; own team highlighted</t>
   </si>
   <si>
-    <t xml:space="preserve">M-03</t>
+    <t xml:space="preserve">M-04</t>
   </si>
   <si>
     <t xml:space="preserve">Search &amp; sort</t>
@@ -1239,7 +1344,7 @@
     <t xml:space="preserve">Filters by name/category/team; sort indicators work</t>
   </si>
   <si>
-    <t xml:space="preserve">M-04</t>
+    <t xml:space="preserve">M-05</t>
   </si>
   <si>
     <t xml:space="preserve">Review Due formatting</t>
@@ -1254,7 +1359,7 @@
     <t xml:space="preserve">British DD/MM/YYYY; overdue red, ≤30d amber, with tooltips</t>
   </si>
   <si>
-    <t xml:space="preserve">M-05</t>
+    <t xml:space="preserve">M-06</t>
   </si>
   <si>
     <t xml:space="preserve">Bulk ops</t>
@@ -1683,6 +1788,21 @@
     <t xml:space="preserve">Switches to org-wide; warning banner if writes rejected (object 'In Development')</t>
   </si>
   <si>
+    <t xml:space="preserve">U-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Org-wide records EVERY user</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usage object deployed; standard-user perm set has Create + FLS-Edit on the fields; admin perm set has 'View All'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A STANDARD (non-admin) user inserts a template, then an admin opens Manager → Usage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The standard user's insertion appears in the admin's org-wide log — not just admins' own activity (the previous admin-only write gate was removed). If Salesforce rejects the write the admin sees the banner; logging resumes automatically once perms/Deployment Status are fixed (no rebuild)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Read-only</t>
   </si>
   <si>
@@ -1968,6 +2088,21 @@
     <t xml:space="preserve">At most one browser notification per day; clicking it opens the manager</t>
   </si>
   <si>
+    <t xml:space="preserve">A-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Not-yet-enabled message</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ack object not deployed / In Development, or the user lacks Create on it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Click 'I have read &amp; understood vX'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Friendly, actionable message that acknowledgements aren't switched on yet (a template admin must finish setup) — NOT a raw 'entity type cannot be inserted' error</t>
+  </si>
+  <si>
     <t xml:space="preserve">Suggestions</t>
   </si>
   <si>
@@ -2061,7 +2196,7 @@
     <t xml:space="preserve">UX</t>
   </si>
   <si>
-    <t xml:space="preserve">U-05</t>
+    <t xml:space="preserve">U-06</t>
   </si>
   <si>
     <t xml:space="preserve">Layout &amp; overflow</t>
@@ -2076,7 +2211,7 @@
     <t xml:space="preserve">No clipping/overflow; tooltips for truncation; narrow-width holds</t>
   </si>
   <si>
-    <t xml:space="preserve">U-06</t>
+    <t xml:space="preserve">U-07</t>
   </si>
   <si>
     <t xml:space="preserve">British spelling</t>
@@ -2091,7 +2226,7 @@
     <t xml:space="preserve">British spellings; consistent terminology</t>
   </si>
   <si>
-    <t xml:space="preserve">U-07</t>
+    <t xml:space="preserve">U-08</t>
   </si>
   <si>
     <t xml:space="preserve">Copy accuracy</t>
@@ -2106,7 +2241,7 @@
     <t xml:space="preserve">Wording matches behaviour; no stale strings</t>
   </si>
   <si>
-    <t xml:space="preserve">U-08</t>
+    <t xml:space="preserve">U-09</t>
   </si>
   <si>
     <t xml:space="preserve">Empty states</t>
@@ -2119,6 +2254,21 @@
   </si>
   <si>
     <t xml:space="preserve">Helpful empty-state messages, not blank panels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">U-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toast clears Save/Cancel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trigger a toast inside a modal with a Save/Cancel bar (e.g. right-click a date in 'New Process')</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Watch where the toast appears</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toast sits near the bottom but ABOVE the Save/Cancel buttons — never covering them, whether a floating modal footer or the inline docked footer</t>
   </si>
   <si>
     <t xml:space="preserve">Summary</t>
@@ -2782,7 +2932,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K164"/>
+  <dimension ref="A1:K175"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7.16"/>
@@ -4517,7 +4667,7 @@
       <c r="J56" s="11"/>
       <c r="K56" s="11"/>
     </row>
-    <row r="57" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="2" t="s">
         <v>256</v>
       </c>
@@ -4552,7 +4702,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="2" t="s">
         <v>261</v>
       </c>
@@ -4587,7 +4737,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="59" customFormat="false" ht="77.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2" t="s">
         <v>266</v>
       </c>
@@ -4598,7 +4748,7 @@
         <v>267</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>268</v>
@@ -4622,7 +4772,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2" t="s">
         <v>271</v>
       </c>
@@ -4633,7 +4783,7 @@
         <v>272</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>273</v>
@@ -4657,7 +4807,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="61" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="2" t="s">
         <v>276</v>
       </c>
@@ -4668,127 +4818,127 @@
         <v>277</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>278</v>
       </c>
       <c r="F61" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="G61" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="G61" s="2" t="s">
+      <c r="H61" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J61" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K61" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="11" t="s">
         <v>280</v>
       </c>
-      <c r="H61" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I61" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J61" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K61" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="2" t="s">
+      <c r="B62" s="11"/>
+      <c r="C62" s="11"/>
+      <c r="D62" s="11"/>
+      <c r="E62" s="11"/>
+      <c r="F62" s="11"/>
+      <c r="G62" s="11"/>
+      <c r="H62" s="11"/>
+      <c r="I62" s="11"/>
+      <c r="J62" s="11"/>
+      <c r="K62" s="11"/>
+    </row>
+    <row r="63" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="B62" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C62" s="2" t="s">
+      <c r="B63" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C63" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="D62" s="2" t="s">
+      <c r="D63" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E62" s="2" t="s">
+      <c r="E63" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="F62" s="2" t="s">
+      <c r="F63" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="G62" s="2" t="s">
+      <c r="G63" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="H62" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I62" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J62" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K62" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="63" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="2" t="s">
+      <c r="H63" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I63" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J63" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K63" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B63" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="C63" s="2" t="s">
+      <c r="B64" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C64" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="D63" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E63" s="2" t="s">
+      <c r="D64" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E64" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="F63" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="G63" s="2" t="s">
+      <c r="F64" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="H63" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I63" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J63" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K63" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="11" t="s">
+      <c r="G64" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="B64" s="11"/>
-      <c r="C64" s="11"/>
-      <c r="D64" s="11"/>
-      <c r="E64" s="11"/>
-      <c r="F64" s="11"/>
-      <c r="G64" s="11"/>
-      <c r="H64" s="11"/>
-      <c r="I64" s="11"/>
-      <c r="J64" s="11"/>
-      <c r="K64" s="11"/>
+      <c r="H64" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J64" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K64" s="2" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2" t="s">
         <v>291</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>292</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>293</v>
@@ -4817,13 +4967,13 @@
         <v>296</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>297</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="E66" s="2" t="s">
         <v>298</v>
@@ -4847,27 +4997,27 @@
         <v>43</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="2" t="s">
         <v>301</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>302</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>303</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H67" s="12" t="s">
         <v>43</v>
@@ -4882,27 +5032,27 @@
         <v>43</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="68" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="H68" s="12" t="s">
         <v>43</v>
@@ -4919,25 +5069,25 @@
     </row>
     <row r="69" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>57</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F69" s="2" t="s">
         <v>299</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="H69" s="12" t="s">
         <v>43</v>
@@ -4954,7 +5104,7 @@
     </row>
     <row r="70" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="11" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B70" s="11"/>
       <c r="C70" s="11"/>
@@ -4967,147 +5117,167 @@
       <c r="J70" s="11"/>
       <c r="K70" s="11"/>
     </row>
-    <row r="71" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C71" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="H71" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J71" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K71" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="B72" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="D71" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="G71" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="H71" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I71" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J71" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K71" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="11" t="s">
-        <v>319</v>
-      </c>
-      <c r="B72" s="11"/>
-      <c r="C72" s="11"/>
-      <c r="D72" s="11"/>
-      <c r="E72" s="11"/>
-      <c r="F72" s="11"/>
-      <c r="G72" s="11"/>
-      <c r="H72" s="11"/>
-      <c r="I72" s="11"/>
-      <c r="J72" s="11"/>
-      <c r="K72" s="11"/>
+      <c r="C72" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="H72" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J72" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K72" s="2" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="73" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="2" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G73" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="H73" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J73" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K73" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="F74" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="H73" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I73" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J73" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K73" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="D74" s="2" t="s">
+      <c r="G74" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="H74" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J74" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K74" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="D75" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E74" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="G74" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="H74" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I74" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J74" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K74" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="E75" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="H75" s="12" t="s">
         <v>43</v>
@@ -5122,282 +5292,282 @@
         <v>43</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="D76" s="2" t="s">
+    <row r="76" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="11" t="s">
+        <v>338</v>
+      </c>
+      <c r="B76" s="11"/>
+      <c r="C76" s="11"/>
+      <c r="D76" s="11"/>
+      <c r="E76" s="11"/>
+      <c r="F76" s="11"/>
+      <c r="G76" s="11"/>
+      <c r="H76" s="11"/>
+      <c r="I76" s="11"/>
+      <c r="J76" s="11"/>
+      <c r="K76" s="11"/>
+    </row>
+    <row r="77" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="D77" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E76" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="G76" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="H76" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I76" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J76" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K76" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="11" t="s">
-        <v>340</v>
-      </c>
-      <c r="B77" s="11"/>
-      <c r="C77" s="11"/>
-      <c r="D77" s="11"/>
-      <c r="E77" s="11"/>
-      <c r="F77" s="11"/>
-      <c r="G77" s="11"/>
-      <c r="H77" s="11"/>
-      <c r="I77" s="11"/>
-      <c r="J77" s="11"/>
-      <c r="K77" s="11"/>
-    </row>
-    <row r="78" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="2" t="s">
+      <c r="E77" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="B78" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="C78" s="2" t="s">
+      <c r="F77" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="D78" s="2" t="s">
+      <c r="G77" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="H77" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J77" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K77" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="11" t="s">
+        <v>344</v>
+      </c>
+      <c r="B78" s="11"/>
+      <c r="C78" s="11"/>
+      <c r="D78" s="11"/>
+      <c r="E78" s="11"/>
+      <c r="F78" s="11"/>
+      <c r="G78" s="11"/>
+      <c r="H78" s="11"/>
+      <c r="I78" s="11"/>
+      <c r="J78" s="11"/>
+      <c r="K78" s="11"/>
+    </row>
+    <row r="79" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D79" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E78" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="F78" s="2" t="s">
+      <c r="E79" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="H79" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K79" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B80" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="G78" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="H78" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I78" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J78" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K78" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="G79" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="H79" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I79" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J79" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K79" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="2" t="s">
+      <c r="C80" s="2" t="s">
         <v>351</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>352</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>57</v>
       </c>
       <c r="E80" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="F80" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="F80" s="2" t="s">
+      <c r="G80" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="G80" s="2" t="s">
+      <c r="H80" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J80" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="H80" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I80" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K80" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="11" t="s">
+      <c r="B81" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="C81" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="B81" s="11"/>
-      <c r="C81" s="11"/>
-      <c r="D81" s="11"/>
-      <c r="E81" s="11"/>
-      <c r="F81" s="11"/>
-      <c r="G81" s="11"/>
-      <c r="H81" s="11"/>
-      <c r="I81" s="11"/>
-      <c r="J81" s="11"/>
-      <c r="K81" s="11"/>
-    </row>
-    <row r="82" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D81" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="H81" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I81" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J81" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K81" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>356</v>
+        <v>344</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="D82" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="H82" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J82" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K82" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="11" t="s">
+        <v>365</v>
+      </c>
+      <c r="B83" s="11"/>
+      <c r="C83" s="11"/>
+      <c r="D83" s="11"/>
+      <c r="E83" s="11"/>
+      <c r="F83" s="11"/>
+      <c r="G83" s="11"/>
+      <c r="H83" s="11"/>
+      <c r="I83" s="11"/>
+      <c r="J83" s="11"/>
+      <c r="K83" s="11"/>
+    </row>
+    <row r="84" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="D84" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E82" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="F82" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="G82" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="H82" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I82" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J82" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K82" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="F83" s="2" t="s">
+      <c r="E84" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="H84" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J84" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K84" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="88.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="B85" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="G83" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="H83" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I83" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J83" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K83" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="11" t="s">
-        <v>367</v>
-      </c>
-      <c r="B84" s="11"/>
-      <c r="C84" s="11"/>
-      <c r="D84" s="11"/>
-      <c r="E84" s="11"/>
-      <c r="F84" s="11"/>
-      <c r="G84" s="11"/>
-      <c r="H84" s="11"/>
-      <c r="I84" s="11"/>
-      <c r="J84" s="11"/>
-      <c r="K84" s="11"/>
-    </row>
-    <row r="85" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>367</v>
-      </c>
       <c r="C85" s="2" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>39</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="H85" s="12" t="s">
         <v>43</v>
@@ -5412,147 +5582,147 @@
         <v>43</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="86" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="2" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="D86" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="H86" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J86" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K86" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="H87" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J87" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K87" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="11" t="s">
+        <v>386</v>
+      </c>
+      <c r="B88" s="11"/>
+      <c r="C88" s="11"/>
+      <c r="D88" s="11"/>
+      <c r="E88" s="11"/>
+      <c r="F88" s="11"/>
+      <c r="G88" s="11"/>
+      <c r="H88" s="11"/>
+      <c r="I88" s="11"/>
+      <c r="J88" s="11"/>
+      <c r="K88" s="11"/>
+    </row>
+    <row r="89" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="D89" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E86" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="F86" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="G86" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="H86" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I86" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J86" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K86" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E87" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="F87" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="G87" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="H87" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I87" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J87" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K87" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E88" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="F88" s="2" t="s">
+      <c r="E89" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="H89" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J89" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K89" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B90" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="G88" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="H88" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I88" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J88" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K88" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="11" t="s">
-        <v>388</v>
-      </c>
-      <c r="B89" s="11"/>
-      <c r="C89" s="11"/>
-      <c r="D89" s="11"/>
-      <c r="E89" s="11"/>
-      <c r="F89" s="11"/>
-      <c r="G89" s="11"/>
-      <c r="H89" s="11"/>
-      <c r="I89" s="11"/>
-      <c r="J89" s="11"/>
-      <c r="K89" s="11"/>
-    </row>
-    <row r="90" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>388</v>
-      </c>
       <c r="C90" s="2" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="H90" s="12" t="s">
         <v>43</v>
@@ -5567,62 +5737,42 @@
         <v>43</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="2" t="s">
-        <v>394</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E91" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="F91" s="2" t="s">
+    <row r="91" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="11" t="s">
         <v>397</v>
       </c>
-      <c r="G91" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="H91" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I91" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J91" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K91" s="2" t="s">
-        <v>43</v>
-      </c>
+      <c r="B91" s="11"/>
+      <c r="C91" s="11"/>
+      <c r="D91" s="11"/>
+      <c r="E91" s="11"/>
+      <c r="F91" s="11"/>
+      <c r="G91" s="11"/>
+      <c r="H91" s="11"/>
+      <c r="I91" s="11"/>
+      <c r="J91" s="11"/>
+      <c r="K91" s="11"/>
     </row>
     <row r="92" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C92" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="B92" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C92" s="2" t="s">
+      <c r="D92" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E92" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="D92" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E92" s="2" t="s">
+      <c r="F92" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="F92" s="2" t="s">
+      <c r="G92" s="2" t="s">
         <v>402</v>
-      </c>
-      <c r="G92" s="2" t="s">
-        <v>403</v>
       </c>
       <c r="H92" s="12" t="s">
         <v>43</v>
@@ -5639,174 +5789,174 @@
     </row>
     <row r="93" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C93" s="2" t="s">
         <v>404</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>405</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E93" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="F93" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="F93" s="2" t="s">
+      <c r="G93" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="G93" s="2" t="s">
+      <c r="H93" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I93" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J93" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K93" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="H93" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I93" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J93" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K93" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="94" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="2" t="s">
+      <c r="B94" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C94" s="2" t="s">
         <v>409</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>410</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E94" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="F94" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="F94" s="2" t="s">
+      <c r="G94" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="G94" s="2" t="s">
+      <c r="H94" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J94" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K94" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="H94" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I94" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J94" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K94" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="95" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="11" t="s">
+      <c r="B95" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C95" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="B95" s="11"/>
-      <c r="C95" s="11"/>
-      <c r="D95" s="11"/>
-      <c r="E95" s="11"/>
-      <c r="F95" s="11"/>
-      <c r="G95" s="11"/>
-      <c r="H95" s="11"/>
-      <c r="I95" s="11"/>
-      <c r="J95" s="11"/>
-      <c r="K95" s="11"/>
-    </row>
-    <row r="96" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="2" t="s">
+      <c r="D95" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E95" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="B96" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="C96" s="2" t="s">
+      <c r="F95" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="D96" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E96" s="2" t="s">
+      <c r="G95" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="F96" s="2" t="s">
+      <c r="H95" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J95" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K95" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="11" t="s">
         <v>418</v>
       </c>
-      <c r="G96" s="2" t="s">
+      <c r="B96" s="11"/>
+      <c r="C96" s="11"/>
+      <c r="D96" s="11"/>
+      <c r="E96" s="11"/>
+      <c r="F96" s="11"/>
+      <c r="G96" s="11"/>
+      <c r="H96" s="11"/>
+      <c r="I96" s="11"/>
+      <c r="J96" s="11"/>
+      <c r="K96" s="11"/>
+    </row>
+    <row r="97" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="H96" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I96" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J96" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K96" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="97" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="2" t="s">
+      <c r="B97" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C97" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="B97" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="C97" s="2" t="s">
+      <c r="D97" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E97" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="D97" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E97" s="2" t="s">
+      <c r="F97" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="F97" s="2" t="s">
+      <c r="G97" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="G97" s="2" t="s">
+      <c r="H97" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J97" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K97" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="H97" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I97" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J97" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K97" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="98" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="2" t="s">
+      <c r="B98" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="C98" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="B98" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="C98" s="2" t="s">
+      <c r="D98" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E98" s="2" t="s">
         <v>426</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E98" s="2" t="s">
-        <v>422</v>
       </c>
       <c r="F98" s="2" t="s">
         <v>427</v>
@@ -5827,12 +5977,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="99" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="2" t="s">
         <v>429</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>430</v>
@@ -5841,13 +5991,13 @@
         <v>51</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H99" s="12" t="s">
         <v>43</v>
@@ -5864,25 +6014,25 @@
     </row>
     <row r="100" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H100" s="12" t="s">
         <v>43</v>
@@ -5897,27 +6047,27 @@
         <v>43</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H101" s="12" t="s">
         <v>43</v>
@@ -5932,27 +6082,27 @@
         <v>43</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H102" s="12" t="s">
         <v>43</v>
@@ -5969,7 +6119,7 @@
     </row>
     <row r="103" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="11" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B103" s="11"/>
       <c r="C103" s="11"/>
@@ -5982,27 +6132,27 @@
       <c r="J103" s="11"/>
       <c r="K103" s="11"/>
     </row>
-    <row r="104" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="104" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="B104" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="B104" s="2" t="s">
-        <v>448</v>
-      </c>
       <c r="C104" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H104" s="12" t="s">
         <v>43</v>
@@ -6019,25 +6169,25 @@
     </row>
     <row r="105" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H105" s="12" t="s">
         <v>43</v>
@@ -6054,25 +6204,25 @@
     </row>
     <row r="106" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H106" s="12" t="s">
         <v>43</v>
@@ -6087,27 +6237,27 @@
         <v>43</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H107" s="12" t="s">
         <v>43</v>
@@ -6124,25 +6274,25 @@
     </row>
     <row r="108" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>456</v>
+        <v>470</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="H108" s="12" t="s">
         <v>43</v>
@@ -6157,27 +6307,27 @@
         <v>43</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="109" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>456</v>
+        <v>475</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="H109" s="12" t="s">
         <v>43</v>
@@ -6192,27 +6342,27 @@
         <v>43</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="110" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="2" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>456</v>
+        <v>480</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="H110" s="12" t="s">
         <v>43</v>
@@ -6227,62 +6377,42 @@
         <v>43</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="B111" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="C111" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="D111" s="2" t="s">
+    <row r="111" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="11" t="s">
+        <v>483</v>
+      </c>
+      <c r="B111" s="11"/>
+      <c r="C111" s="11"/>
+      <c r="D111" s="11"/>
+      <c r="E111" s="11"/>
+      <c r="F111" s="11"/>
+      <c r="G111" s="11"/>
+      <c r="H111" s="11"/>
+      <c r="I111" s="11"/>
+      <c r="J111" s="11"/>
+      <c r="K111" s="11"/>
+    </row>
+    <row r="112" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="D112" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E111" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="F111" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="G111" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="H111" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I111" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J111" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K111" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="112" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="B112" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="C112" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="D112" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="E112" s="2" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H112" s="12" t="s">
         <v>43</v>
@@ -6299,60 +6429,60 @@
     </row>
     <row r="113" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>448</v>
+        <v>483</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F113" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="G113" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="H113" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I113" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J113" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K113" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E114" s="2" t="s">
         <v>491</v>
       </c>
-      <c r="G113" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="H113" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I113" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J113" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K113" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="B114" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="C114" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="D114" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E114" s="2" t="s">
-        <v>456</v>
-      </c>
       <c r="F114" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H114" s="12" t="s">
         <v>43</v>
@@ -6367,21 +6497,21 @@
         <v>43</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="115" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="2" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>448</v>
+        <v>483</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>500</v>
@@ -6402,42 +6532,62 @@
         <v>43</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A116" s="11" t="s">
+    <row r="116" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="B116" s="11"/>
-      <c r="C116" s="11"/>
-      <c r="D116" s="11"/>
-      <c r="E116" s="11"/>
-      <c r="F116" s="11"/>
-      <c r="G116" s="11"/>
-      <c r="H116" s="11"/>
-      <c r="I116" s="11"/>
-      <c r="J116" s="11"/>
-      <c r="K116" s="11"/>
-    </row>
-    <row r="117" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B116" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="G116" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="H116" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I116" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J116" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K116" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="2" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>502</v>
+        <v>483</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>505</v>
+        <v>491</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="H117" s="12" t="s">
         <v>43</v>
@@ -6452,27 +6602,27 @@
         <v>43</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="2" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>502</v>
+        <v>483</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>510</v>
+        <v>491</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>506</v>
+        <v>512</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="H118" s="12" t="s">
         <v>43</v>
@@ -6489,25 +6639,25 @@
     </row>
     <row r="119" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="2" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>502</v>
+        <v>483</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>514</v>
+        <v>491</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H119" s="12" t="s">
         <v>43</v>
@@ -6524,75 +6674,95 @@
     </row>
     <row r="120" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="2" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>502</v>
+        <v>483</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D120" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="H120" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I120" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J120" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K120" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="D121" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E120" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="F120" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="G120" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="H120" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I120" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J120" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K120" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="121" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A121" s="11" t="s">
-        <v>522</v>
-      </c>
-      <c r="B121" s="11"/>
-      <c r="C121" s="11"/>
-      <c r="D121" s="11"/>
-      <c r="E121" s="11"/>
-      <c r="F121" s="11"/>
-      <c r="G121" s="11"/>
-      <c r="H121" s="11"/>
-      <c r="I121" s="11"/>
-      <c r="J121" s="11"/>
-      <c r="K121" s="11"/>
+      <c r="E121" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="H121" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I121" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J121" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K121" s="2" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="122" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="2" t="s">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>522</v>
+        <v>483</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>524</v>
+        <v>529</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>435</v>
+        <v>491</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>525</v>
+        <v>530</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="H122" s="12" t="s">
         <v>43</v>
@@ -6609,25 +6779,25 @@
     </row>
     <row r="123" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="2" t="s">
-        <v>527</v>
+        <v>532</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>522</v>
+        <v>483</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>528</v>
+        <v>533</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>529</v>
+        <v>534</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>528</v>
+        <v>535</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="H123" s="12" t="s">
         <v>43</v>
@@ -6644,7 +6814,7 @@
     </row>
     <row r="124" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="11" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="B124" s="11"/>
       <c r="C124" s="11"/>
@@ -6657,27 +6827,27 @@
       <c r="J124" s="11"/>
       <c r="K124" s="11"/>
     </row>
-    <row r="125" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="2" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="H125" s="12" t="s">
         <v>43</v>
@@ -6694,25 +6864,25 @@
     </row>
     <row r="126" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="B126" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="B126" s="2" t="s">
-        <v>531</v>
-      </c>
       <c r="C126" s="2" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>541</v>
+        <v>546</v>
       </c>
       <c r="H126" s="12" t="s">
         <v>43</v>
@@ -6729,25 +6899,25 @@
     </row>
     <row r="127" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="2" t="s">
-        <v>542</v>
+        <v>547</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>543</v>
+        <v>548</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>544</v>
+        <v>549</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>545</v>
+        <v>550</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>546</v>
+        <v>551</v>
       </c>
       <c r="H127" s="12" t="s">
         <v>43</v>
@@ -6764,25 +6934,25 @@
     </row>
     <row r="128" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="2" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="H128" s="12" t="s">
         <v>43</v>
@@ -6799,7 +6969,7 @@
     </row>
     <row r="129" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="11" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="B129" s="11"/>
       <c r="C129" s="11"/>
@@ -6812,27 +6982,27 @@
       <c r="J129" s="11"/>
       <c r="K129" s="11"/>
     </row>
-    <row r="130" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="2" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>554</v>
+        <v>559</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>555</v>
+        <v>470</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="H130" s="12" t="s">
         <v>43</v>
@@ -6849,25 +7019,25 @@
     </row>
     <row r="131" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="2" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="H131" s="12" t="s">
         <v>43</v>
@@ -6884,7 +7054,7 @@
     </row>
     <row r="132" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="11" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="B132" s="11"/>
       <c r="C132" s="11"/>
@@ -6897,77 +7067,97 @@
       <c r="J132" s="11"/>
       <c r="K132" s="11"/>
     </row>
-    <row r="133" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="2" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E133" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="H133" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I133" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J133" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K133" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="B134" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="F133" s="2" t="s">
-        <v>567</v>
-      </c>
-      <c r="G133" s="2" t="s">
-        <v>568</v>
-      </c>
-      <c r="H133" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I133" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J133" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K133" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="134" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="11" t="s">
-        <v>569</v>
-      </c>
-      <c r="B134" s="11"/>
-      <c r="C134" s="11"/>
-      <c r="D134" s="11"/>
-      <c r="E134" s="11"/>
-      <c r="F134" s="11"/>
-      <c r="G134" s="11"/>
-      <c r="H134" s="11"/>
-      <c r="I134" s="11"/>
-      <c r="J134" s="11"/>
-      <c r="K134" s="11"/>
+      <c r="C134" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="H134" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I134" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J134" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K134" s="2" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="135" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="2" t="s">
-        <v>570</v>
+        <v>577</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>571</v>
+        <v>578</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>57</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>574</v>
+        <v>581</v>
       </c>
       <c r="H135" s="12" t="s">
         <v>43</v>
@@ -6984,25 +7174,25 @@
     </row>
     <row r="136" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="2" t="s">
-        <v>575</v>
+        <v>582</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>569</v>
+        <v>566</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>576</v>
+        <v>583</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>57</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>577</v>
+        <v>584</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>578</v>
+        <v>585</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>579</v>
+        <v>586</v>
       </c>
       <c r="H136" s="12" t="s">
         <v>43</v>
@@ -7017,77 +7207,77 @@
         <v>43</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="11" t="s">
-        <v>580</v>
-      </c>
-      <c r="B137" s="11"/>
-      <c r="C137" s="11"/>
-      <c r="D137" s="11"/>
-      <c r="E137" s="11"/>
-      <c r="F137" s="11"/>
-      <c r="G137" s="11"/>
-      <c r="H137" s="11"/>
-      <c r="I137" s="11"/>
-      <c r="J137" s="11"/>
-      <c r="K137" s="11"/>
-    </row>
-    <row r="138" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="2" t="s">
-        <v>581</v>
-      </c>
-      <c r="B138" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="C138" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="D138" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E138" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="F138" s="2" t="s">
-        <v>583</v>
-      </c>
-      <c r="G138" s="2" t="s">
-        <v>584</v>
-      </c>
-      <c r="H138" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I138" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J138" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K138" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="139" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="137" customFormat="false" ht="88.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="2" t="s">
+        <v>587</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="G137" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="H137" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I137" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J137" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K137" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="138" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A138" s="11" t="s">
+        <v>592</v>
+      </c>
+      <c r="B138" s="11"/>
+      <c r="C138" s="11"/>
+      <c r="D138" s="11"/>
+      <c r="E138" s="11"/>
+      <c r="F138" s="11"/>
+      <c r="G138" s="11"/>
+      <c r="H138" s="11"/>
+      <c r="I138" s="11"/>
+      <c r="J138" s="11"/>
+      <c r="K138" s="11"/>
+    </row>
+    <row r="139" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="2" t="s">
-        <v>585</v>
+        <v>593</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>586</v>
+        <v>594</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>587</v>
+        <v>595</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>588</v>
+        <v>596</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>589</v>
+        <v>597</v>
       </c>
       <c r="H139" s="12" t="s">
         <v>43</v>
@@ -7102,77 +7292,77 @@
         <v>43</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A140" s="11" t="s">
-        <v>590</v>
-      </c>
-      <c r="B140" s="11"/>
-      <c r="C140" s="11"/>
-      <c r="D140" s="11"/>
-      <c r="E140" s="11"/>
-      <c r="F140" s="11"/>
-      <c r="G140" s="11"/>
-      <c r="H140" s="11"/>
-      <c r="I140" s="11"/>
-      <c r="J140" s="11"/>
-      <c r="K140" s="11"/>
-    </row>
-    <row r="141" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A141" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="B141" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="C141" s="2" t="s">
+    <row r="140" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A140" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="B140" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="D141" s="2" t="s">
+      <c r="C140" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="D140" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E141" s="2" t="s">
-        <v>593</v>
-      </c>
-      <c r="F141" s="2" t="s">
-        <v>594</v>
-      </c>
-      <c r="G141" s="2" t="s">
-        <v>595</v>
-      </c>
-      <c r="H141" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I141" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J141" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K141" s="2" t="s">
-        <v>43</v>
-      </c>
+      <c r="E140" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="F140" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="G140" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="H140" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I140" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J140" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K140" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="141" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A141" s="11" t="s">
+        <v>603</v>
+      </c>
+      <c r="B141" s="11"/>
+      <c r="C141" s="11"/>
+      <c r="D141" s="11"/>
+      <c r="E141" s="11"/>
+      <c r="F141" s="11"/>
+      <c r="G141" s="11"/>
+      <c r="H141" s="11"/>
+      <c r="I141" s="11"/>
+      <c r="J141" s="11"/>
+      <c r="K141" s="11"/>
     </row>
     <row r="142" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="2" t="s">
-        <v>596</v>
+        <v>604</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>590</v>
+        <v>603</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>597</v>
+        <v>605</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>598</v>
+        <v>606</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>599</v>
+        <v>607</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>600</v>
+        <v>608</v>
       </c>
       <c r="H142" s="12" t="s">
         <v>43</v>
@@ -7187,182 +7377,162 @@
         <v>43</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="B143" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="C143" s="2" t="s">
-        <v>602</v>
-      </c>
-      <c r="D143" s="2" t="s">
+    <row r="143" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="11" t="s">
+        <v>609</v>
+      </c>
+      <c r="B143" s="11"/>
+      <c r="C143" s="11"/>
+      <c r="D143" s="11"/>
+      <c r="E143" s="11"/>
+      <c r="F143" s="11"/>
+      <c r="G143" s="11"/>
+      <c r="H143" s="11"/>
+      <c r="I143" s="11"/>
+      <c r="J143" s="11"/>
+      <c r="K143" s="11"/>
+    </row>
+    <row r="144" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A144" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="F144" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="G144" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="H144" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I144" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J144" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K144" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="145" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A145" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="F145" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="G145" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="H145" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J145" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K145" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="146" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A146" s="11" t="s">
+        <v>620</v>
+      </c>
+      <c r="B146" s="11"/>
+      <c r="C146" s="11"/>
+      <c r="D146" s="11"/>
+      <c r="E146" s="11"/>
+      <c r="F146" s="11"/>
+      <c r="G146" s="11"/>
+      <c r="H146" s="11"/>
+      <c r="I146" s="11"/>
+      <c r="J146" s="11"/>
+      <c r="K146" s="11"/>
+    </row>
+    <row r="147" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A147" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="D147" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E143" s="2" t="s">
-        <v>603</v>
-      </c>
-      <c r="F143" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="G143" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="H143" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I143" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J143" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K143" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="144" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A144" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="B144" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="C144" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="D144" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E144" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="F144" s="2" t="s">
-        <v>609</v>
-      </c>
-      <c r="G144" s="2" t="s">
-        <v>610</v>
-      </c>
-      <c r="H144" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I144" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J144" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K144" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="145" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A145" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="B145" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="C145" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="D145" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E145" s="2" t="s">
-        <v>613</v>
-      </c>
-      <c r="F145" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="G145" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="H145" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I145" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J145" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K145" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="146" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A146" s="2" t="s">
-        <v>616</v>
-      </c>
-      <c r="B146" s="2" t="s">
-        <v>590</v>
-      </c>
-      <c r="C146" s="2" t="s">
-        <v>617</v>
-      </c>
-      <c r="D146" s="2" t="s">
+      <c r="E147" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F147" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="G147" s="2" t="s">
+        <v>624</v>
+      </c>
+      <c r="H147" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J147" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K147" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="148" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A148" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="D148" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E146" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="F146" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="G146" s="2" t="s">
-        <v>620</v>
-      </c>
-      <c r="H146" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I146" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J146" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K146" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="147" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A147" s="11" t="s">
-        <v>621</v>
-      </c>
-      <c r="B147" s="11"/>
-      <c r="C147" s="11"/>
-      <c r="D147" s="11"/>
-      <c r="E147" s="11"/>
-      <c r="F147" s="11"/>
-      <c r="G147" s="11"/>
-      <c r="H147" s="11"/>
-      <c r="I147" s="11"/>
-      <c r="J147" s="11"/>
-      <c r="K147" s="11"/>
-    </row>
-    <row r="148" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A148" s="2" t="s">
-        <v>622</v>
-      </c>
-      <c r="B148" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>623</v>
-      </c>
-      <c r="D148" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="E148" s="2" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="H148" s="12" t="s">
         <v>43</v>
@@ -7377,97 +7547,77 @@
         <v>43</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A149" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="B149" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="C149" s="2" t="s">
-        <v>628</v>
-      </c>
-      <c r="D149" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E149" s="2" t="s">
-        <v>629</v>
-      </c>
-      <c r="F149" s="2" t="s">
+    <row r="149" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A149" s="11" t="s">
         <v>630</v>
       </c>
-      <c r="G149" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="H149" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I149" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J149" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K149" s="2" t="s">
-        <v>43</v>
-      </c>
+      <c r="B149" s="11"/>
+      <c r="C149" s="11"/>
+      <c r="D149" s="11"/>
+      <c r="E149" s="11"/>
+      <c r="F149" s="11"/>
+      <c r="G149" s="11"/>
+      <c r="H149" s="11"/>
+      <c r="I149" s="11"/>
+      <c r="J149" s="11"/>
+      <c r="K149" s="11"/>
     </row>
     <row r="150" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="C150" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="B150" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="C150" s="2" t="s">
+      <c r="D150" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E150" s="2" t="s">
         <v>633</v>
       </c>
-      <c r="D150" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E150" s="2" t="s">
+      <c r="F150" s="2" t="s">
         <v>634</v>
       </c>
-      <c r="F150" s="2" t="s">
+      <c r="G150" s="2" t="s">
         <v>635</v>
       </c>
-      <c r="G150" s="2" t="s">
+      <c r="H150" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I150" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J150" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K150" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="151" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A151" s="2" t="s">
         <v>636</v>
       </c>
-      <c r="H150" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I150" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J150" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K150" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="151" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="2" t="s">
+      <c r="B151" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="C151" s="2" t="s">
         <v>637</v>
       </c>
-      <c r="B151" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="C151" s="2" t="s">
+      <c r="D151" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E151" s="2" t="s">
         <v>638</v>
       </c>
-      <c r="D151" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E151" s="2" t="s">
+      <c r="F151" s="2" t="s">
         <v>639</v>
       </c>
-      <c r="F151" s="2" t="s">
+      <c r="G151" s="2" t="s">
         <v>640</v>
-      </c>
-      <c r="G151" s="2" t="s">
-        <v>641</v>
       </c>
       <c r="H151" s="12" t="s">
         <v>43</v>
@@ -7484,75 +7634,95 @@
     </row>
     <row r="152" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A152" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="C152" s="2" t="s">
         <v>642</v>
       </c>
-      <c r="B152" s="2" t="s">
-        <v>621</v>
-      </c>
-      <c r="C152" s="2" t="s">
+      <c r="D152" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E152" s="2" t="s">
         <v>643</v>
       </c>
-      <c r="D152" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E152" s="2" t="s">
+      <c r="F152" s="2" t="s">
         <v>644</v>
       </c>
-      <c r="F152" s="2" t="s">
+      <c r="G152" s="2" t="s">
         <v>645</v>
       </c>
-      <c r="G152" s="2" t="s">
+      <c r="H152" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I152" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J152" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K152" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="153" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A153" s="2" t="s">
         <v>646</v>
       </c>
-      <c r="H152" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I152" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J152" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K152" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="153" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A153" s="11" t="s">
+      <c r="B153" s="2" t="s">
+        <v>630</v>
+      </c>
+      <c r="C153" s="2" t="s">
         <v>647</v>
       </c>
-      <c r="B153" s="11"/>
-      <c r="C153" s="11"/>
-      <c r="D153" s="11"/>
-      <c r="E153" s="11"/>
-      <c r="F153" s="11"/>
-      <c r="G153" s="11"/>
-      <c r="H153" s="11"/>
-      <c r="I153" s="11"/>
-      <c r="J153" s="11"/>
-      <c r="K153" s="11"/>
-    </row>
-    <row r="154" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D153" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="F153" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="G153" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="H153" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I153" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J153" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K153" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="154" customFormat="false" ht="67.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A154" s="2" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>647</v>
+        <v>630</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="H154" s="12" t="s">
         <v>43</v>
@@ -7569,25 +7739,25 @@
     </row>
     <row r="155" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="2" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>647</v>
+        <v>630</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="H155" s="12" t="s">
         <v>43</v>
@@ -7602,91 +7772,71 @@
         <v>43</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A156" s="2" t="s">
-        <v>658</v>
-      </c>
-      <c r="B156" s="2" t="s">
-        <v>647</v>
-      </c>
-      <c r="C156" s="2" t="s">
-        <v>659</v>
-      </c>
-      <c r="D156" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E156" s="2" t="s">
-        <v>660</v>
-      </c>
-      <c r="F156" s="2" t="s">
+    <row r="156" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A156" s="11" t="s">
         <v>661</v>
       </c>
-      <c r="G156" s="2" t="s">
+      <c r="B156" s="11"/>
+      <c r="C156" s="11"/>
+      <c r="D156" s="11"/>
+      <c r="E156" s="11"/>
+      <c r="F156" s="11"/>
+      <c r="G156" s="11"/>
+      <c r="H156" s="11"/>
+      <c r="I156" s="11"/>
+      <c r="J156" s="11"/>
+      <c r="K156" s="11"/>
+    </row>
+    <row r="157" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A157" s="2" t="s">
         <v>662</v>
       </c>
-      <c r="H156" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I156" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J156" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K156" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="157" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A157" s="2" t="s">
+      <c r="B157" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="C157" s="2" t="s">
         <v>663</v>
-      </c>
-      <c r="B157" s="2" t="s">
-        <v>647</v>
-      </c>
-      <c r="C157" s="2" t="s">
-        <v>664</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>51</v>
       </c>
       <c r="E157" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="F157" s="2" t="s">
         <v>665</v>
       </c>
-      <c r="F157" s="2" t="s">
+      <c r="G157" s="2" t="s">
         <v>666</v>
       </c>
-      <c r="G157" s="2" t="s">
+      <c r="H157" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I157" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J157" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K157" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="158" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A158" s="2" t="s">
         <v>667</v>
       </c>
-      <c r="H157" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I157" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J157" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K157" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="158" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A158" s="2" t="s">
+      <c r="B158" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="C158" s="2" t="s">
         <v>668</v>
       </c>
-      <c r="B158" s="2" t="s">
-        <v>647</v>
-      </c>
-      <c r="C158" s="2" t="s">
+      <c r="D158" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E158" s="2" t="s">
         <v>669</v>
-      </c>
-      <c r="D158" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E158" s="2" t="s">
-        <v>665</v>
       </c>
       <c r="F158" s="2" t="s">
         <v>670</v>
@@ -7707,18 +7857,18 @@
         <v>43</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="159" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="2" t="s">
         <v>672</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>647</v>
+        <v>661</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>673</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E159" s="2" t="s">
         <v>674</v>
@@ -7742,42 +7892,62 @@
         <v>43</v>
       </c>
     </row>
-    <row r="160" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A160" s="11" t="s">
+    <row r="160" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A160" s="2" t="s">
         <v>677</v>
       </c>
-      <c r="B160" s="11"/>
-      <c r="C160" s="11"/>
-      <c r="D160" s="11"/>
-      <c r="E160" s="11"/>
-      <c r="F160" s="11"/>
-      <c r="G160" s="11"/>
-      <c r="H160" s="11"/>
-      <c r="I160" s="11"/>
-      <c r="J160" s="11"/>
-      <c r="K160" s="11"/>
+      <c r="B160" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="F160" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="G160" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="H160" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I160" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J160" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K160" s="2" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="161" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="2" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>677</v>
+        <v>661</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="H161" s="12" t="s">
         <v>43</v>
@@ -7792,27 +7962,27 @@
         <v>43</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="162" customFormat="false" ht="56.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="2" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>677</v>
+        <v>661</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>57</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="H162" s="12" t="s">
         <v>43</v>
@@ -7827,53 +7997,33 @@
         <v>43</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="2" t="s">
-        <v>688</v>
-      </c>
-      <c r="B163" s="2" t="s">
-        <v>677</v>
-      </c>
-      <c r="C163" s="2" t="s">
-        <v>689</v>
-      </c>
-      <c r="D163" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E163" s="2" t="s">
-        <v>690</v>
-      </c>
-      <c r="F163" s="2" t="s">
-        <v>691</v>
-      </c>
-      <c r="G163" s="2" t="s">
+    <row r="163" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A163" s="11" t="s">
         <v>692</v>
       </c>
-      <c r="H163" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="I163" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="J163" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="K163" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="164" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B163" s="11"/>
+      <c r="C163" s="11"/>
+      <c r="D163" s="11"/>
+      <c r="E163" s="11"/>
+      <c r="F163" s="11"/>
+      <c r="G163" s="11"/>
+      <c r="H163" s="11"/>
+      <c r="I163" s="11"/>
+      <c r="J163" s="11"/>
+      <c r="K163" s="11"/>
+    </row>
+    <row r="164" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="2" t="s">
         <v>693</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>677</v>
+        <v>692</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>694</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E164" s="2" t="s">
         <v>695</v>
@@ -7897,8 +8047,373 @@
         <v>43</v>
       </c>
     </row>
+    <row r="165" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A165" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="F165" s="2" t="s">
+        <v>701</v>
+      </c>
+      <c r="G165" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="H165" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I165" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J165" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K165" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="166" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A166" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>705</v>
+      </c>
+      <c r="F166" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="G166" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="H166" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I166" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J166" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K166" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="167" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A167" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="F167" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="G167" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="H167" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I167" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J167" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K167" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="168" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A168" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="F168" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="G168" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="H168" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I168" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J168" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K168" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="169" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A169" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="F169" s="2" t="s">
+        <v>720</v>
+      </c>
+      <c r="G169" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="H169" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I169" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J169" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K169" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="170" customFormat="false" ht="14.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A170" s="11" t="s">
+        <v>722</v>
+      </c>
+      <c r="B170" s="11"/>
+      <c r="C170" s="11"/>
+      <c r="D170" s="11"/>
+      <c r="E170" s="11"/>
+      <c r="F170" s="11"/>
+      <c r="G170" s="11"/>
+      <c r="H170" s="11"/>
+      <c r="I170" s="11"/>
+      <c r="J170" s="11"/>
+      <c r="K170" s="11"/>
+    </row>
+    <row r="171" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A171" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>724</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="F171" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="G171" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="H171" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I171" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J171" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K171" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="172" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A172" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="F172" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="G172" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="H172" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I172" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J172" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K172" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="173" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A173" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="F173" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="G173" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="H173" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I173" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J173" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K173" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="174" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A174" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="F174" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="G174" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="H174" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I174" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J174" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K174" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="175" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A175" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>722</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>745</v>
+      </c>
+      <c r="F175" s="2" t="s">
+        <v>746</v>
+      </c>
+      <c r="G175" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="H175" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="I175" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="J175" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K175" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="32">
+  <mergeCells count="33">
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A8:K8"/>
@@ -7911,26 +8426,27 @@
     <mergeCell ref="A41:K41"/>
     <mergeCell ref="A45:K45"/>
     <mergeCell ref="A56:K56"/>
-    <mergeCell ref="A64:K64"/>
+    <mergeCell ref="A62:K62"/>
     <mergeCell ref="A70:K70"/>
-    <mergeCell ref="A72:K72"/>
-    <mergeCell ref="A77:K77"/>
-    <mergeCell ref="A81:K81"/>
-    <mergeCell ref="A84:K84"/>
-    <mergeCell ref="A89:K89"/>
-    <mergeCell ref="A95:K95"/>
+    <mergeCell ref="A76:K76"/>
+    <mergeCell ref="A78:K78"/>
+    <mergeCell ref="A83:K83"/>
+    <mergeCell ref="A88:K88"/>
+    <mergeCell ref="A91:K91"/>
+    <mergeCell ref="A96:K96"/>
     <mergeCell ref="A103:K103"/>
-    <mergeCell ref="A116:K116"/>
-    <mergeCell ref="A121:K121"/>
+    <mergeCell ref="A111:K111"/>
     <mergeCell ref="A124:K124"/>
     <mergeCell ref="A129:K129"/>
     <mergeCell ref="A132:K132"/>
-    <mergeCell ref="A134:K134"/>
-    <mergeCell ref="A137:K137"/>
-    <mergeCell ref="A140:K140"/>
-    <mergeCell ref="A147:K147"/>
-    <mergeCell ref="A153:K153"/>
-    <mergeCell ref="A160:K160"/>
+    <mergeCell ref="A138:K138"/>
+    <mergeCell ref="A141:K141"/>
+    <mergeCell ref="A143:K143"/>
+    <mergeCell ref="A146:K146"/>
+    <mergeCell ref="A149:K149"/>
+    <mergeCell ref="A156:K156"/>
+    <mergeCell ref="A163:K163"/>
+    <mergeCell ref="A170:K170"/>
   </mergeCells>
   <conditionalFormatting sqref="H3:H400">
     <cfRule type="cellIs" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -7947,7 +8463,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" prompt="Choose Pass / Fail / Partial / N/A / Not run" promptTitle="Result" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H4:H7 H9:H13 H15:H20 H22:H26 H28:H30 H32 H34:H35 H37:H40 H42:H44 H46:H55 H57:H63 H65:H69 H71 H73:H76 H78:H80 H82:H83 H85:H88 H90:H94 H96:H102 H104:H115 H117:H120 H122:H123 H125:H128 H130:H131 H133 H135:H136 H138:H139 H141:H146 H148:H152 H154:H159 H161:H164" type="none">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" prompt="Choose Pass / Fail / Partial / N/A / Not run" promptTitle="Result" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H4:H7 H9:H13 H15:H20 H22:H26 H28:H30 H32 H34:H35 H37:H40 H42:H44 H46:H55 H57:H61 H63:H69 H71:H75 H77 H79:H82 H84:H87 H89:H90 H92:H95 H97:H102 H104:H110 H112:H123 H125:H128 H130:H131 H133:H137 H139:H140 H142 H144:H145 H147:H148 H150:H155 H157:H162 H164:H169 H171:H175" type="none">
       <formula1>0</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -7967,7 +8483,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B40"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17.37"/>
@@ -7976,13 +8492,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>698</v>
+        <v>748</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
-        <v>699</v>
+        <v>749</v>
       </c>
       <c r="B2" s="3"/>
     </row>
@@ -8033,7 +8549,7 @@
     </row>
     <row r="8" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>700</v>
+        <v>750</v>
       </c>
       <c r="B8" s="2" t="e">
         <f aca="false">of:=COUNTA('Test Cases'!A3:A400)-COUNTIF('Test Cases'!D3:D400,"")</f>
@@ -8042,7 +8558,7 @@
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="3" t="s">
-        <v>701</v>
+        <v>751</v>
       </c>
       <c r="B9" s="3"/>
     </row>
@@ -8141,186 +8657,195 @@
         <v>255</v>
       </c>
       <c r="B20" s="2" t="e">
+        <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Generated Material",'Test Cases'!H3:H400,"Pass")</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="8" t="s">
+        <v>280</v>
+      </c>
+      <c r="B21" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Templates",'Test Cases'!H3:H400,"Pass")</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="8" t="s">
-        <v>290</v>
-      </c>
-      <c r="B21" s="2" t="e">
+    <row r="22" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="8" t="s">
+        <v>315</v>
+      </c>
+      <c r="B22" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Rich-text insert",'Test Cases'!H3:H400,"Pass")</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="8" t="s">
-        <v>313</v>
-      </c>
-      <c r="B22" s="2" t="e">
+    <row r="23" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="B23" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Notes format",'Test Cases'!H3:H400,"Pass")</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8" t="s">
-        <v>319</v>
-      </c>
-      <c r="B23" s="2" t="e">
+    <row r="24" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="8" t="s">
+        <v>344</v>
+      </c>
+      <c r="B24" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Navigation",'Test Cases'!H3:H400,"Pass")</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="B24" s="2" t="e">
+    <row r="25" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="8" t="s">
+        <v>365</v>
+      </c>
+      <c r="B25" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Case alias",'Test Cases'!H3:H400,"Pass")</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="8" t="s">
-        <v>356</v>
-      </c>
-      <c r="B25" s="2" t="e">
+    <row r="26" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="B26" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Photo download",'Test Cases'!H3:H400,"Pass")</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="8" t="s">
-        <v>367</v>
-      </c>
-      <c r="B26" s="2" t="e">
+    <row r="27" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="B27" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Case report",'Test Cases'!H3:H400,"Pass")</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="8" t="s">
-        <v>388</v>
-      </c>
-      <c r="B27" s="2" t="e">
+    <row r="28" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="8" t="s">
+        <v>418</v>
+      </c>
+      <c r="B28" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Manager",'Test Cases'!H3:H400,"Pass")</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="8" t="s">
-        <v>414</v>
-      </c>
-      <c r="B28" s="2" t="e">
+    <row r="29" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="8" t="s">
+        <v>449</v>
+      </c>
+      <c r="B29" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Manager edit",'Test Cases'!H3:H400,"Pass")</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="8" t="s">
-        <v>448</v>
-      </c>
-      <c r="B29" s="2" t="e">
+    <row r="30" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="8" t="s">
+        <v>483</v>
+      </c>
+      <c r="B30" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"RTE editor",'Test Cases'!H3:H400,"Pass")</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="8" t="s">
-        <v>502</v>
-      </c>
-      <c r="B30" s="2" t="e">
+    <row r="31" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="8" t="s">
+        <v>537</v>
+      </c>
+      <c r="B31" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Teams",'Test Cases'!H3:H400,"Pass")</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="8" t="s">
-        <v>522</v>
-      </c>
-      <c r="B31" s="2" t="e">
+    <row r="32" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="8" t="s">
+        <v>557</v>
+      </c>
+      <c r="B32" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"History",'Test Cases'!H3:H400,"Pass")</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="8" t="s">
-        <v>531</v>
-      </c>
-      <c r="B32" s="2" t="e">
+    <row r="33" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="8" t="s">
+        <v>566</v>
+      </c>
+      <c r="B33" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Usage",'Test Cases'!H3:H400,"Pass")</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="8" t="s">
-        <v>552</v>
-      </c>
-      <c r="B33" s="2" t="e">
+    <row r="34" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="8" t="s">
+        <v>592</v>
+      </c>
+      <c r="B34" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Read-only",'Test Cases'!H3:H400,"Pass")</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="8" t="s">
-        <v>563</v>
-      </c>
-      <c r="B34" s="2" t="e">
+    <row r="35" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="8" t="s">
+        <v>603</v>
+      </c>
+      <c r="B35" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Dark mode",'Test Cases'!H3:H400,"Pass")</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="8" t="s">
-        <v>569</v>
-      </c>
-      <c r="B35" s="2" t="e">
+    <row r="36" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="8" t="s">
+        <v>609</v>
+      </c>
+      <c r="B36" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Background",'Test Cases'!H3:H400,"Pass")</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="8" t="s">
-        <v>580</v>
-      </c>
-      <c r="B36" s="2" t="e">
+    <row r="37" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="8" t="s">
+        <v>620</v>
+      </c>
+      <c r="B37" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Diagnostics",'Test Cases'!H3:H400,"Pass")</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="8" t="s">
-        <v>590</v>
-      </c>
-      <c r="B37" s="2" t="e">
+    <row r="38" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="8" t="s">
+        <v>630</v>
+      </c>
+      <c r="B38" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Security",'Test Cases'!H3:H400,"Pass")</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="8" t="s">
-        <v>621</v>
-      </c>
-      <c r="B38" s="2" t="e">
+    <row r="39" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="8" t="s">
+        <v>661</v>
+      </c>
+      <c r="B39" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Acknowledgements",'Test Cases'!H3:H400,"Pass")</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="8" t="s">
-        <v>647</v>
-      </c>
-      <c r="B39" s="2" t="e">
+    <row r="40" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="8" t="s">
+        <v>692</v>
+      </c>
+      <c r="B40" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"Suggestions",'Test Cases'!H3:H400,"Pass")</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="8" t="s">
-        <v>677</v>
-      </c>
-      <c r="B40" s="2" t="e">
+    <row r="41" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="8" t="s">
+        <v>722</v>
+      </c>
+      <c r="B41" s="2" t="e">
         <f aca="false">of:=COUNTIFS('Test Cases'!B3:B400,"UX",'Test Cases'!H3:H400,"Pass")</f>
         <v>#VALUE!</v>
       </c>
@@ -8355,88 +8880,88 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>702</v>
+        <v>752</v>
       </c>
       <c r="B1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>703</v>
+        <v>753</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>704</v>
+        <v>754</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>705</v>
+        <v>755</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>706</v>
+        <v>756</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>707</v>
+        <v>757</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>708</v>
+        <v>758</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>709</v>
+        <v>759</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>710</v>
+        <v>760</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>711</v>
+        <v>761</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>712</v>
+        <v>762</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>713</v>
+        <v>763</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>714</v>
+        <v>764</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>715</v>
+        <v>765</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>716</v>
+        <v>766</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>717</v>
+        <v>767</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>718</v>
+        <v>768</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="8" t="s">
-        <v>719</v>
+        <v>769</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>720</v>
+        <v>770</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="8" t="s">
-        <v>721</v>
+        <v>771</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>722</v>
+        <v>772</v>
       </c>
     </row>
   </sheetData>
